--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-1771346.22</v>
+        <v>7228653.78</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-1771346.2</v>
+        <v>7228653.8</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>-0.02</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>-1771346.2</v>
+        <v>7228653.8</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-1771346.2</v>
+        <v>7228653.8</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>78794048.05</v>
+        <v>69794048.05</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>78794048.05</v>
+        <v>69794048.05</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -913,7 +913,11 @@
           <t>сходится</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>из итога исключено оплаченное за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1066,7 +1070,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-1771346.2</v>
+        <v>7228653.8</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1242,7 +1246,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>78794048.05</v>
+        <v>69794048.05</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1512,7 +1516,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>23362254.56</v>
+        <v>14362254.56</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -1572,7 +1576,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>9000000</v>
+        <v>516000</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -1602,7 +1606,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>-1771346.22</v>
+        <v>7228653.78</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -1842,7 +1846,7 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-48987083.72</v>
+        <v>-44487083.72</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -1872,7 +1876,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-5322613.48</v>
+        <v>-822613.48</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -1962,7 +1966,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>19453929.54</v>
+        <v>23953929.54</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -2082,7 +2086,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>-48987083.72</v>
+        <v>-44487083.72</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -2112,7 +2116,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>3551267.27</v>
+        <v>8051267.27</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -2202,7 +2206,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>42944886.48</v>
+        <v>47444886.48</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -4252,7 +4256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4586,14 +4590,14 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ремонт нового корпуса</t>
+          <t>Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>9000000</v>
+        <v>4692500</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="21">
@@ -4604,14 +4608,14 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Урегулирование досудебного спора</t>
+          <t>Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>4692500</v>
+        <v>2505800</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="22">
@@ -4622,14 +4626,14 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Маркетинговые услуги</t>
+          <t>Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>2505800</v>
+        <v>1155000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="23">
@@ -4640,14 +4644,14 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Аренда Самокатная 1 стр1</t>
+          <t>Прочие управленческие</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1155000</v>
+        <v>878789.77</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="24">
@@ -4658,11 +4662,11 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>ЗП Заведягин ОН</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>878789.77</v>
+        <v>570005</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>0.04</v>
@@ -4676,14 +4680,14 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ЗП Заведягин ОН</t>
+          <t>Ремонт</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>570005</v>
+        <v>516000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="26">
@@ -4694,14 +4698,14 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Ремонт</t>
+          <t>Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>516000</v>
+        <v>435435</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="27">
@@ -4712,11 +4716,11 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Обслуживание 1СУправление</t>
+          <t>Фото видео</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>435435</v>
+        <v>337440</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>0.02</v>
@@ -4730,14 +4734,14 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Фото видео</t>
+          <t>Услуги юриста</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>337440</v>
+        <v>330000</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="29">
@@ -4748,14 +4752,14 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Услуги юриста</t>
+          <t>Складской учет</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>330000</v>
+        <v>320000</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="30">
@@ -4766,14 +4770,14 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Складской учет</t>
+          <t>ПО и IT-сервисы</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>320000</v>
+        <v>279349.86</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="31">
@@ -4784,14 +4788,14 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ПО и IT-сервисы</t>
+          <t>Битрикс 24</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>279349.86</v>
+        <v>264850</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="32">
@@ -4802,14 +4806,14 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Битрикс 24</t>
+          <t>Сайт</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>264850</v>
+        <v>254000</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="33">
@@ -4820,14 +4824,14 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Сайт</t>
+          <t>IT услуги</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>254000</v>
+        <v>247935.06</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34">
@@ -4838,11 +4842,11 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>IT услуги</t>
+          <t>Услуги инженера</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>247935.06</v>
+        <v>159575</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>0.01</v>
@@ -4856,11 +4860,11 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Услуги инженера</t>
+          <t>Канц и хоз расходы</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>159575</v>
+        <v>157671.72</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>0.01</v>
@@ -4874,11 +4878,11 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Канц и хоз расходы</t>
+          <t>Сервис речевой аналитики</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>157671.72</v>
+        <v>152250</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>0.01</v>
@@ -4892,11 +4896,11 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Сервис речевой аналитики</t>
+          <t>Общехозяйственные</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>152250</v>
+        <v>137116</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>0.01</v>
@@ -4910,11 +4914,11 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Общехозяйственные</t>
+          <t>Косметология</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>137116</v>
+        <v>114858</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>0.01</v>
@@ -4928,14 +4932,14 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Косметология</t>
+          <t>Реклама</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>114858</v>
+        <v>100000</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="40">
@@ -4946,14 +4950,14 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Реклама</t>
+          <t>Такси</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
         <v>100000</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="41">
@@ -4964,14 +4968,14 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Такси</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>100000</v>
+        <v>81075</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="42">
@@ -4982,14 +4986,14 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Хоз расходы</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>81075</v>
+        <v>77247</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43">
@@ -5000,11 +5004,11 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Хоз расходы</t>
+          <t>Связь</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>77247</v>
+        <v>53760</v>
       </c>
       <c r="D43" s="10" t="n">
         <v>0</v>
@@ -5018,11 +5022,11 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Связь</t>
+          <t>Кофе</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>53760</v>
+        <v>48301.44</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -5036,11 +5040,11 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Кофе</t>
+          <t>Цветы</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>48301.44</v>
+        <v>40000</v>
       </c>
       <c r="D45" s="10" t="n">
         <v>0</v>
@@ -5054,11 +5058,11 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Цветы</t>
+          <t>Программное обнспечение</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>40000</v>
+        <v>39200</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>0</v>
@@ -5072,11 +5076,11 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Программное обнспечение</t>
+          <t>Средства гигиены</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>39200</v>
+        <v>37568</v>
       </c>
       <c r="D47" s="10" t="n">
         <v>0</v>
@@ -5090,11 +5094,11 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Средства гигиены</t>
+          <t>Капвложения и работы</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>37568</v>
+        <v>29800</v>
       </c>
       <c r="D48" s="10" t="n">
         <v>0</v>
@@ -5108,11 +5112,11 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Капвложения и работы</t>
+          <t>Подбор персонала</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>29800</v>
+        <v>27629</v>
       </c>
       <c r="D49" s="10" t="n">
         <v>0</v>
@@ -5126,11 +5130,11 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Подбор персонала</t>
+          <t>Охрана</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>27629</v>
+        <v>26600</v>
       </c>
       <c r="D50" s="10" t="n">
         <v>0</v>
@@ -5144,11 +5148,11 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Охрана</t>
+          <t>Мебель, инвентарь</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>26600</v>
+        <v>22130</v>
       </c>
       <c r="D51" s="10" t="n">
         <v>0</v>
@@ -5162,11 +5166,11 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Мебель, инвентарь</t>
+          <t>Вода</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>22130</v>
+        <v>20000</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>0</v>
@@ -5180,11 +5184,11 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Вода</t>
+          <t>Техподдержка ККТ</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>20000</v>
+        <v>17900</v>
       </c>
       <c r="D53" s="10" t="n">
         <v>0</v>
@@ -5198,11 +5202,11 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Техподдержка ККТ</t>
+          <t>Электрооборудование</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>17900</v>
+        <v>17740</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>0</v>
@@ -5216,11 +5220,11 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Электрооборудование</t>
+          <t>Интернет</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>17740</v>
+        <v>16235.15</v>
       </c>
       <c r="D55" s="10" t="n">
         <v>0</v>
@@ -5234,11 +5238,11 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Интернет</t>
+          <t>Расходник</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>16235.15</v>
+        <v>15120</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>0</v>
@@ -5252,11 +5256,11 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Расходник</t>
+          <t>Аренда кофемашины</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>15120</v>
+        <v>15000</v>
       </c>
       <c r="D57" s="10" t="n">
         <v>0</v>
@@ -5270,11 +5274,11 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Аренда кофемашины</t>
+          <t>Дизайн-услуги</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>15000</v>
+        <v>11660</v>
       </c>
       <c r="D58" s="10" t="n">
         <v>0</v>
@@ -5288,11 +5292,11 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Дизайн-услуги</t>
+          <t>Обучение персонала</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>11660</v>
+        <v>10900</v>
       </c>
       <c r="D59" s="10" t="n">
         <v>0</v>
@@ -5306,11 +5310,11 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Обучение персонала</t>
+          <t>Общехоз.расходы прочие</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>10900</v>
+        <v>10000</v>
       </c>
       <c r="D60" s="10" t="n">
         <v>0</v>
@@ -5324,7 +5328,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Общехоз.расходы прочие</t>
+          <t>ПроДокторов</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
@@ -5342,11 +5346,11 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>ПроДокторов</t>
+          <t>Доставка</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>10000</v>
+        <v>7495</v>
       </c>
       <c r="D62" s="10" t="n">
         <v>0</v>
@@ -5360,11 +5364,11 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Доставка</t>
+          <t>ТО СКУД, пожарной сигнализации</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>7495</v>
+        <v>7000</v>
       </c>
       <c r="D63" s="10" t="n">
         <v>0</v>
@@ -5378,11 +5382,11 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>ТО СКУД, пожарной сигнализации</t>
+          <t>Оргтехника</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>7000</v>
+        <v>5100</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>0</v>
@@ -5396,11 +5400,11 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Оргтехника</t>
+          <t>Обслуживание аквариума</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="D65" s="10" t="n">
         <v>0</v>
@@ -5414,63 +5418,45 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Обслуживание аквариума</t>
+          <t>Услуги банка</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>5000</v>
+        <v>1218.56</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Услуги банка</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="n">
-        <v>1218.56</v>
-      </c>
-      <c r="D67" s="10" t="n">
-        <v>0</v>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>14362254.56</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>Управленческие</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="n">
-        <v>23362254.56</v>
-      </c>
-      <c r="D68" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr"/>
-      <c r="C69" s="14" t="n">
-        <v>78794048.05</v>
-      </c>
-      <c r="D69" s="15" t="n"/>
+      <c r="B68" s="13" t="inlineStr"/>
+      <c r="C68" s="14" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D68" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7887,13 +7873,13 @@
         </is>
       </c>
       <c r="C9" s="18" t="n">
-        <v>-48987083.72</v>
+        <v>-44487083.72</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>-48987083.72</v>
+        <v>-44487083.72</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-97974167.44</v>
+        <v>-88974167.44</v>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
@@ -8035,13 +8021,13 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>-39397024.02</v>
+        <v>-34897024.02</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>-39397024.02</v>
+        <v>-34897024.02</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>-78794048.04000001</v>
+        <v>-69794048.04000001</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -8057,13 +8043,13 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>-5322613.48</v>
+        <v>-822613.48</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>3551267.27</v>
+        <v>8051267.27</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-1771346.2</v>
+        <v>7228653.8</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -8135,13 +8121,13 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>19453929.54</v>
+        <v>23953929.54</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>42944886.48</v>
+        <v>47444886.48</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>62398816.03</v>
+        <v>71398816.03</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -8297,13 +8283,13 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>-14362254.56</v>
+        <v>-13846254.56</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7347085.16</v>
+        <v>7863085.16</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="10">
@@ -8316,13 +8302,13 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>-9000000</v>
+        <v>-516000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-1652914.84</v>
+        <v>7347085.16</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -8338,7 +8324,7 @@
         <v>-514768.62</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-2167683.46</v>
+        <v>6832316.54</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0.5</v>
@@ -8357,7 +8343,7 @@
         <v>396337.24</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>-1771346.22</v>
+        <v>7228653.78</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>0.4</v>
@@ -8373,13 +8359,13 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>-1771346.22</v>
+        <v>7228653.78</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>-1771346.22</v>
+        <v>7228653.78</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -17,6 +17,9 @@
     <sheet name="07 Учредители" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="08 Водопад" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="09 Контроль" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11 Классификация расходов" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12 Июль-август" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13 Разнесение выручки" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -114,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +175,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -972,6 +984,3752 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E127"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Счёт 60: как классифицирован каждый контрагент</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Проверьте столбец «основание» — по нему видно, откуда взялась категория</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Контрагент</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Оплачено с р/с</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Блок</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Основание</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Маркарян Максим Рачьянович ИП</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>10966274</v>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>КВАЛИТЕТ ООО</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Ремонт нового корпуса</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>БУРДИНА Е.С. ИП</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5382764</v>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Сехина Виктория Дмитриевна</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4692500</v>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Урегулирование досудебного спора</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Ужахов Тимур Магомедович ИП</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>4518074</v>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>КЛОВЕРМЕД ООО</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>4196900</v>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Импланты</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Завиркин Антон Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>2887658</v>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>ИП Завиркин А.В.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Маржохов Астемир Ануарович ИП</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2811745</v>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Габеев Алан Ирбекович ИП</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2631347</v>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Ласукова Екатерина Борисовна</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2505800</v>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Маркетинговые услуги</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Пономарёва Елена Юрьевна ИП</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2272677</v>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>БУРДИН С. А. ИП</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>2227217</v>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Ханукаев Александр Ильич</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2210015</v>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>СистеМед ООО</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1857678.61</v>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1740957</v>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1337422</v>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>ДельтаМед ООО</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1157543.1</v>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Расходка</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Никифоров Сергей Арнольдович</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Аренда Самокатная 1 стр1</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Врачев Владислав Юрьевич ИП</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>927938</v>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Береснев Алексей Игоревич ИП</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>792876</v>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Макеенко Николай Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>703266</v>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>ИП КАЧАЯН В.А. ИП</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>656611</v>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Чугуевская Ирина Сергеевна ИП</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>570005</v>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>ЗП Заведягин ОН</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>СИРИУС ММ ООО</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>550653.36</v>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Расходка</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Громова Наталья Юрьевна ИП</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>516000</v>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Ремонт</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>КИТ МЕД ООО</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>515528</v>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>18550-расходка, 320588-мед.оборудованеи</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>ЦВ ПРОТЕК АО</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>477406.58</v>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Лекарства</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>ИТ-ЭКСПЕРТ ООО</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>435435</v>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Обслуживание 1СУправление</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>АЛЬДЖЕНСА ООО</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>376950</v>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Питание</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>ВИТТА КОМПАНИ ООО</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>349946.07</v>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Лекарства</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>331000</v>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Импланты</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Электростальский филиал МОКА</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>330000</v>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Услуги юриста</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Самозанятый Завиркина Лилия Викторовна</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>320000</v>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Складской учет</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Стародубов Дмитрий Александрович ИП</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>293400</v>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>ПФ СКБ Контур АО</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>279349.86</v>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>ПО и IT-сервисы</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Выскуб Ольга Анатольевна ИП</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>275300</v>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>РОКЕТ СЕРВИС ООО</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>264850</v>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Битрикс 24</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>ГЕРАСИМОВА А.В. ИП</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>260766</v>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>Хафизов Станислав Ильшатович ИП</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>254000</v>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Сайт</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>КРЕЙТ ООО</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>246913.68</v>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>МЕДПРО ООО</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>235200</v>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Белье</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>ЛЕ МОНЛИД ООО</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>222551.24</v>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>Рыболова Анастасия Алексеевна ИП</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>220000</v>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Расходка</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>Богачко Елизавета Максимовна ИП</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>210000</v>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Аренда Inmode</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>МЕДИНТОРГ АО</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>206303.7</v>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Расходка</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>181735.9</v>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Кровь</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>ПЗСПП ООО</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>179400</v>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>БЕЛВА ООО ПТК</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>173834.16</v>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Самозанятый Маланичев Юрий Васильевич</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>159575</v>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Услуги инженера</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>КОМУС ООО</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>157671.72</v>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Канц и хоз расходы</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>ИМОТИО ООО</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>152250</v>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Сервис речевой аналитики</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Кудря Дарья Сергеевна ИП</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>149600</v>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Фото видео</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>АЛКАНА А ООО</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>146600</v>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>ИТМЕДИКАЛ ООО</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>136000</v>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>ТД ТИНКО ООО</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>118740.75</v>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Елизаров Андрей Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>118735.06</v>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>IT услуги</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>А410 ООО</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>114858</v>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Косметология</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Ершов Эдуард Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>111300</v>
+      </c>
+      <c r="C62" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Фото видео</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>МИА ООО</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C63" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Белье</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Дубровина Юлия Игоревна ИП</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>104374</v>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>фамилия совпала с врачом из управленки</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>102102</v>
+      </c>
+      <c r="C65" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Анализы</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Звоник Юрий Алексеевич</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C66" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Реклама</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>ЯНДЕКС.ТАКСИ ООО</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C67" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Такси</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>ТЕХПРОФИТ ООО</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>99200</v>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>IT услуги</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>90100</v>
+      </c>
+      <c r="C69" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>ДельтаМедКомпани ООО</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>87600</v>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Расходка</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>ЦЕНТР-ОТЕЛЬ ООО</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>81075</v>
+      </c>
+      <c r="C72" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>М-ИНВЕСТ ООО</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>77412</v>
+      </c>
+      <c r="C73" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>77247</v>
+      </c>
+      <c r="C74" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Хоз расходы</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>ДЕЗНЭТ ООО</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>76940</v>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>Самозанятый Лукина Екатерина Витальевна</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>76540</v>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Фото видео</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>Самозанятый Орлов Сергей Юрьевич</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>72360</v>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Общехозяйственные</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t>Евтеев Александр Викторович Самозанятый</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>64756</v>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Общехозяйственные</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>АЛКАНА М ООО</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>64600</v>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>СитиМед ООО</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>63600</v>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>ЭКОТЕХПРОМ АО</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>52136.72</v>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Вывоз ТКО и мед отходов</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>51760</v>
+      </c>
+      <c r="C83" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>КРИОФАРМ ООО</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>51675</v>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>БАРИСТА ООО</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>48301.44</v>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Кофе</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>СИСТЕМА ООО</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>48285.78</v>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>Семин Сергей Владиславович</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Цветы</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>КОЛТАЧ СОЛЮШНС ООО</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>39200</v>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Программное обнспечение</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>СМБ-СЕРВИС ООО</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>37700</v>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>ГРАНД КОМФОРТ ООО</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>37568</v>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Средства гигиены</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>ДОКТОР ДИСКАУНТ ООО</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>35920.61</v>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>Селектел АО</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>IT услуги</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>МЕДЛИГА АО</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>29800</v>
+      </c>
+      <c r="C93" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Капвложения и работы</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>кор. счета 08, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>ХЭДХАНТЕР ООО</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>27629</v>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Подбор персонала</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="22" t="inlineStr">
+        <is>
+          <t>ЭКМУС ООО</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="n">
+        <v>23625</v>
+      </c>
+      <c r="C95" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>утилизация мед отходов до июль-октябрь</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>22130</v>
+      </c>
+      <c r="C96" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Мебель, инвентарь</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="22" t="inlineStr">
+        <is>
+          <t>МАНГО ТЕЛЕКОМ ООО</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C97" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>ТАТАРОВА В. Г. ИП</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C98" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Вода</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="22" t="inlineStr">
+        <is>
+          <t>ТАКСКОМ ООО</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>17900</v>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Техподдержка ККТ</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>МРК-СНАБ ООО</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>17750</v>
+      </c>
+      <c r="C100" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Расходка</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="22" t="inlineStr">
+        <is>
+          <t>ОнЛайн Трейд ООО</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>17740</v>
+      </c>
+      <c r="C101" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Электрооборудование</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>КантриКом АО</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>17568</v>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="22" t="inlineStr">
+        <is>
+          <t>ЧОО Спектр секъюрити ООО</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>16800</v>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Охрана</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>ВЕСТ КОЛЛ ЛТД ООО</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>16235.15</v>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Интернет</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="22" t="inlineStr">
+        <is>
+          <t>ТЕЛЕМИР ООО</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>16192</v>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Связь</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>ИНСТРУ-МЕД ООО</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>15120</v>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Расходник</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="22" t="inlineStr">
+        <is>
+          <t>Алдошин Павел Александрович ИП</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C107" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Аренда кофемашины</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t>Вилорд ООО</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>12800</v>
+      </c>
+      <c r="C108" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t>ГБУЗ ЦЛО ДЗМ</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="n">
+        <v>12760</v>
+      </c>
+      <c r="C109" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Наркотики</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>АТОЛ ОНЛАЙН ООО</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>12505</v>
+      </c>
+      <c r="C110" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="22" t="inlineStr">
+        <is>
+          <t>Самозанятый Кожина Наталия Васильевна</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>11660</v>
+      </c>
+      <c r="C111" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Дизайн-услуги</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="22" t="inlineStr">
+        <is>
+          <t>АСПРОМЕД ООО</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>10940</v>
+      </c>
+      <c r="C112" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Расходка</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="22" t="inlineStr">
+        <is>
+          <t>МГУТУ АНО ДПО</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>10900</v>
+      </c>
+      <c r="C113" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Обучение персонала</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>АО "Почта России"</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C114" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Общехоз.расходы прочие</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="22" t="inlineStr">
+        <is>
+          <t>МЕДРОКЕТ ООО</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C115" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>ПроДокторов</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>ТЕХМОНТАЖ ООО</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>9800</v>
+      </c>
+      <c r="C116" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Охрана</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>Деловые линии ООО</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="n">
+        <v>7495</v>
+      </c>
+      <c r="C117" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>ТЕХМОНТАЖСЕРВИС ООО</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C118" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>ТО СКУД, пожарной сигнализации</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="22" t="inlineStr">
+        <is>
+          <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>6135</v>
+      </c>
+      <c r="C119" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>Самозанятый Кучер Татьяна Александровна</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C120" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="22" t="inlineStr">
+        <is>
+          <t>ДЕАЛМЕД АО</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>5170</v>
+      </c>
+      <c r="C121" s="22" t="inlineStr">
+        <is>
+          <t>Медицинские</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>кор. счёт 10 — материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>ИНФОТЕХ ООО</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>5100</v>
+      </c>
+      <c r="C122" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Оргтехника</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="22" t="inlineStr">
+        <is>
+          <t>Аквапрактика ООО</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C123" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Обслуживание аквариума</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>назначение платежа за июнь</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="22" t="inlineStr">
+        <is>
+          <t>Cамозанятый Котлярова Олеся Владимировна</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C124" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="22" t="inlineStr">
+        <is>
+          <t>АО "Альфа Банк"</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="n">
+        <v>668.5599999999999</v>
+      </c>
+      <c r="C125" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Услуги банка</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>БАНК ВТБ (ПАО)</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="C126" s="22" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Услуги банка</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>ручная пометка</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="23" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>78794048.05</v>
+      </c>
+      <c r="C127" s="23" t="inlineStr"/>
+      <c r="D127" s="16" t="inlineStr"/>
+      <c r="E127" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Что изменилось против июля</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Из расходов исключено оплаченное за счёт кредитной линии: 6 545 366,22 в июле и 9 000 000 в августе</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Разница</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Выручка</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>108126415.72</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>95806484</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>-12319931.72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Налоги с ФОТ</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6370709.49</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6135792.28</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-234917.21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Зарплата</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>12148685.72</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>12490831.85</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>342146.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Расходы по кассе</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1170</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-1170</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Услуги банка (общие)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>399308.17</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>141281.46</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-258026.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Эквайринг (персонально)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>41563.8</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>331923.36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Алименты</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>23201.61</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>38726.66</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>15525.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>% по кредиту</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>151764.47</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>-151764.47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Поставщики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>53416727.72</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>16377320.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>72553130.98</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>88974167.45999999</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>16421036.48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>ДОХОД (выручка − расходы)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>35573284.74</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>6832316.54</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>-28740968.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Внутри поставщиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Разница</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>25223566</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>39819623</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>14596057</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Аренда Самокатная 1 стр.1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>4462500</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-3307500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Коммунальные услуги</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>224103.63</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-224103.63</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Досудебный спор</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>4692500</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>4692500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Прочие поставщики</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>23506558.09</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>24126925.05</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>620366.96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>53416727.72</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>16377320.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Как выручка разложена по группам</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>01–10.08 — старая программа по фактической оплате; 11–31.08 — новая, платежи с врачом напрямую, авансы — через пациента</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>01–10.08, старая управленка</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>29748144</v>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>«Отчет по врачам (УК)», колонка «Фактическая оплата»</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>11–31.08, новая управленка</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>66058340</v>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>ИТОГО ВЫРУЧКА</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>95806484</v>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>деньги, поступившие за месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>из них привязано к врачу напрямую</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>46412341</v>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>документы «Оказание услуг» — врач указан в документе</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>авансы, разнесённые через пациента</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>14598500</v>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>оплата картой и кассовые ордера</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>авансы без совпадения по пациенту</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>5078499</v>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>разнесены пропорционально; пациентов нет в реестре услуг августа</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>01–10.08</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>11–31.08</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Доля</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Маланичев</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n">
+        <v>4180781.46</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Погосян</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>13054662.21</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Другие хирурги</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n">
+        <v>75249046.11</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Прочие доходы</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n">
+        <v>271238.64</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Косметология</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n">
+        <v>3050755.58</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>95806484</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1426,7 +5184,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1936,7 +5694,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -2176,7 +5934,7 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
@@ -3902,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>4180781.46</v>
@@ -3928,7 +7686,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>13054662.21</v>
@@ -3954,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>75249046.11</v>
@@ -3980,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>271238.64</v>
@@ -4006,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3050755.58</v>
@@ -4032,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>95806484</v>
@@ -7931,13 +11689,13 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -8003,13 +11761,13 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -8095,13 +11853,13 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>78794048.05</v>
+        <v>80794048.05</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>78794048.05</v>
+        <v>80794048.05</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0</v>
@@ -1044,50 +1044,50 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>Маркарян Максим Рачьянович ИП</t>
+          <t>КВАЛИТЕТ ООО</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>10966274</v>
+        <v>11000000</v>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Управленческие</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Гонорары ИП хирургов</t>
+          <t>Ремонт нового корпуса</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>фамилия совпала с врачом из управленки</t>
+          <t>назначение платежа</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>КВАЛИТЕТ ООО</t>
+          <t>Маркарян Максим Рачьянович ИП</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>9000000</v>
+        <v>10966274</v>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>Управленческие</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Ремонт нового корпуса</t>
+          <t>Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>назначение платежа</t>
+          <t>фамилия совпала с врачом из управленки</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="B127" s="9" t="n">
-        <v>78794048.05</v>
+        <v>80794048.05</v>
       </c>
       <c r="C127" s="23" t="inlineStr"/>
       <c r="D127" s="16" t="inlineStr"/>
@@ -4134,7 +4134,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Из расходов исключено оплаченное за счёт кредитной линии: 6 545 366,22 в июле и 9 000 000 в августе</t>
+          <t>Из расходов исключено оплаченное за счёт кредитной линии: 6 545 366,22 в июле и 11 000 000 в августе</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>672731579.65</v>
+        <v>674731579.65</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>656380332.66</v>
+        <v>658380332.66</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -9262,30 +9262,30 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Маркарян Максим Рачьянович ИП</t>
+          <t>КВАЛИТЕТ ООО</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>10966274</v>
+        <v>11000000</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Гонорары ИП хирургов</t>
+          <t>Ремонт Самокатная 1 стр12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>КВАЛИТЕТ ООО</t>
+          <t>Маркарян Максим Рачьянович ИП</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>9000000</v>
+        <v>10966274</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Ремонт Самокатная 1 стр12</t>
+          <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="B126" s="9" t="n">
-        <v>78794048.05</v>
+        <v>80794048.05</v>
       </c>
       <c r="C126" s="8" t="inlineStr"/>
     </row>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>9000000</v>
+        <v>11000000</v>
       </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="7" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>78794048.05</v>
+        <v>80794048.05</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>672731579.65</v>
+        <v>674731579.65</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>656380332.66</v>
+        <v>658380332.66</v>
       </c>
       <c r="D21" s="16" t="inlineStr"/>
     </row>
@@ -11458,7 +11458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11620,64 +11620,72 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>+ ½ процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>198168.62</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>198168.62</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>проценты по депозитам / 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>− Доля расходов, в том числе:</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C10" s="18" t="n">
         <v>-44487083.72</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D10" s="18" t="n">
         <v>-44487083.72</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E10" s="18" t="n">
         <v>-88974167.44</v>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>½ общих + персональные</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      налоги с ФОТ (68.90 + 69)</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>-3067896.14</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>-3067896.14</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>-6135792.28</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      зарплата по банку</t>
+          <t xml:space="preserve">      налоги с ФОТ (68.90 + 69)</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>-6245415.92</v>
+        <v>-3067896.14</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-6245415.92</v>
+        <v>-3067896.14</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-12490831.84</v>
+        <v>-6135792.28</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -11685,17 +11693,17 @@
       <c r="A12" s="4" t="inlineStr"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      расходы по кассе</t>
+          <t xml:space="preserve">      зарплата по банку</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0</v>
+        <v>-6245415.92</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>-6245415.92</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0</v>
+        <v>-12490831.84</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -11703,17 +11711,17 @@
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      услуги банка (общие)</t>
+          <t xml:space="preserve">      расходы по кассе</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-70640.73</v>
+        <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-70640.73</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-141281.46</v>
+        <v>0</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -11721,17 +11729,17 @@
       <c r="A14" s="4" t="inlineStr"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      услуги банка (эквайринг, персонально)</t>
+          <t xml:space="preserve">      услуги банка (общие)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-186743.58</v>
+        <v>-70640.73</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-186743.58</v>
+        <v>-70640.73</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-373487.16</v>
+        <v>-141281.46</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -11739,17 +11747,17 @@
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      алименты (удержание из ЗП)</t>
+          <t xml:space="preserve">      услуги банка (эквайринг, персонально)</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-19363.33</v>
+        <v>-186743.58</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-19363.33</v>
+        <v>-186743.58</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-38726.66</v>
+        <v>-373487.16</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -11757,17 +11765,17 @@
       <c r="A16" s="4" t="inlineStr"/>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      дополнительные корректировки</t>
+          <t xml:space="preserve">      алименты (удержание из ЗП)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0</v>
+        <v>-19363.33</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0</v>
+        <v>-19363.33</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>-38726.66</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -11775,69 +11783,61 @@
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">      дополнительные корректировки</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">      поставщики (счёт 60) + Халва</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C18" s="6" t="n">
         <v>-34897024.02</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D18" s="6" t="n">
         <v>-34897024.02</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E18" s="6" t="n">
         <v>-69794048.04000001</v>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>ДОХОД ЗА МЕСЯЦ (шаги 1–5)</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
+      <c r="F18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>ДОХОД ЗА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
         <v>-822613.48</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D19" s="9" t="n">
         <v>8051267.27</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E19" s="9" t="n">
         <v>7228653.8</v>
       </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>шаги 1–5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>+ Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>45275972.21</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>75934868.23</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>сумма шагов выше</t>
         </is>
       </c>
     </row>
@@ -11849,17 +11849,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>− Удержано в резерв (аренда)</t>
+          <t>+ Остаток с прошлого месяца</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>0</v>
+        <v>30658896.02</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0</v>
+        <v>45275972.21</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0</v>
+        <v>75934868.23</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -11868,28 +11868,54 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>− Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-11764706</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C22" s="9" t="n">
         <v>23953929.54</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D22" s="9" t="n">
         <v>47444886.48</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E22" s="9" t="n">
         <v>71398816.03</v>
       </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>шаги 6 + 7 − 8</t>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>доход + остаток − дивиденды − резерв</t>
         </is>
       </c>
     </row>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="# ##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00;-#,##0.00;—"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
   </numFmts>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -829,11 +829,7 @@
           <t>сходится</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>часть месяца без разбивки по каналам</t>
-        </is>
-      </c>
+      <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -5094,7 +5090,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24293400</v>
+        <v>31243030</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -5124,7 +5120,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>41764940</v>
+        <v>64563454</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -7781,10 +7777,10 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>24293400</v>
+        <v>31243030</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>41764940</v>
+        <v>64563454</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>0</v>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7228653.78</v>
+        <v>9129603.779999999</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>7228653.8</v>
+        <v>9129603.800000001</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>-0.02</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>7228653.8</v>
+        <v>9129603.800000001</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>7228653.8</v>
+        <v>9129603.800000001</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -4166,10 +4166,10 @@
         <v>108126415.72</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-12319931.72</v>
+        <v>-10418981.72</v>
       </c>
     </row>
     <row r="6">
@@ -4326,10 +4326,10 @@
         <v>35573284.74</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>6832316.54</v>
+        <v>8733266.539999999</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>-28740968.2</v>
+        <v>-26840018.2</v>
       </c>
     </row>
     <row r="17">
@@ -4658,7 +4658,7 @@
         <v>13054662.21</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16">
@@ -4670,7 +4670,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n">
-        <v>75249046.11</v>
+        <v>77250611.63</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0.79</v>
@@ -4685,7 +4685,7 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n">
-        <v>271238.64</v>
+        <v>261238.64</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n">
-        <v>3050755.58</v>
+        <v>2960140.06</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0.03</v>
@@ -4715,7 +4715,7 @@
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>1</v>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7228653.8</v>
+        <v>9129603.800000001</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>792457101.51</v>
+        <v>794358051.51</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3090531.74</v>
+        <v>3151852.71</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>31243030</v>
+        <v>34981900</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>64563454</v>
+        <v>61654454</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0</v>
+        <v>1071080</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>7228653.78</v>
+        <v>9129603.779999999</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>37624523.05</v>
+        <v>38625305.81</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1660997.11</v>
+        <v>1610689.35</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-822613.48</v>
+        <v>127861.52</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>23953929.54</v>
+        <v>24904404.54</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>37624523.05</v>
+        <v>38625305.81</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1660997.11</v>
+        <v>1610689.35</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>8051267.27</v>
+        <v>9001742.27</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>47444886.48</v>
+        <v>48395361.48</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>1197075</v>
+        <v>4365745</v>
       </c>
       <c r="M5" s="6" t="n"/>
       <c r="N5" s="6" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>4598500</v>
+        <v>2545000</v>
       </c>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n"/>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>4484200</v>
+        <v>4277000</v>
       </c>
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>4073500</v>
+        <v>4552200</v>
       </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
@@ -6417,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>3208094</v>
+        <v>2728594</v>
       </c>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>2403200</v>
+        <v>1615200</v>
       </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>2301500</v>
+        <v>3019500</v>
       </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>1938000</v>
+        <v>3852280</v>
       </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>3858000</v>
+        <v>1491000</v>
       </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
@@ -6627,7 +6627,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>1686075</v>
+        <v>3202575</v>
       </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0</v>
@@ -7688,7 +7688,7 @@
         <v>13054662.21</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H6" s="6" t="n"/>
     </row>
@@ -7711,7 +7711,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>75249046.11</v>
+        <v>77250611.63</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.79</v>
@@ -7737,7 +7737,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>271238.64</v>
+        <v>261238.64</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3050755.58</v>
+        <v>2960140.06</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.03</v>
@@ -7777,19 +7777,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>31243030</v>
+        <v>34981900</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>64563454</v>
+        <v>61654454</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0</v>
+        <v>1071080</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>1</v>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="D21" s="12" t="n"/>
     </row>
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>37624523.05</v>
+        <v>38625305.81</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>37624523.05</v>
+        <v>38625305.81</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>75249046.11</v>
+        <v>77250611.63</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -11575,13 +11575,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1525377.79</v>
+        <v>1480070.03</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1525377.79</v>
+        <v>1480070.03</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>3050755.58</v>
+        <v>2960140.06</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -11601,13 +11601,13 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>135619.32</v>
+        <v>130619.32</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>135619.32</v>
+        <v>130619.32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>271238.64</v>
+        <v>261238.64</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -11823,13 +11823,13 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>-822613.48</v>
+        <v>127861.52</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>8051267.27</v>
+        <v>9001742.27</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>7228653.8</v>
+        <v>9129603.800000001</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -11901,13 +11901,13 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>23953929.54</v>
+        <v>24904404.54</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>47444886.48</v>
+        <v>48395361.48</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>71398816.03</v>
+        <v>73299766.03</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
@@ -11987,10 +11987,10 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>95806484</v>
+        <v>97707434</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>100</v>
@@ -12009,10 +12009,10 @@
         <v>-39819623</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>55986861</v>
+        <v>57887811</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="7">
@@ -12028,10 +12028,10 @@
         <v>-15612170.49</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>40374690.51</v>
+        <v>42275640.51</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -12047,10 +12047,10 @@
         <v>-18665350.79</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>21709339.72</v>
+        <v>23610289.72</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="9">
@@ -12066,10 +12066,10 @@
         <v>-13846254.56</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7863085.16</v>
+        <v>9764035.16</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="10">
@@ -12085,7 +12085,7 @@
         <v>-516000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7347085.16</v>
+        <v>9248035.16</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0.5</v>
@@ -12104,7 +12104,7 @@
         <v>-514768.62</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6832316.54</v>
+        <v>8733266.539999999</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0.5</v>
@@ -12123,7 +12123,7 @@
         <v>396337.24</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>7228653.78</v>
+        <v>9129603.779999999</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>0.4</v>
@@ -12139,13 +12139,13 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>7228653.78</v>
+        <v>9129603.779999999</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>7228653.78</v>
+        <v>9129603.779999999</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -1598,17 +1598,17 @@
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>Управленческие</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>ЗП Заведягин ОН</t>
+          <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>назначение платежа за июнь</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>55431793.49</v>
+        <v>56001798.49</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>14362254.56</v>
+        <v>13792249.56</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>39819623</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="5">
@@ -8164,11 +8164,11 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>18550-расходка, 320588-мед.оборудованеи</t>
+          <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>515528</v>
+        <v>570005</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>0.01</v>
@@ -8182,11 +8182,11 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Питание</t>
+          <t>18550-расходка, 320588-мед.оборудованеи</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>376950</v>
+        <v>515528</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>0.01</v>
@@ -8200,11 +8200,11 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Белье</t>
+          <t>Питание</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>345200</v>
+        <v>376950</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>0.01</v>
@@ -8218,14 +8218,14 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Аренда Inmode</t>
+          <t>Белье</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>210000</v>
+        <v>345200</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="14">
@@ -8236,11 +8236,11 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Кровь</t>
+          <t>Аренда Inmode</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>181735.9</v>
+        <v>210000</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>0</v>
@@ -8254,11 +8254,11 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Анализы</t>
+          <t>Кровь</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>102102</v>
+        <v>181735.9</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>0</v>
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Вывоз ТКО и мед отходов</t>
+          <t>Анализы</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>52136.72</v>
+        <v>102102</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>0</v>
@@ -8290,11 +8290,11 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>утилизация мед отходов до июль-октябрь</t>
+          <t>Вывоз ТКО и мед отходов</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>23625</v>
+        <v>52136.72</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>0</v>
@@ -8308,50 +8308,50 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>утилизация мед отходов до июль-октябрь</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>23625</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Медицинские + ИП</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Наркотики</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C19" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="D18" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>55431793.49</v>
-      </c>
-      <c r="D19" s="11" t="n">
+      <c r="C20" s="9" t="n">
+        <v>56001798.49</v>
+      </c>
+      <c r="D20" s="11" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Управленческие</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Урегулирование досудебного спора</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>4692500</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>0.33</v>
       </c>
     </row>
     <row r="21">
@@ -8362,14 +8362,14 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Маркетинговые услуги</t>
+          <t>Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>2505800</v>
+        <v>4692500</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="22">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Аренда Самокатная 1 стр1</t>
+          <t>Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1155000</v>
+        <v>2505800</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="23">
@@ -8398,14 +8398,14 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>878789.77</v>
+        <v>1155000</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">
@@ -8416,14 +8416,14 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ЗП Заведягин ОН</t>
+          <t>Прочие управленческие</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>570005</v>
+        <v>878789.77</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="25">
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>14362254.56</v>
+        <v>13792249.56</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>1</v>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>ЗП Заведягин ОН</t>
+          <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
     </row>
@@ -12025,13 +12025,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-15612170.49</v>
+        <v>-16182175.49</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>42275640.51</v>
+        <v>41705635.51</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="8">
@@ -12047,7 +12047,7 @@
         <v>-18665350.79</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>23610289.72</v>
+        <v>23040284.72</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>19.1</v>
@@ -12063,13 +12063,13 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>-13846254.56</v>
+        <v>-13276249.56</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>9764035.16</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="10">

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -1678,12 +1678,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>18550-расходка, 320588-мед.оборудованеи</t>
+          <t>Медоборудование и расходники</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>назначение платежа за июнь</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3303,12 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>утилизация мед отходов до июль-октябрь</t>
+          <t>Утилизация медотходов</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>назначение платежа за июнь</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>18550-расходка, 320588-мед.оборудованеи</t>
+          <t>Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>утилизация мед отходов до июль-октябрь</t>
+          <t>Утилизация медотходов</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>18550-расходка, 320588-мед.оборудованеи</t>
+          <t>Медоборудование и расходники</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>утилизация мед отходов до июль-октябрь</t>
+          <t>Утилизация медотходов</t>
         </is>
       </c>
     </row>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +175,51 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -584,108 +629,108 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>01 Цифры отчёта</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Каждая цифра из HTML-отчёта: значение, формула, источник. Главный лист расшифровки.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>02 Выручка по дням</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Дневная выручка по группам врачей и каналам оплаты + сверка с онлайн-кассой.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>03 Выручка структура</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Итоги по группам врачей и каналам поступления, доли в выручке, комиссия эквайринга.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>04 Расходы категории</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Счёт 60 в разрезе статей: медицинские + ИП и управленческие.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>05 Расходы контрагенты</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Счёт 60 построчно по контрагентам с назначением платежа.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>06 ДДС сч.51</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Обороты расчётного счёта: поступления и списания по корреспондирующим счетам.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>07 Учредители</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Методика 50/50 по шагам: выручка, доли расходов, доход, остаток, резерв, к выплате.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>08 Водопад</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>От выручки к доходу месяца — те же шаги, что на графике «Куда уходит выручка».</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>09 Контроль</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Контрольные равенства: сходится ли отчёт сам с собой и с данными бухгалтерии.</t>
         </is>
@@ -788,7 +833,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Сумма выручки по группам = итог выручки</t>
         </is>
@@ -810,7 +855,7 @@
       <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Касса + эквайринг + р/с физлиц − возвраты = итог выручки</t>
         </is>
@@ -832,7 +877,7 @@
       <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Сумма шагов водопада = доход месяца</t>
         </is>
@@ -858,7 +903,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Доход Маланичева + Погосяна = доход компании</t>
         </is>
@@ -880,7 +925,7 @@
       <c r="F8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Расходы 60: медицинские + управленческие = итог по счёту</t>
         </is>
@@ -902,7 +947,7 @@
       <c r="F9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Расходы 60: сумма по контрагентам = итог по счёту</t>
         </is>
@@ -928,7 +973,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>ДДС: сальдо нач. + приход − расход = сальдо кон.</t>
         </is>
@@ -950,7 +995,7 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Выручка (отчёт) vs выручка кассовым методом (график динамики)</t>
         </is>
@@ -1038,7 +1083,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -1046,7 +1091,7 @@
       <c r="B5" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1063,7 +1108,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -1071,7 +1116,7 @@
       <c r="B6" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1088,7 +1133,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -1096,7 +1141,7 @@
       <c r="B7" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1113,7 +1158,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -1121,7 +1166,7 @@
       <c r="B8" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1138,7 +1183,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -1146,7 +1191,7 @@
       <c r="B9" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1163,7 +1208,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -1171,7 +1216,7 @@
       <c r="B10" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1188,7 +1233,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -1196,7 +1241,7 @@
       <c r="B11" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1213,7 +1258,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -1221,7 +1266,7 @@
       <c r="B12" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1238,7 +1283,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -1246,7 +1291,7 @@
       <c r="B13" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1263,7 +1308,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -1271,7 +1316,7 @@
       <c r="B14" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1288,7 +1333,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -1296,7 +1341,7 @@
       <c r="B15" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1313,7 +1358,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -1321,7 +1366,7 @@
       <c r="B16" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1338,7 +1383,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -1346,7 +1391,7 @@
       <c r="B17" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1363,7 +1408,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -1371,7 +1416,7 @@
       <c r="B18" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1388,7 +1433,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -1396,7 +1441,7 @@
       <c r="B19" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1413,7 +1458,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -1421,7 +1466,7 @@
       <c r="B20" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1438,7 +1483,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -1446,7 +1491,7 @@
       <c r="B21" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1463,7 +1508,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -1471,7 +1516,7 @@
       <c r="B22" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1488,7 +1533,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -1496,7 +1541,7 @@
       <c r="B23" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1513,7 +1558,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -1521,7 +1566,7 @@
       <c r="B24" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1538,7 +1583,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -1546,7 +1591,7 @@
       <c r="B25" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1563,7 +1608,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -1571,7 +1616,7 @@
       <c r="B26" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1588,7 +1633,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -1596,7 +1641,7 @@
       <c r="B27" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1613,7 +1658,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -1621,7 +1666,7 @@
       <c r="B28" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1638,7 +1683,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -1646,7 +1691,7 @@
       <c r="B29" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1663,7 +1708,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -1671,7 +1716,7 @@
       <c r="B30" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1688,7 +1733,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -1696,7 +1741,7 @@
       <c r="B31" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1713,7 +1758,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -1721,7 +1766,7 @@
       <c r="B32" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1738,7 +1783,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -1746,7 +1791,7 @@
       <c r="B33" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1763,7 +1808,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -1771,7 +1816,7 @@
       <c r="B34" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1788,7 +1833,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -1796,7 +1841,7 @@
       <c r="B35" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1813,7 +1858,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -1821,7 +1866,7 @@
       <c r="B36" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1838,7 +1883,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -1846,7 +1891,7 @@
       <c r="B37" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1863,7 +1908,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -1871,7 +1916,7 @@
       <c r="B38" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1888,7 +1933,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -1896,7 +1941,7 @@
       <c r="B39" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1913,7 +1958,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -1921,7 +1966,7 @@
       <c r="B40" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1938,7 +1983,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -1946,7 +1991,7 @@
       <c r="B41" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1963,7 +2008,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -1971,7 +2016,7 @@
       <c r="B42" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1988,7 +2033,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -1996,7 +2041,7 @@
       <c r="B43" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2013,7 +2058,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -2021,7 +2066,7 @@
       <c r="B44" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2038,7 +2083,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -2046,7 +2091,7 @@
       <c r="B45" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C45" s="22" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2063,7 +2108,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -2071,7 +2116,7 @@
       <c r="B46" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2088,7 +2133,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -2096,7 +2141,7 @@
       <c r="B47" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C47" s="22" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2113,7 +2158,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -2121,7 +2166,7 @@
       <c r="B48" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C48" s="22" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2138,7 +2183,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -2146,7 +2191,7 @@
       <c r="B49" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C49" s="22" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2163,7 +2208,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="37" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -2171,7 +2216,7 @@
       <c r="B50" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C50" s="22" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2188,7 +2233,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -2196,7 +2241,7 @@
       <c r="B51" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2213,7 +2258,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -2221,7 +2266,7 @@
       <c r="B52" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C52" s="22" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2238,7 +2283,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -2246,7 +2291,7 @@
       <c r="B53" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C53" s="22" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2263,7 +2308,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -2271,7 +2316,7 @@
       <c r="B54" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C54" s="22" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2288,7 +2333,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -2296,7 +2341,7 @@
       <c r="B55" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C55" s="22" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2313,7 +2358,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="inlineStr">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -2321,7 +2366,7 @@
       <c r="B56" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C56" s="22" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2338,7 +2383,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="inlineStr">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -2346,7 +2391,7 @@
       <c r="B57" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C57" s="22" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2363,7 +2408,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="inlineStr">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -2371,7 +2416,7 @@
       <c r="B58" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C58" s="22" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2388,7 +2433,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -2396,7 +2441,7 @@
       <c r="B59" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C59" s="22" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2413,7 +2458,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="inlineStr">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -2421,7 +2466,7 @@
       <c r="B60" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C60" s="22" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2438,7 +2483,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -2446,7 +2491,7 @@
       <c r="B61" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C61" s="22" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2463,7 +2508,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="inlineStr">
+      <c r="A62" s="37" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -2471,7 +2516,7 @@
       <c r="B62" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C62" s="22" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2488,7 +2533,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -2496,7 +2541,7 @@
       <c r="B63" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C63" s="22" t="inlineStr">
+      <c r="C63" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2513,7 +2558,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="37" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -2521,7 +2566,7 @@
       <c r="B64" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C64" s="22" t="inlineStr">
+      <c r="C64" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2538,7 +2583,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -2546,7 +2591,7 @@
       <c r="B65" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C65" s="22" t="inlineStr">
+      <c r="C65" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2563,7 +2608,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="inlineStr">
+      <c r="A66" s="37" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -2571,7 +2616,7 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="22" t="inlineStr">
+      <c r="C66" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2588,7 +2633,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -2596,7 +2641,7 @@
       <c r="B67" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="C67" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2613,7 +2658,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="inlineStr">
+      <c r="A68" s="37" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -2621,7 +2666,7 @@
       <c r="B68" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C68" s="22" t="inlineStr">
+      <c r="C68" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2638,7 +2683,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="inlineStr">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -2646,7 +2691,7 @@
       <c r="B69" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C69" s="22" t="inlineStr">
+      <c r="C69" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2663,7 +2708,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="inlineStr">
+      <c r="A70" s="37" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -2671,7 +2716,7 @@
       <c r="B70" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C70" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2688,7 +2733,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="inlineStr">
+      <c r="A71" s="37" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -2696,7 +2741,7 @@
       <c r="B71" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C71" s="22" t="inlineStr">
+      <c r="C71" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2713,7 +2758,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="22" t="inlineStr">
+      <c r="A72" s="37" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -2721,7 +2766,7 @@
       <c r="B72" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C72" s="22" t="inlineStr">
+      <c r="C72" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2738,7 +2783,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="22" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -2746,7 +2791,7 @@
       <c r="B73" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C73" s="22" t="inlineStr">
+      <c r="C73" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2763,7 +2808,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="inlineStr">
+      <c r="A74" s="37" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -2771,7 +2816,7 @@
       <c r="B74" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C74" s="22" t="inlineStr">
+      <c r="C74" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2788,7 +2833,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="22" t="inlineStr">
+      <c r="A75" s="37" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -2796,7 +2841,7 @@
       <c r="B75" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C75" s="22" t="inlineStr">
+      <c r="C75" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2813,7 +2858,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="A76" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -2821,7 +2866,7 @@
       <c r="B76" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C76" s="22" t="inlineStr">
+      <c r="C76" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2838,7 +2883,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="inlineStr">
+      <c r="A77" s="37" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -2846,7 +2891,7 @@
       <c r="B77" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C77" s="22" t="inlineStr">
+      <c r="C77" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2863,7 +2908,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="22" t="inlineStr">
+      <c r="A78" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -2871,7 +2916,7 @@
       <c r="B78" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C78" s="22" t="inlineStr">
+      <c r="C78" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2888,7 +2933,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="inlineStr">
+      <c r="A79" s="37" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -2896,7 +2941,7 @@
       <c r="B79" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C79" s="22" t="inlineStr">
+      <c r="C79" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2913,7 +2958,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="inlineStr">
+      <c r="A80" s="37" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -2921,7 +2966,7 @@
       <c r="B80" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C80" s="22" t="inlineStr">
+      <c r="C80" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2938,7 +2983,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="22" t="inlineStr">
+      <c r="A81" s="37" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -2946,7 +2991,7 @@
       <c r="B81" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C81" s="22" t="inlineStr">
+      <c r="C81" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2963,7 +3008,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="22" t="inlineStr">
+      <c r="A82" s="37" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -2971,7 +3016,7 @@
       <c r="B82" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C82" s="22" t="inlineStr">
+      <c r="C82" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2988,7 +3033,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="inlineStr">
+      <c r="A83" s="37" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -2996,7 +3041,7 @@
       <c r="B83" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C83" s="22" t="inlineStr">
+      <c r="C83" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3013,7 +3058,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="22" t="inlineStr">
+      <c r="A84" s="37" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -3021,7 +3066,7 @@
       <c r="B84" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C84" s="22" t="inlineStr">
+      <c r="C84" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3038,7 +3083,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="inlineStr">
+      <c r="A85" s="37" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -3046,7 +3091,7 @@
       <c r="B85" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C85" s="22" t="inlineStr">
+      <c r="C85" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3063,7 +3108,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="22" t="inlineStr">
+      <c r="A86" s="37" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -3071,7 +3116,7 @@
       <c r="B86" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C86" s="22" t="inlineStr">
+      <c r="C86" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3088,7 +3133,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="22" t="inlineStr">
+      <c r="A87" s="37" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -3096,7 +3141,7 @@
       <c r="B87" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C87" s="22" t="inlineStr">
+      <c r="C87" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3113,7 +3158,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="inlineStr">
+      <c r="A88" s="37" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -3121,7 +3166,7 @@
       <c r="B88" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C88" s="22" t="inlineStr">
+      <c r="C88" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3138,7 +3183,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="22" t="inlineStr">
+      <c r="A89" s="37" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -3146,7 +3191,7 @@
       <c r="B89" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C89" s="22" t="inlineStr">
+      <c r="C89" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3163,7 +3208,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="inlineStr">
+      <c r="A90" s="37" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -3171,7 +3216,7 @@
       <c r="B90" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C90" s="22" t="inlineStr">
+      <c r="C90" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3188,7 +3233,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="22" t="inlineStr">
+      <c r="A91" s="37" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -3196,7 +3241,7 @@
       <c r="B91" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C91" s="22" t="inlineStr">
+      <c r="C91" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3213,7 +3258,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="22" t="inlineStr">
+      <c r="A92" s="37" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -3221,7 +3266,7 @@
       <c r="B92" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C92" s="22" t="inlineStr">
+      <c r="C92" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3238,7 +3283,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="inlineStr">
+      <c r="A93" s="37" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -3246,7 +3291,7 @@
       <c r="B93" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C93" s="22" t="inlineStr">
+      <c r="C93" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3263,7 +3308,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="22" t="inlineStr">
+      <c r="A94" s="37" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -3271,7 +3316,7 @@
       <c r="B94" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C94" s="22" t="inlineStr">
+      <c r="C94" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3288,7 +3333,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="22" t="inlineStr">
+      <c r="A95" s="37" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -3296,7 +3341,7 @@
       <c r="B95" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C95" s="22" t="inlineStr">
+      <c r="C95" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3313,7 +3358,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="22" t="inlineStr">
+      <c r="A96" s="37" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -3321,7 +3366,7 @@
       <c r="B96" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C96" s="22" t="inlineStr">
+      <c r="C96" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3338,7 +3383,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="22" t="inlineStr">
+      <c r="A97" s="37" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -3346,7 +3391,7 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="22" t="inlineStr">
+      <c r="C97" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3363,7 +3408,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="inlineStr">
+      <c r="A98" s="37" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -3371,7 +3416,7 @@
       <c r="B98" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C98" s="22" t="inlineStr">
+      <c r="C98" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3388,7 +3433,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="22" t="inlineStr">
+      <c r="A99" s="37" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -3396,7 +3441,7 @@
       <c r="B99" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C99" s="22" t="inlineStr">
+      <c r="C99" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3413,7 +3458,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="22" t="inlineStr">
+      <c r="A100" s="37" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -3421,7 +3466,7 @@
       <c r="B100" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C100" s="22" t="inlineStr">
+      <c r="C100" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3438,7 +3483,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="22" t="inlineStr">
+      <c r="A101" s="37" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -3446,7 +3491,7 @@
       <c r="B101" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C101" s="22" t="inlineStr">
+      <c r="C101" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3463,7 +3508,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="22" t="inlineStr">
+      <c r="A102" s="37" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -3471,7 +3516,7 @@
       <c r="B102" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C102" s="22" t="inlineStr">
+      <c r="C102" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3488,7 +3533,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="22" t="inlineStr">
+      <c r="A103" s="37" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -3496,7 +3541,7 @@
       <c r="B103" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C103" s="22" t="inlineStr">
+      <c r="C103" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3513,7 +3558,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="22" t="inlineStr">
+      <c r="A104" s="37" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -3521,7 +3566,7 @@
       <c r="B104" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C104" s="22" t="inlineStr">
+      <c r="C104" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3538,7 +3583,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="22" t="inlineStr">
+      <c r="A105" s="37" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -3546,7 +3591,7 @@
       <c r="B105" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C105" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3563,7 +3608,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="22" t="inlineStr">
+      <c r="A106" s="37" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -3571,7 +3616,7 @@
       <c r="B106" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C106" s="22" t="inlineStr">
+      <c r="C106" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3588,7 +3633,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="22" t="inlineStr">
+      <c r="A107" s="37" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -3596,7 +3641,7 @@
       <c r="B107" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C107" s="22" t="inlineStr">
+      <c r="C107" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3613,7 +3658,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="22" t="inlineStr">
+      <c r="A108" s="37" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -3621,7 +3666,7 @@
       <c r="B108" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C108" s="22" t="inlineStr">
+      <c r="C108" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3638,7 +3683,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="22" t="inlineStr">
+      <c r="A109" s="37" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -3646,7 +3691,7 @@
       <c r="B109" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C109" s="22" t="inlineStr">
+      <c r="C109" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3663,7 +3708,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="22" t="inlineStr">
+      <c r="A110" s="37" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -3671,7 +3716,7 @@
       <c r="B110" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C110" s="22" t="inlineStr">
+      <c r="C110" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3688,7 +3733,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="22" t="inlineStr">
+      <c r="A111" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -3696,7 +3741,7 @@
       <c r="B111" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C111" s="22" t="inlineStr">
+      <c r="C111" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3713,7 +3758,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="22" t="inlineStr">
+      <c r="A112" s="37" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -3721,7 +3766,7 @@
       <c r="B112" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C112" s="22" t="inlineStr">
+      <c r="C112" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3738,7 +3783,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="22" t="inlineStr">
+      <c r="A113" s="37" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -3746,7 +3791,7 @@
       <c r="B113" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C113" s="22" t="inlineStr">
+      <c r="C113" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3763,7 +3808,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="22" t="inlineStr">
+      <c r="A114" s="37" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -3771,7 +3816,7 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="22" t="inlineStr">
+      <c r="C114" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3788,7 +3833,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="22" t="inlineStr">
+      <c r="A115" s="37" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -3796,7 +3841,7 @@
       <c r="B115" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C115" s="22" t="inlineStr">
+      <c r="C115" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3813,7 +3858,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="22" t="inlineStr">
+      <c r="A116" s="37" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -3821,7 +3866,7 @@
       <c r="B116" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C116" s="22" t="inlineStr">
+      <c r="C116" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3838,7 +3883,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="22" t="inlineStr">
+      <c r="A117" s="37" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -3846,7 +3891,7 @@
       <c r="B117" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C117" s="22" t="inlineStr">
+      <c r="C117" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3863,7 +3908,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="22" t="inlineStr">
+      <c r="A118" s="37" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -3871,7 +3916,7 @@
       <c r="B118" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C118" s="22" t="inlineStr">
+      <c r="C118" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3888,7 +3933,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="22" t="inlineStr">
+      <c r="A119" s="37" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -3896,7 +3941,7 @@
       <c r="B119" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C119" s="22" t="inlineStr">
+      <c r="C119" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3913,7 +3958,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="22" t="inlineStr">
+      <c r="A120" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -3921,7 +3966,7 @@
       <c r="B120" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C120" s="22" t="inlineStr">
+      <c r="C120" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3938,7 +3983,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="22" t="inlineStr">
+      <c r="A121" s="37" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -3946,7 +3991,7 @@
       <c r="B121" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C121" s="22" t="inlineStr">
+      <c r="C121" s="37" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3963,7 +4008,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="22" t="inlineStr">
+      <c r="A122" s="37" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -3971,7 +4016,7 @@
       <c r="B122" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C122" s="22" t="inlineStr">
+      <c r="C122" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3988,7 +4033,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="22" t="inlineStr">
+      <c r="A123" s="37" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -3996,7 +4041,7 @@
       <c r="B123" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C123" s="22" t="inlineStr">
+      <c r="C123" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4013,7 +4058,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="22" t="inlineStr">
+      <c r="A124" s="37" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -4021,7 +4066,7 @@
       <c r="B124" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C124" s="22" t="inlineStr">
+      <c r="C124" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4038,7 +4083,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="22" t="inlineStr">
+      <c r="A125" s="37" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -4046,7 +4091,7 @@
       <c r="B125" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C125" s="22" t="inlineStr">
+      <c r="C125" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4063,7 +4108,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="22" t="inlineStr">
+      <c r="A126" s="37" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -4071,7 +4116,7 @@
       <c r="B126" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C126" s="22" t="inlineStr">
+      <c r="C126" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4088,7 +4133,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="23" t="inlineStr">
+      <c r="A127" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4096,7 +4141,7 @@
       <c r="B127" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C127" s="23" t="inlineStr"/>
+      <c r="C127" s="38" t="inlineStr"/>
       <c r="D127" s="16" t="inlineStr"/>
       <c r="E127" s="16" t="inlineStr"/>
     </row>
@@ -4157,7 +4202,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -4166,14 +4211,14 @@
         <v>108126415.72</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>97707434</v>
+        <v>97301853.98999999</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-10418981.72</v>
+        <v>-10824561.73</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Налоги с ФОТ</t>
         </is>
@@ -4189,7 +4234,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -4205,7 +4250,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Расходы по кассе</t>
         </is>
@@ -4221,7 +4266,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Услуги банка (общие)</t>
         </is>
@@ -4237,7 +4282,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Эквайринг (персонально)</t>
         </is>
@@ -4253,7 +4298,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -4269,7 +4314,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>% по кредиту</t>
         </is>
@@ -4285,7 +4330,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Поставщики (счёт 60)</t>
         </is>
@@ -4301,7 +4346,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
@@ -4317,7 +4362,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>ДОХОД (выручка − расходы)</t>
         </is>
@@ -4326,10 +4371,10 @@
         <v>35573284.74</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>8733266.539999999</v>
+        <v>8327686.53</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>-26840018.2</v>
+        <v>-27245598.21</v>
       </c>
     </row>
     <row r="17">
@@ -4362,7 +4407,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -4378,7 +4423,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр.1</t>
         </is>
@@ -4394,7 +4439,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
@@ -4410,7 +4455,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Досудебный спор</t>
         </is>
@@ -4426,7 +4471,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Прочие поставщики</t>
         </is>
@@ -4442,7 +4487,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4468,7 +4513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4510,22 +4555,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>01–10.08, старая управленка</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>29748144</v>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>«Отчет по врачам (УК)», колонка «Фактическая оплата»</t>
+        <v>31613514</v>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>реестр «Оплаты от пациента» без двух документов, помеченных на удаление; сходится с «Ежедневным отчётом по кассам»</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>11–31.08, новая управленка</t>
         </is>
@@ -4533,191 +4578,260 @@
       <c r="B6" s="6" t="n">
         <v>66058340</v>
       </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными»</t>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными», уже за вычетом возвратов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>Возвраты пациентам, 01–10.08</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>-370000</v>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>колонка «Возврат денег» «Ежедневного отчёта по кассам»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>95806484</v>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="B8" s="9" t="n">
+        <v>97301854</v>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>деньги, поступившие за месяц</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="22" t="inlineStr"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="22" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>из них привязано к врачу напрямую</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>46412341</v>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="37" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>01–10.08: платежи с указанным специалистом</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>30904014</v>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>колонка «Специалист» реестра платежей</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>01–10.08: без специалиста</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>709500</v>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>разнесены по врачам того же пациента, остаток — пропорционально</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>11–31.08: привязано к врачу напрямую</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>46401840</v>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>документы «Оказание услуг» — врач указан в документе</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>авансы, разнесённые через пациента</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>14598500</v>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>11–31.08: авансы, разнесённые через пациента</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>14588000</v>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>оплата картой и кассовые ордера</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>авансы без совпадения по пациенту</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>5078499</v>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>11–31.08: авансы без совпадения по пациенту</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>5068500</v>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>разнесены пропорционально; пациентов нет в реестре услуг августа</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Группа</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>01–10.08</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>11–31.08</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Доля</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n">
+      <c r="B17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="6" t="n">
         <v>4180781.46</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="D17" s="6" t="n">
+        <v>4180781.46</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>0.04</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n">
+      <c r="B18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6" t="n">
         <v>13054662.21</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="D18" s="6" t="n">
+        <v>13054662.21</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>0.13</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n">
-        <v>77250611.63</v>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="B19" s="6" t="n">
+        <v>30239933.64</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>46606046.11</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>76845979.75</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>0.79</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n">
+      <c r="B20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="n">
         <v>261238.64</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="D20" s="6" t="n">
+        <v>261238.64</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n">
-        <v>2960140.06</v>
-      </c>
-      <c r="E18" s="10" t="n">
+      <c r="B21" s="6" t="n">
+        <v>1003580.36</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1955611.58</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2959191.93</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n">
-        <v>97707434</v>
-      </c>
-      <c r="E19" s="11" t="n">
+      <c r="B22" s="9" t="n">
+        <v>31243514</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>66058340</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>97301853.98999999</v>
+      </c>
+      <c r="E22" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4783,12 +4897,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Выручка за месяц</t>
         </is>
@@ -4813,12 +4927,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Доход учредителей за месяц</t>
         </is>
@@ -4843,12 +4957,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
@@ -4873,12 +4987,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Рост выручки с начала года</t>
         </is>
@@ -4901,12 +5015,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Выручка месяца, год к году</t>
         </is>
@@ -4929,12 +5043,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Выручка с начала года</t>
         </is>
@@ -4959,12 +5073,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Средняя выручка в день</t>
         </is>
@@ -4989,12 +5103,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Оплаты поставщикам (сч. 60)</t>
         </is>
@@ -5019,12 +5133,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>ФОТ с налогами по банку</t>
         </is>
@@ -5049,12 +5163,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
@@ -5079,12 +5193,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Касса (наличные)</t>
         </is>
@@ -5109,12 +5223,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Эквайринг (карты)</t>
         </is>
@@ -5139,12 +5253,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Оплаты физлиц на р/с</t>
         </is>
@@ -5169,12 +5283,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
@@ -5199,12 +5313,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Комиссия эквайринга</t>
         </is>
@@ -5229,12 +5343,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Медицинские расходы + ИП</t>
         </is>
@@ -5259,12 +5373,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -5289,12 +5403,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>в т.ч. гонорары ИП хирургов</t>
         </is>
@@ -5319,12 +5433,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>в т.ч. ремонт нового корпуса</t>
         </is>
@@ -5349,12 +5463,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Экономика</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Доход месяца (итог водопада)</t>
         </is>
@@ -5379,12 +5493,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Остаток на начало месяца</t>
         </is>
@@ -5409,12 +5523,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Поступления за месяц</t>
         </is>
@@ -5439,12 +5553,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>Списания за месяц</t>
         </is>
@@ -5469,12 +5583,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>Остаток на конец месяца</t>
         </is>
@@ -5499,12 +5613,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="34" t="inlineStr">
         <is>
           <t>Маланичев: личная выручка</t>
         </is>
@@ -5529,12 +5643,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>Маланичев: ½ выручки других хирургов</t>
         </is>
@@ -5559,12 +5673,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>Маланичев: ½ косметологии и прочего</t>
         </is>
@@ -5589,12 +5703,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>Маланичев: доля расходов</t>
         </is>
@@ -5619,12 +5733,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>Маланичев: доход за месяц</t>
         </is>
@@ -5649,12 +5763,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>Маланичев: остаток с прошлого месяца</t>
         </is>
@@ -5679,12 +5793,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>Маланичев: удержано в резерв (аренда)</t>
         </is>
@@ -5709,12 +5823,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>Маланичев: к выплате на конец месяца</t>
         </is>
@@ -5739,12 +5853,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>Погосян: личная выручка</t>
         </is>
@@ -5769,12 +5883,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>Погосян: ½ выручки других хирургов</t>
         </is>
@@ -5799,12 +5913,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="34" t="inlineStr">
         <is>
           <t>Погосян: ½ косметологии и прочего</t>
         </is>
@@ -5829,12 +5943,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Погосян: доля расходов</t>
         </is>
@@ -5859,12 +5973,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>Погосян: доход за месяц</t>
         </is>
@@ -5889,12 +6003,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>Погосян: остаток с прошлого месяца</t>
         </is>
@@ -5919,12 +6033,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="34" t="inlineStr">
         <is>
           <t>Погосян: удержано в резерв (аренда)</t>
         </is>
@@ -5949,12 +6063,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>Погосян: к выплате на конец месяца</t>
         </is>
@@ -5979,12 +6093,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="34" t="inlineStr">
         <is>
           <t>Долг по кредитной линии</t>
         </is>
@@ -6009,12 +6123,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>Остаток наличных в кассе</t>
         </is>
@@ -6037,12 +6151,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="34" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -6067,12 +6181,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="34" t="inlineStr">
         <is>
           <t>Зарезервировано на аренду (всего)</t>
         </is>
@@ -6213,7 +6327,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
@@ -6255,7 +6369,7 @@
       <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -6297,7 +6411,7 @@
       <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
@@ -6339,7 +6453,7 @@
       <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
@@ -6381,7 +6495,7 @@
       <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -6423,7 +6537,7 @@
       <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
@@ -6465,7 +6579,7 @@
       <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -6507,7 +6621,7 @@
       <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
@@ -6549,7 +6663,7 @@
       <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
@@ -6591,7 +6705,7 @@
       <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
@@ -6633,7 +6747,7 @@
       <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
@@ -6675,7 +6789,7 @@
       <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -6717,7 +6831,7 @@
       <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
@@ -6759,7 +6873,7 @@
       <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
@@ -6801,7 +6915,7 @@
       <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -6843,7 +6957,7 @@
       <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
@@ -6885,7 +6999,7 @@
       <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
@@ -6927,7 +7041,7 @@
       <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -6969,7 +7083,7 @@
       <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7011,7 +7125,7 @@
       <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -7053,7 +7167,7 @@
       <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
@@ -7095,7 +7209,7 @@
       <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
@@ -7137,7 +7251,7 @@
       <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
@@ -7179,7 +7293,7 @@
       <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -7221,7 +7335,7 @@
       <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -7263,7 +7377,7 @@
       <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
@@ -7305,7 +7419,7 @@
       <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -7347,7 +7461,7 @@
       <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -7389,7 +7503,7 @@
       <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
@@ -7431,7 +7545,7 @@
       <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
@@ -7473,7 +7587,7 @@
       <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -7515,7 +7629,7 @@
       <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7641,7 +7755,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -7667,7 +7781,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -7693,7 +7807,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
@@ -7719,7 +7833,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -7745,7 +7859,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -7771,7 +7885,7 @@
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7828,7 +7942,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
@@ -7844,7 +7958,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
@@ -7860,7 +7974,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
@@ -7876,7 +7990,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
@@ -7892,7 +8006,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
@@ -7908,7 +8022,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
@@ -7924,7 +8038,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
@@ -7940,7 +8054,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
@@ -7952,7 +8066,7 @@
       <c r="D21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
@@ -7964,7 +8078,7 @@
       <c r="D22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
@@ -7976,7 +8090,7 @@
       <c r="D23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
@@ -7988,7 +8102,7 @@
       <c r="D24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
@@ -8049,12 +8163,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -8067,12 +8181,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
@@ -8085,12 +8199,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -8103,12 +8217,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
@@ -8121,12 +8235,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -8139,12 +8253,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
@@ -8157,12 +8271,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
@@ -8175,12 +8289,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
@@ -8193,12 +8307,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
@@ -8211,12 +8325,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
@@ -8229,12 +8343,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
@@ -8247,12 +8361,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
@@ -8265,12 +8379,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
@@ -8283,12 +8397,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
@@ -8301,12 +8415,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
@@ -8319,12 +8433,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
@@ -8337,12 +8451,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -8355,12 +8469,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
@@ -8373,12 +8487,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
@@ -8391,12 +8505,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
@@ -8409,12 +8523,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -8427,12 +8541,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
@@ -8445,12 +8559,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
@@ -8463,12 +8577,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -8481,12 +8595,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="34" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
@@ -8499,12 +8613,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
@@ -8517,12 +8631,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
@@ -8535,12 +8649,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
@@ -8553,12 +8667,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
@@ -8571,12 +8685,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -8589,12 +8703,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
@@ -8607,12 +8721,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
@@ -8625,12 +8739,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
@@ -8643,12 +8757,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
@@ -8661,12 +8775,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="34" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -8679,12 +8793,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
@@ -8697,12 +8811,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
@@ -8715,12 +8829,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
@@ -8733,12 +8847,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="34" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
@@ -8751,12 +8865,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -8769,12 +8883,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="34" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
@@ -8787,12 +8901,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
@@ -8805,12 +8919,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="34" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
@@ -8823,12 +8937,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="34" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
@@ -8841,12 +8955,12 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="34" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
@@ -8859,12 +8973,12 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="34" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
@@ -8877,12 +8991,12 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="34" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
@@ -8895,12 +9009,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="34" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
@@ -8913,12 +9027,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="34" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
@@ -8931,12 +9045,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="34" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
@@ -8949,12 +9063,12 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="34" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
@@ -8967,12 +9081,12 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="34" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
@@ -8985,12 +9099,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="34" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
@@ -9003,12 +9117,12 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="34" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
@@ -9021,12 +9135,12 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="34" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
@@ -9039,12 +9153,12 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="34" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
@@ -9057,12 +9171,12 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="34" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
@@ -9075,12 +9189,12 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
@@ -9093,12 +9207,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="34" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
@@ -9111,12 +9225,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
@@ -9129,12 +9243,12 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="34" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
@@ -9147,12 +9261,12 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="34" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
@@ -9165,12 +9279,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="34" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="34" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -9183,12 +9297,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="35" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="35" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -9201,12 +9315,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr"/>
+      <c r="B68" s="36" t="inlineStr"/>
       <c r="C68" s="14" t="n">
         <v>69794048.05</v>
       </c>
@@ -9256,7 +9370,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -9264,14 +9378,14 @@
       <c r="B4" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Ремонт Самокатная 1 стр12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -9279,14 +9393,14 @@
       <c r="B5" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -9294,14 +9408,14 @@
       <c r="B6" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -9309,14 +9423,14 @@
       <c r="B7" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -9324,14 +9438,14 @@
       <c r="B8" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -9339,14 +9453,14 @@
       <c r="B9" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -9354,14 +9468,14 @@
       <c r="B10" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -9369,14 +9483,14 @@
       <c r="B11" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -9384,14 +9498,14 @@
       <c r="B12" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -9399,14 +9513,14 @@
       <c r="B13" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -9414,14 +9528,14 @@
       <c r="B14" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -9429,14 +9543,14 @@
       <c r="B15" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -9444,14 +9558,14 @@
       <c r="B16" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -9459,14 +9573,14 @@
       <c r="B17" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -9474,14 +9588,14 @@
       <c r="B18" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -9489,14 +9603,14 @@
       <c r="B19" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -9504,14 +9618,14 @@
       <c r="B20" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -9519,14 +9633,14 @@
       <c r="B21" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -9534,14 +9648,14 @@
       <c r="B22" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -9549,14 +9663,14 @@
       <c r="B23" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -9564,14 +9678,14 @@
       <c r="B24" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -9579,14 +9693,14 @@
       <c r="B25" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -9594,14 +9708,14 @@
       <c r="B26" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -9609,14 +9723,14 @@
       <c r="B27" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -9624,14 +9738,14 @@
       <c r="B28" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -9639,14 +9753,14 @@
       <c r="B29" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -9654,14 +9768,14 @@
       <c r="B30" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="34" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -9669,14 +9783,14 @@
       <c r="B31" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -9684,14 +9798,14 @@
       <c r="B32" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="34" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -9699,14 +9813,14 @@
       <c r="B33" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -9714,14 +9828,14 @@
       <c r="B34" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -9729,14 +9843,14 @@
       <c r="B35" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -9744,14 +9858,14 @@
       <c r="B36" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -9759,14 +9873,14 @@
       <c r="B37" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -9774,14 +9888,14 @@
       <c r="B38" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -9789,14 +9903,14 @@
       <c r="B39" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -9804,14 +9918,14 @@
       <c r="B40" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -9819,14 +9933,14 @@
       <c r="B41" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -9834,14 +9948,14 @@
       <c r="B42" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="34" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -9849,14 +9963,14 @@
       <c r="B43" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -9864,14 +9978,14 @@
       <c r="B44" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="34" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -9879,14 +9993,14 @@
       <c r="B45" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -9894,14 +10008,14 @@
       <c r="B46" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -9909,14 +10023,14 @@
       <c r="B47" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="34" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -9924,14 +10038,14 @@
       <c r="B48" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -9939,14 +10053,14 @@
       <c r="B49" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="34" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -9954,14 +10068,14 @@
       <c r="B50" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -9969,14 +10083,14 @@
       <c r="B51" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -9984,14 +10098,14 @@
       <c r="B52" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="34" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -9999,14 +10113,14 @@
       <c r="B53" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="34" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -10014,14 +10128,14 @@
       <c r="B54" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="34" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -10029,14 +10143,14 @@
       <c r="B55" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="34" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -10044,14 +10158,14 @@
       <c r="B56" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="34" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -10059,14 +10173,14 @@
       <c r="B57" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="34" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -10074,14 +10188,14 @@
       <c r="B58" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -10089,14 +10203,14 @@
       <c r="B59" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="34" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="34" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -10104,14 +10218,14 @@
       <c r="B60" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="34" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="34" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -10119,14 +10233,14 @@
       <c r="B61" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="34" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="34" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -10134,14 +10248,14 @@
       <c r="B62" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="34" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="34" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -10149,14 +10263,14 @@
       <c r="B63" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="34" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -10164,14 +10278,14 @@
       <c r="B64" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="34" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -10179,14 +10293,14 @@
       <c r="B65" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="34" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -10194,14 +10308,14 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="34" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -10209,14 +10323,14 @@
       <c r="B67" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="34" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="34" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -10224,14 +10338,14 @@
       <c r="B68" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="34" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -10239,14 +10353,14 @@
       <c r="B69" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="34" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -10254,14 +10368,14 @@
       <c r="B70" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="34" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -10269,14 +10383,14 @@
       <c r="B71" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="34" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="34" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -10284,14 +10398,14 @@
       <c r="B72" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="34" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -10299,14 +10413,14 @@
       <c r="B73" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="34" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="34" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -10314,14 +10428,14 @@
       <c r="B74" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="34" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -10329,14 +10443,14 @@
       <c r="B75" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="34" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="34" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -10344,14 +10458,14 @@
       <c r="B76" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="34" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -10359,14 +10473,14 @@
       <c r="B77" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="34" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="34" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -10374,14 +10488,14 @@
       <c r="B78" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="34" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="34" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -10389,14 +10503,14 @@
       <c r="B79" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="34" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -10404,14 +10518,14 @@
       <c r="B80" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="34" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -10419,14 +10533,14 @@
       <c r="B81" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" s="34" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="34" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -10434,14 +10548,14 @@
       <c r="B82" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="34" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -10449,14 +10563,14 @@
       <c r="B83" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="34" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -10464,14 +10578,14 @@
       <c r="B84" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="34" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="34" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -10479,14 +10593,14 @@
       <c r="B85" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="34" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -10494,14 +10608,14 @@
       <c r="B86" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" s="34" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="34" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -10509,14 +10623,14 @@
       <c r="B87" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="34" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="34" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -10524,14 +10638,14 @@
       <c r="B88" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="34" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -10539,14 +10653,14 @@
       <c r="B89" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" s="34" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="34" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -10554,14 +10668,14 @@
       <c r="B90" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="34" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -10569,14 +10683,14 @@
       <c r="B91" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="34" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="34" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -10584,14 +10698,14 @@
       <c r="B92" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" s="34" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="34" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -10599,14 +10713,14 @@
       <c r="B93" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="34" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="34" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -10614,14 +10728,14 @@
       <c r="B94" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="34" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="34" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -10629,14 +10743,14 @@
       <c r="B95" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="34" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="34" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -10644,14 +10758,14 @@
       <c r="B96" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="34" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="34" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -10659,14 +10773,14 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="34" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="34" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -10674,14 +10788,14 @@
       <c r="B98" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="34" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="34" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -10689,14 +10803,14 @@
       <c r="B99" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="34" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -10704,14 +10818,14 @@
       <c r="B100" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C100" s="34" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="34" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -10719,14 +10833,14 @@
       <c r="B101" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" s="34" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="34" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -10734,14 +10848,14 @@
       <c r="B102" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="34" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="34" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -10749,14 +10863,14 @@
       <c r="B103" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="34" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="34" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -10764,14 +10878,14 @@
       <c r="B104" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" s="34" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="34" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -10779,14 +10893,14 @@
       <c r="B105" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C105" s="34" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="34" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -10794,14 +10908,14 @@
       <c r="B106" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="34" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="34" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -10809,14 +10923,14 @@
       <c r="B107" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="34" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -10824,14 +10938,14 @@
       <c r="B108" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" s="34" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="34" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -10839,14 +10953,14 @@
       <c r="B109" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="34" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -10854,14 +10968,14 @@
       <c r="B110" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="34" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="34" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -10869,14 +10983,14 @@
       <c r="B111" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="34" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="34" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -10884,14 +10998,14 @@
       <c r="B112" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" s="34" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="34" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -10899,14 +11013,14 @@
       <c r="B113" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="34" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="34" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -10914,14 +11028,14 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="34" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="34" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -10929,14 +11043,14 @@
       <c r="B115" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="34" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="34" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -10944,14 +11058,14 @@
       <c r="B116" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="34" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="34" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -10959,14 +11073,14 @@
       <c r="B117" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="34" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="34" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -10974,14 +11088,14 @@
       <c r="B118" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="34" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -10989,14 +11103,14 @@
       <c r="B119" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="34" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -11004,14 +11118,14 @@
       <c r="B120" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="34" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="34" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -11019,14 +11133,14 @@
       <c r="B121" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" s="34" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="34" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -11034,14 +11148,14 @@
       <c r="B122" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C122" s="34" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="34" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -11049,14 +11163,14 @@
       <c r="B123" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" s="34" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="34" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -11064,14 +11178,14 @@
       <c r="B124" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" s="34" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="34" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -11079,14 +11193,14 @@
       <c r="B125" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" s="34" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="A126" s="35" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -11094,7 +11208,7 @@
       <c r="B126" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C126" s="8" t="inlineStr"/>
+      <c r="C126" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11146,7 +11260,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Начальное сальдо</t>
         </is>
@@ -11158,7 +11272,7 @@
       <c r="D4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Возврат средств с депозитов</t>
         </is>
@@ -11174,7 +11288,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Инкассация и эквайринг</t>
         </is>
@@ -11190,7 +11304,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Возвраты от поставщиков</t>
         </is>
@@ -11206,7 +11320,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Кредит банка</t>
         </is>
@@ -11222,7 +11336,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
@@ -11238,7 +11352,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -11254,7 +11368,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Размещение на депозиты</t>
         </is>
@@ -11270,7 +11384,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Переводы между счетами</t>
         </is>
@@ -11286,7 +11400,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Оплаты поставщикам и подрядчикам</t>
         </is>
@@ -11302,7 +11416,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
@@ -11318,7 +11432,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
@@ -11334,7 +11448,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Страховые взносы</t>
         </is>
@@ -11350,7 +11464,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -11366,7 +11480,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Выплата дивидендов</t>
         </is>
@@ -11382,7 +11496,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -11398,7 +11512,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -11414,7 +11528,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>Оборот за месяц</t>
         </is>
@@ -11428,7 +11542,7 @@
       <c r="D21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>Конечное сальдо</t>
         </is>
@@ -11512,12 +11626,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Личная выручка (свои операции)</t>
         </is>
@@ -11538,12 +11652,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>+ ½ выручки других хирургов</t>
         </is>
@@ -11564,12 +11678,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>+ ½ косметологии</t>
         </is>
@@ -11590,12 +11704,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>+ ½ прочих доходов</t>
         </is>
@@ -11616,12 +11730,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>+ ½ процентов по депозитам</t>
         </is>
@@ -11668,8 +11782,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr"/>
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      налоги с ФОТ (68.90 + 69)</t>
         </is>
@@ -11686,8 +11800,8 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr"/>
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      зарплата по банку</t>
         </is>
@@ -11704,8 +11818,8 @@
       <c r="F12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr"/>
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      расходы по кассе</t>
         </is>
@@ -11722,8 +11836,8 @@
       <c r="F13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr"/>
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      услуги банка (общие)</t>
         </is>
@@ -11740,8 +11854,8 @@
       <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr"/>
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      услуги банка (эквайринг, персонально)</t>
         </is>
@@ -11758,8 +11872,8 @@
       <c r="F15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr"/>
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      алименты (удержание из ЗП)</t>
         </is>
@@ -11776,8 +11890,8 @@
       <c r="F16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr"/>
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      дополнительные корректировки</t>
         </is>
@@ -11794,8 +11908,8 @@
       <c r="F17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr"/>
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">      поставщики (счёт 60) + Халва</t>
         </is>
@@ -11812,12 +11926,12 @@
       <c r="F18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
@@ -11838,12 +11952,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>+ Остаток с прошлого месяца</t>
         </is>
@@ -11864,12 +11978,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>− Выплачены дивиденды</t>
         </is>
@@ -11890,12 +12004,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
@@ -11978,10 +12092,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -11997,10 +12111,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -12016,10 +12130,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Медицинские расходы</t>
         </is>
@@ -12035,10 +12149,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>ФОТ, налоги, алименты</t>
         </is>
@@ -12054,10 +12168,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -12073,10 +12187,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Ремонт нового корпуса</t>
         </is>
@@ -12092,10 +12206,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -12111,10 +12225,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -12130,10 +12244,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Доход месяца</t>
         </is>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +175,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -629,108 +638,108 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>01 Цифры отчёта</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Каждая цифра из HTML-отчёта: значение, формула, источник. Главный лист расшифровки.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>02 Выручка по дням</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Дневная выручка по группам врачей и каналам оплаты + сверка с онлайн-кассой.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>03 Выручка структура</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Итоги по группам врачей и каналам поступления, доли в выручке, комиссия эквайринга.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>04 Расходы категории</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Счёт 60 в разрезе статей: медицинские + ИП и управленческие.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>05 Расходы контрагенты</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Счёт 60 построчно по контрагентам с назначением платежа.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>06 ДДС сч.51</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Обороты расчётного счёта: поступления и списания по корреспондирующим счетам.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>07 Учредители</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Методика 50/50 по шагам: выручка, доли расходов, доход, остаток, резерв, к выплате.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>08 Водопад</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>От выручки к доходу месяца — те же шаги, что на графике «Куда уходит выручка».</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>09 Контроль</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Контрольные равенства: сходится ли отчёт сам с собой и с данными бухгалтерии.</t>
         </is>
@@ -833,7 +842,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Сумма выручки по группам = итог выручки</t>
         </is>
@@ -855,7 +864,7 @@
       <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Касса + эквайринг + р/с физлиц − возвраты = итог выручки</t>
         </is>
@@ -877,7 +886,7 @@
       <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Сумма шагов водопада = доход месяца</t>
         </is>
@@ -903,7 +912,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Доход Маланичева + Погосяна = доход компании</t>
         </is>
@@ -925,7 +934,7 @@
       <c r="F8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Расходы 60: медицинские + управленческие = итог по счёту</t>
         </is>
@@ -947,7 +956,7 @@
       <c r="F9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Расходы 60: сумма по контрагентам = итог по счёту</t>
         </is>
@@ -973,7 +982,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>ДДС: сальдо нач. + приход − расход = сальдо кон.</t>
         </is>
@@ -995,7 +1004,7 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Выручка (отчёт) vs выручка кассовым методом (график динамики)</t>
         </is>
@@ -1083,7 +1092,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -1091,7 +1100,7 @@
       <c r="B5" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1108,7 +1117,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -1116,7 +1125,7 @@
       <c r="B6" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1133,7 +1142,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -1141,7 +1150,7 @@
       <c r="B7" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1158,7 +1167,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -1166,7 +1175,7 @@
       <c r="B8" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1183,7 +1192,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -1191,7 +1200,7 @@
       <c r="B9" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1208,7 +1217,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -1216,7 +1225,7 @@
       <c r="B10" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1233,7 +1242,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -1241,7 +1250,7 @@
       <c r="B11" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1258,7 +1267,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -1266,7 +1275,7 @@
       <c r="B12" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1283,7 +1292,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -1291,7 +1300,7 @@
       <c r="B13" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1308,7 +1317,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -1316,7 +1325,7 @@
       <c r="B14" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1333,7 +1342,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -1341,7 +1350,7 @@
       <c r="B15" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1358,7 +1367,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -1366,7 +1375,7 @@
       <c r="B16" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1383,7 +1392,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -1391,7 +1400,7 @@
       <c r="B17" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1408,7 +1417,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -1416,7 +1425,7 @@
       <c r="B18" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1433,7 +1442,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -1441,7 +1450,7 @@
       <c r="B19" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1458,7 +1467,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -1466,7 +1475,7 @@
       <c r="B20" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1483,7 +1492,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -1491,7 +1500,7 @@
       <c r="B21" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1508,7 +1517,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -1516,7 +1525,7 @@
       <c r="B22" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C22" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1533,7 +1542,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -1541,7 +1550,7 @@
       <c r="B23" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1558,7 +1567,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -1566,7 +1575,7 @@
       <c r="B24" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1583,7 +1592,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -1591,7 +1600,7 @@
       <c r="B25" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1608,7 +1617,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -1616,7 +1625,7 @@
       <c r="B26" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1633,7 +1642,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -1641,7 +1650,7 @@
       <c r="B27" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1658,7 +1667,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -1666,7 +1675,7 @@
       <c r="B28" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1683,7 +1692,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -1691,7 +1700,7 @@
       <c r="B29" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1708,7 +1717,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -1716,7 +1725,7 @@
       <c r="B30" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1733,7 +1742,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -1741,7 +1750,7 @@
       <c r="B31" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1758,7 +1767,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -1766,7 +1775,7 @@
       <c r="B32" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C32" s="37" t="inlineStr">
+      <c r="C32" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1783,7 +1792,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -1791,7 +1800,7 @@
       <c r="B33" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C33" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1808,7 +1817,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -1816,7 +1825,7 @@
       <c r="B34" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1833,7 +1842,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -1841,7 +1850,7 @@
       <c r="B35" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C35" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1858,7 +1867,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -1866,7 +1875,7 @@
       <c r="B36" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C36" s="37" t="inlineStr">
+      <c r="C36" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1883,7 +1892,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -1891,7 +1900,7 @@
       <c r="B37" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1908,7 +1917,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -1916,7 +1925,7 @@
       <c r="B38" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C38" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1933,7 +1942,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -1941,7 +1950,7 @@
       <c r="B39" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1958,7 +1967,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -1966,7 +1975,7 @@
       <c r="B40" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1983,7 +1992,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -1991,7 +2000,7 @@
       <c r="B41" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2008,7 +2017,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="37" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -2016,7 +2025,7 @@
       <c r="B42" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2033,7 +2042,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -2041,7 +2050,7 @@
       <c r="B43" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2058,7 +2067,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -2066,7 +2075,7 @@
       <c r="B44" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2083,7 +2092,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="37" t="inlineStr">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -2091,7 +2100,7 @@
       <c r="B45" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2108,7 +2117,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="37" t="inlineStr">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -2116,7 +2125,7 @@
       <c r="B46" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C46" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2133,7 +2142,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="37" t="inlineStr">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -2141,7 +2150,7 @@
       <c r="B47" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C47" s="37" t="inlineStr">
+      <c r="C47" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2158,7 +2167,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="37" t="inlineStr">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -2166,7 +2175,7 @@
       <c r="B48" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C48" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2183,7 +2192,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="37" t="inlineStr">
+      <c r="A49" s="40" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -2191,7 +2200,7 @@
       <c r="B49" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2208,7 +2217,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="37" t="inlineStr">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -2216,7 +2225,7 @@
       <c r="B50" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C50" s="37" t="inlineStr">
+      <c r="C50" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2233,7 +2242,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="37" t="inlineStr">
+      <c r="A51" s="40" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -2241,7 +2250,7 @@
       <c r="B51" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C51" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2258,7 +2267,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="37" t="inlineStr">
+      <c r="A52" s="40" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -2266,7 +2275,7 @@
       <c r="B52" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C52" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2283,7 +2292,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="37" t="inlineStr">
+      <c r="A53" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -2291,7 +2300,7 @@
       <c r="B53" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2308,7 +2317,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="37" t="inlineStr">
+      <c r="A54" s="40" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -2316,7 +2325,7 @@
       <c r="B54" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2333,7 +2342,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="37" t="inlineStr">
+      <c r="A55" s="40" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -2341,7 +2350,7 @@
       <c r="B55" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C55" s="37" t="inlineStr">
+      <c r="C55" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2358,7 +2367,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="37" t="inlineStr">
+      <c r="A56" s="40" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -2366,7 +2375,7 @@
       <c r="B56" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C56" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2383,7 +2392,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="37" t="inlineStr">
+      <c r="A57" s="40" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -2391,7 +2400,7 @@
       <c r="B57" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C57" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2408,7 +2417,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="37" t="inlineStr">
+      <c r="A58" s="40" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -2416,7 +2425,7 @@
       <c r="B58" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C58" s="37" t="inlineStr">
+      <c r="C58" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2433,7 +2442,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="37" t="inlineStr">
+      <c r="A59" s="40" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -2441,7 +2450,7 @@
       <c r="B59" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C59" s="37" t="inlineStr">
+      <c r="C59" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2458,7 +2467,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="37" t="inlineStr">
+      <c r="A60" s="40" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -2466,7 +2475,7 @@
       <c r="B60" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C60" s="37" t="inlineStr">
+      <c r="C60" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2483,7 +2492,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="37" t="inlineStr">
+      <c r="A61" s="40" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -2491,7 +2500,7 @@
       <c r="B61" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2508,7 +2517,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="37" t="inlineStr">
+      <c r="A62" s="40" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -2516,7 +2525,7 @@
       <c r="B62" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C62" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2533,7 +2542,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="37" t="inlineStr">
+      <c r="A63" s="40" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -2541,7 +2550,7 @@
       <c r="B63" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C63" s="37" t="inlineStr">
+      <c r="C63" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2558,7 +2567,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="37" t="inlineStr">
+      <c r="A64" s="40" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -2566,7 +2575,7 @@
       <c r="B64" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C64" s="37" t="inlineStr">
+      <c r="C64" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2583,7 +2592,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="37" t="inlineStr">
+      <c r="A65" s="40" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -2591,7 +2600,7 @@
       <c r="B65" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C65" s="37" t="inlineStr">
+      <c r="C65" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2608,7 +2617,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="37" t="inlineStr">
+      <c r="A66" s="40" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -2616,7 +2625,7 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="37" t="inlineStr">
+      <c r="C66" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2633,7 +2642,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="37" t="inlineStr">
+      <c r="A67" s="40" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -2641,7 +2650,7 @@
       <c r="B67" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C67" s="37" t="inlineStr">
+      <c r="C67" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2658,7 +2667,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="37" t="inlineStr">
+      <c r="A68" s="40" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -2666,7 +2675,7 @@
       <c r="B68" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C68" s="37" t="inlineStr">
+      <c r="C68" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2683,7 +2692,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="A69" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -2691,7 +2700,7 @@
       <c r="B69" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C69" s="37" t="inlineStr">
+      <c r="C69" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2708,7 +2717,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="37" t="inlineStr">
+      <c r="A70" s="40" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -2716,7 +2725,7 @@
       <c r="B70" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C70" s="37" t="inlineStr">
+      <c r="C70" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2733,7 +2742,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="37" t="inlineStr">
+      <c r="A71" s="40" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -2741,7 +2750,7 @@
       <c r="B71" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C71" s="37" t="inlineStr">
+      <c r="C71" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2758,7 +2767,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="37" t="inlineStr">
+      <c r="A72" s="40" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -2766,7 +2775,7 @@
       <c r="B72" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C72" s="37" t="inlineStr">
+      <c r="C72" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2783,7 +2792,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="37" t="inlineStr">
+      <c r="A73" s="40" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -2791,7 +2800,7 @@
       <c r="B73" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C73" s="37" t="inlineStr">
+      <c r="C73" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2808,7 +2817,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="37" t="inlineStr">
+      <c r="A74" s="40" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -2816,7 +2825,7 @@
       <c r="B74" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C74" s="37" t="inlineStr">
+      <c r="C74" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2833,7 +2842,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="37" t="inlineStr">
+      <c r="A75" s="40" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -2841,7 +2850,7 @@
       <c r="B75" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C75" s="37" t="inlineStr">
+      <c r="C75" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2858,7 +2867,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="37" t="inlineStr">
+      <c r="A76" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -2866,7 +2875,7 @@
       <c r="B76" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C76" s="37" t="inlineStr">
+      <c r="C76" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2883,7 +2892,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="37" t="inlineStr">
+      <c r="A77" s="40" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -2891,7 +2900,7 @@
       <c r="B77" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C77" s="37" t="inlineStr">
+      <c r="C77" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2908,7 +2917,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="37" t="inlineStr">
+      <c r="A78" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -2916,7 +2925,7 @@
       <c r="B78" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C78" s="37" t="inlineStr">
+      <c r="C78" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2933,7 +2942,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="37" t="inlineStr">
+      <c r="A79" s="40" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -2941,7 +2950,7 @@
       <c r="B79" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C79" s="37" t="inlineStr">
+      <c r="C79" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2958,7 +2967,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="37" t="inlineStr">
+      <c r="A80" s="40" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -2966,7 +2975,7 @@
       <c r="B80" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C80" s="37" t="inlineStr">
+      <c r="C80" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2983,7 +2992,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="37" t="inlineStr">
+      <c r="A81" s="40" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -2991,7 +3000,7 @@
       <c r="B81" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C81" s="37" t="inlineStr">
+      <c r="C81" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3008,7 +3017,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="37" t="inlineStr">
+      <c r="A82" s="40" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -3016,7 +3025,7 @@
       <c r="B82" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C82" s="37" t="inlineStr">
+      <c r="C82" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3033,7 +3042,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="37" t="inlineStr">
+      <c r="A83" s="40" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -3041,7 +3050,7 @@
       <c r="B83" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C83" s="37" t="inlineStr">
+      <c r="C83" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3058,7 +3067,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="37" t="inlineStr">
+      <c r="A84" s="40" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -3066,7 +3075,7 @@
       <c r="B84" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C84" s="37" t="inlineStr">
+      <c r="C84" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3083,7 +3092,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="37" t="inlineStr">
+      <c r="A85" s="40" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -3091,7 +3100,7 @@
       <c r="B85" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C85" s="37" t="inlineStr">
+      <c r="C85" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3108,7 +3117,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="37" t="inlineStr">
+      <c r="A86" s="40" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -3116,7 +3125,7 @@
       <c r="B86" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C86" s="37" t="inlineStr">
+      <c r="C86" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3133,7 +3142,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="37" t="inlineStr">
+      <c r="A87" s="40" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -3141,7 +3150,7 @@
       <c r="B87" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C87" s="37" t="inlineStr">
+      <c r="C87" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3158,7 +3167,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="37" t="inlineStr">
+      <c r="A88" s="40" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -3166,7 +3175,7 @@
       <c r="B88" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C88" s="37" t="inlineStr">
+      <c r="C88" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3183,7 +3192,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="37" t="inlineStr">
+      <c r="A89" s="40" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -3191,7 +3200,7 @@
       <c r="B89" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C89" s="37" t="inlineStr">
+      <c r="C89" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3208,7 +3217,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="37" t="inlineStr">
+      <c r="A90" s="40" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -3216,7 +3225,7 @@
       <c r="B90" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C90" s="37" t="inlineStr">
+      <c r="C90" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3233,7 +3242,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="37" t="inlineStr">
+      <c r="A91" s="40" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -3241,7 +3250,7 @@
       <c r="B91" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C91" s="37" t="inlineStr">
+      <c r="C91" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3258,7 +3267,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="37" t="inlineStr">
+      <c r="A92" s="40" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -3266,7 +3275,7 @@
       <c r="B92" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C92" s="37" t="inlineStr">
+      <c r="C92" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3283,7 +3292,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="37" t="inlineStr">
+      <c r="A93" s="40" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -3291,7 +3300,7 @@
       <c r="B93" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C93" s="37" t="inlineStr">
+      <c r="C93" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3308,7 +3317,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="37" t="inlineStr">
+      <c r="A94" s="40" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -3316,7 +3325,7 @@
       <c r="B94" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C94" s="37" t="inlineStr">
+      <c r="C94" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3333,7 +3342,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="37" t="inlineStr">
+      <c r="A95" s="40" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -3341,7 +3350,7 @@
       <c r="B95" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C95" s="37" t="inlineStr">
+      <c r="C95" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3358,7 +3367,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="37" t="inlineStr">
+      <c r="A96" s="40" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -3366,7 +3375,7 @@
       <c r="B96" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C96" s="37" t="inlineStr">
+      <c r="C96" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3383,7 +3392,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="37" t="inlineStr">
+      <c r="A97" s="40" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -3391,7 +3400,7 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="37" t="inlineStr">
+      <c r="C97" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3408,7 +3417,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="37" t="inlineStr">
+      <c r="A98" s="40" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -3416,7 +3425,7 @@
       <c r="B98" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C98" s="37" t="inlineStr">
+      <c r="C98" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3433,7 +3442,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="37" t="inlineStr">
+      <c r="A99" s="40" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -3441,7 +3450,7 @@
       <c r="B99" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C99" s="37" t="inlineStr">
+      <c r="C99" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3458,7 +3467,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="37" t="inlineStr">
+      <c r="A100" s="40" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -3466,7 +3475,7 @@
       <c r="B100" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C100" s="37" t="inlineStr">
+      <c r="C100" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3483,7 +3492,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="37" t="inlineStr">
+      <c r="A101" s="40" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -3491,7 +3500,7 @@
       <c r="B101" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C101" s="37" t="inlineStr">
+      <c r="C101" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3508,7 +3517,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="37" t="inlineStr">
+      <c r="A102" s="40" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -3516,7 +3525,7 @@
       <c r="B102" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C102" s="37" t="inlineStr">
+      <c r="C102" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3533,7 +3542,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="37" t="inlineStr">
+      <c r="A103" s="40" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -3541,7 +3550,7 @@
       <c r="B103" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C103" s="37" t="inlineStr">
+      <c r="C103" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3558,7 +3567,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="37" t="inlineStr">
+      <c r="A104" s="40" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -3566,7 +3575,7 @@
       <c r="B104" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C104" s="37" t="inlineStr">
+      <c r="C104" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3583,7 +3592,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="37" t="inlineStr">
+      <c r="A105" s="40" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -3591,7 +3600,7 @@
       <c r="B105" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C105" s="37" t="inlineStr">
+      <c r="C105" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3608,7 +3617,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="37" t="inlineStr">
+      <c r="A106" s="40" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -3616,7 +3625,7 @@
       <c r="B106" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C106" s="37" t="inlineStr">
+      <c r="C106" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3633,7 +3642,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="37" t="inlineStr">
+      <c r="A107" s="40" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -3641,7 +3650,7 @@
       <c r="B107" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C107" s="37" t="inlineStr">
+      <c r="C107" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3658,7 +3667,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="37" t="inlineStr">
+      <c r="A108" s="40" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -3666,7 +3675,7 @@
       <c r="B108" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C108" s="37" t="inlineStr">
+      <c r="C108" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3683,7 +3692,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="37" t="inlineStr">
+      <c r="A109" s="40" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -3691,7 +3700,7 @@
       <c r="B109" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C109" s="37" t="inlineStr">
+      <c r="C109" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3708,7 +3717,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="37" t="inlineStr">
+      <c r="A110" s="40" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -3716,7 +3725,7 @@
       <c r="B110" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C110" s="37" t="inlineStr">
+      <c r="C110" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3733,7 +3742,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="37" t="inlineStr">
+      <c r="A111" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -3741,7 +3750,7 @@
       <c r="B111" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C111" s="37" t="inlineStr">
+      <c r="C111" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3758,7 +3767,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="37" t="inlineStr">
+      <c r="A112" s="40" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -3766,7 +3775,7 @@
       <c r="B112" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C112" s="37" t="inlineStr">
+      <c r="C112" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3783,7 +3792,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="37" t="inlineStr">
+      <c r="A113" s="40" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -3791,7 +3800,7 @@
       <c r="B113" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C113" s="37" t="inlineStr">
+      <c r="C113" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3808,7 +3817,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="37" t="inlineStr">
+      <c r="A114" s="40" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -3816,7 +3825,7 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="37" t="inlineStr">
+      <c r="C114" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3833,7 +3842,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="37" t="inlineStr">
+      <c r="A115" s="40" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -3841,7 +3850,7 @@
       <c r="B115" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C115" s="37" t="inlineStr">
+      <c r="C115" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3858,7 +3867,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="37" t="inlineStr">
+      <c r="A116" s="40" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -3866,7 +3875,7 @@
       <c r="B116" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C116" s="37" t="inlineStr">
+      <c r="C116" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3883,7 +3892,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="37" t="inlineStr">
+      <c r="A117" s="40" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -3891,7 +3900,7 @@
       <c r="B117" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C117" s="37" t="inlineStr">
+      <c r="C117" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3908,7 +3917,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="37" t="inlineStr">
+      <c r="A118" s="40" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -3916,7 +3925,7 @@
       <c r="B118" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C118" s="37" t="inlineStr">
+      <c r="C118" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3933,7 +3942,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="37" t="inlineStr">
+      <c r="A119" s="40" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -3941,7 +3950,7 @@
       <c r="B119" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C119" s="37" t="inlineStr">
+      <c r="C119" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3958,7 +3967,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="37" t="inlineStr">
+      <c r="A120" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -3966,7 +3975,7 @@
       <c r="B120" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C120" s="37" t="inlineStr">
+      <c r="C120" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3983,7 +3992,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="37" t="inlineStr">
+      <c r="A121" s="40" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -3991,7 +4000,7 @@
       <c r="B121" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C121" s="37" t="inlineStr">
+      <c r="C121" s="40" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -4008,7 +4017,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="37" t="inlineStr">
+      <c r="A122" s="40" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -4016,7 +4025,7 @@
       <c r="B122" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C122" s="37" t="inlineStr">
+      <c r="C122" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4033,7 +4042,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="37" t="inlineStr">
+      <c r="A123" s="40" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -4041,7 +4050,7 @@
       <c r="B123" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C123" s="37" t="inlineStr">
+      <c r="C123" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4058,7 +4067,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="37" t="inlineStr">
+      <c r="A124" s="40" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -4066,7 +4075,7 @@
       <c r="B124" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C124" s="37" t="inlineStr">
+      <c r="C124" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4083,7 +4092,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="37" t="inlineStr">
+      <c r="A125" s="40" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -4091,7 +4100,7 @@
       <c r="B125" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C125" s="37" t="inlineStr">
+      <c r="C125" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4108,7 +4117,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="37" t="inlineStr">
+      <c r="A126" s="40" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -4116,7 +4125,7 @@
       <c r="B126" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C126" s="37" t="inlineStr">
+      <c r="C126" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4133,7 +4142,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="38" t="inlineStr">
+      <c r="A127" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4141,7 +4150,7 @@
       <c r="B127" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C127" s="38" t="inlineStr"/>
+      <c r="C127" s="41" t="inlineStr"/>
       <c r="D127" s="16" t="inlineStr"/>
       <c r="E127" s="16" t="inlineStr"/>
     </row>
@@ -4202,7 +4211,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -4211,14 +4220,14 @@
         <v>108126415.72</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>97301853.98999999</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-10824561.73</v>
+        <v>-11174561.73</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Налоги с ФОТ</t>
         </is>
@@ -4234,7 +4243,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -4250,7 +4259,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Расходы по кассе</t>
         </is>
@@ -4266,7 +4275,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Услуги банка (общие)</t>
         </is>
@@ -4275,14 +4284,14 @@
         <v>399308.17</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>141281.46</v>
+        <v>141191.07</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-258026.71</v>
+        <v>-258117.1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Эквайринг (персонально)</t>
         </is>
@@ -4298,7 +4307,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -4314,7 +4323,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>% по кредиту</t>
         </is>
@@ -4330,7 +4339,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Поставщики (счёт 60)</t>
         </is>
@@ -4346,7 +4355,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
@@ -4355,14 +4364,14 @@
         <v>72553130.98</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>88974167.45999999</v>
+        <v>88974077.06999999</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>16421036.48</v>
+        <v>16420946.09</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>ДОХОД (выручка − расходы)</t>
         </is>
@@ -4371,10 +4380,10 @@
         <v>35573284.74</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>8327686.53</v>
+        <v>7977776.92</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>-27245598.21</v>
+        <v>-27595507.82</v>
       </c>
     </row>
     <row r="17">
@@ -4407,7 +4416,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -4423,7 +4432,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр.1</t>
         </is>
@@ -4439,7 +4448,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
@@ -4455,7 +4464,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Досудебный спор</t>
         </is>
@@ -4471,7 +4480,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Прочие поставщики</t>
         </is>
@@ -4487,7 +4496,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4555,7 +4564,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>01–10.08, старая управленка</t>
         </is>
@@ -4563,14 +4572,14 @@
       <c r="B5" s="6" t="n">
         <v>31613514</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>реестр «Оплаты от пациента» без двух документов, помеченных на удаление; сходится с «Ежедневным отчётом по кассам»</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>11–31.08, новая управленка</t>
         </is>
@@ -4578,49 +4587,49 @@
       <c r="B6" s="6" t="n">
         <v>66058340</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными», уже за вычетом возвратов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Возвраты пациентам, 01–10.08</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-370000</v>
-      </c>
-      <c r="C7" s="37" t="inlineStr">
+        <v>-720000</v>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>колонка «Возврат денег» «Ежедневного отчёта по кассам»</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>97301854</v>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
+        <v>96951854</v>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>деньги, поступившие за месяц</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr"/>
+      <c r="A9" s="40" t="inlineStr"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="37" t="inlineStr"/>
+      <c r="C9" s="40" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>01–10.08: платежи с указанным специалистом</t>
         </is>
@@ -4628,14 +4637,14 @@
       <c r="B10" s="6" t="n">
         <v>30904014</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>колонка «Специалист» реестра платежей</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>01–10.08: без специалиста</t>
         </is>
@@ -4643,14 +4652,14 @@
       <c r="B11" s="6" t="n">
         <v>709500</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>разнесены по врачам того же пациента, остаток — пропорционально</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>11–31.08: привязано к врачу напрямую</t>
         </is>
@@ -4658,14 +4667,14 @@
       <c r="B12" s="6" t="n">
         <v>46401840</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>документы «Оказание услуг» — врач указан в документе</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>11–31.08: авансы, разнесённые через пациента</t>
         </is>
@@ -4673,14 +4682,14 @@
       <c r="B13" s="6" t="n">
         <v>14588000</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>оплата картой и кассовые ордера</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>11–31.08: авансы без совпадения по пациенту</t>
         </is>
@@ -4688,7 +4697,7 @@
       <c r="B14" s="6" t="n">
         <v>5068500</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="40" t="inlineStr">
         <is>
           <t>разнесены пропорционально; пациентов нет в реестре услуг августа</t>
         </is>
@@ -4722,7 +4731,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -4741,7 +4750,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -4760,26 +4769,26 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>30239933.64</v>
+        <v>29889933.64</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>46606046.11</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>76845979.75</v>
+        <v>76495979.75</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0.79</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -4798,7 +4807,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -4817,19 +4826,19 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>31243514</v>
+        <v>30893514</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>66058340</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>97301853.98999999</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>1</v>
@@ -4897,12 +4906,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Выручка за месяц</t>
         </is>
@@ -4927,12 +4936,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Доход учредителей за месяц</t>
         </is>
@@ -4957,12 +4966,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
@@ -4987,12 +4996,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Рост выручки с начала года</t>
         </is>
@@ -5015,12 +5024,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Выручка месяца, год к году</t>
         </is>
@@ -5043,12 +5052,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Выручка с начала года</t>
         </is>
@@ -5073,12 +5082,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Средняя выручка в день</t>
         </is>
@@ -5103,12 +5112,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Оплаты поставщикам (сч. 60)</t>
         </is>
@@ -5133,12 +5142,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>ФОТ с налогами по банку</t>
         </is>
@@ -5163,12 +5172,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
@@ -5193,12 +5202,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Касса (наличные)</t>
         </is>
@@ -5223,12 +5232,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Эквайринг (карты)</t>
         </is>
@@ -5253,12 +5262,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Оплаты физлиц на р/с</t>
         </is>
@@ -5283,12 +5292,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
@@ -5313,12 +5322,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Комиссия эквайринга</t>
         </is>
@@ -5343,12 +5352,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Медицинские расходы + ИП</t>
         </is>
@@ -5373,12 +5382,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -5403,12 +5412,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>в т.ч. гонорары ИП хирургов</t>
         </is>
@@ -5433,12 +5442,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>в т.ч. ремонт нового корпуса</t>
         </is>
@@ -5463,12 +5472,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Экономика</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Доход месяца (итог водопада)</t>
         </is>
@@ -5493,12 +5502,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Остаток на начало месяца</t>
         </is>
@@ -5523,12 +5532,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Поступления за месяц</t>
         </is>
@@ -5553,12 +5562,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Списания за месяц</t>
         </is>
@@ -5583,12 +5592,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Остаток на конец месяца</t>
         </is>
@@ -5613,12 +5622,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Маланичев: личная выручка</t>
         </is>
@@ -5643,12 +5652,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Маланичев: ½ выручки других хирургов</t>
         </is>
@@ -5673,12 +5682,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>Маланичев: ½ косметологии и прочего</t>
         </is>
@@ -5703,12 +5712,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>Маланичев: доля расходов</t>
         </is>
@@ -5733,12 +5742,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B32" s="34" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>Маланичев: доход за месяц</t>
         </is>
@@ -5763,12 +5772,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>Маланичев: остаток с прошлого месяца</t>
         </is>
@@ -5793,12 +5802,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B34" s="34" t="inlineStr">
+      <c r="B34" s="37" t="inlineStr">
         <is>
           <t>Маланичев: удержано в резерв (аренда)</t>
         </is>
@@ -5823,12 +5832,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>Маланичев: к выплате на конец месяца</t>
         </is>
@@ -5853,12 +5862,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>Погосян: личная выручка</t>
         </is>
@@ -5883,12 +5892,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>Погосян: ½ выручки других хирургов</t>
         </is>
@@ -5913,12 +5922,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>Погосян: ½ косметологии и прочего</t>
         </is>
@@ -5943,12 +5952,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>Погосян: доля расходов</t>
         </is>
@@ -5973,12 +5982,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>Погосян: доход за месяц</t>
         </is>
@@ -6003,12 +6012,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>Погосян: остаток с прошлого месяца</t>
         </is>
@@ -6033,12 +6042,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="B42" s="37" t="inlineStr">
         <is>
           <t>Погосян: удержано в резерв (аренда)</t>
         </is>
@@ -6063,12 +6072,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>Погосян: к выплате на конец месяца</t>
         </is>
@@ -6093,12 +6102,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B44" s="34" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>Долг по кредитной линии</t>
         </is>
@@ -6123,12 +6132,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B45" s="34" t="inlineStr">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>Остаток наличных в кассе</t>
         </is>
@@ -6151,12 +6160,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B46" s="34" t="inlineStr">
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -6181,12 +6190,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B47" s="34" t="inlineStr">
+      <c r="B47" s="37" t="inlineStr">
         <is>
           <t>Зарезервировано на аренду (всего)</t>
         </is>
@@ -6327,7 +6336,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
@@ -6369,7 +6378,7 @@
       <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -6411,7 +6420,7 @@
       <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
@@ -6453,7 +6462,7 @@
       <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
@@ -6495,7 +6504,7 @@
       <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -6537,7 +6546,7 @@
       <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
@@ -6579,7 +6588,7 @@
       <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -6621,7 +6630,7 @@
       <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
@@ -6663,7 +6672,7 @@
       <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
@@ -6705,7 +6714,7 @@
       <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
@@ -6747,7 +6756,7 @@
       <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
@@ -6789,7 +6798,7 @@
       <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -6831,7 +6840,7 @@
       <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
@@ -6873,7 +6882,7 @@
       <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
@@ -6915,7 +6924,7 @@
       <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -6957,7 +6966,7 @@
       <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
@@ -6999,7 +7008,7 @@
       <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
@@ -7041,7 +7050,7 @@
       <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -7083,7 +7092,7 @@
       <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7125,7 +7134,7 @@
       <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -7167,7 +7176,7 @@
       <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
@@ -7209,7 +7218,7 @@
       <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
@@ -7251,7 +7260,7 @@
       <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
@@ -7293,7 +7302,7 @@
       <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -7335,7 +7344,7 @@
       <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -7377,7 +7386,7 @@
       <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
@@ -7419,7 +7428,7 @@
       <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -7461,7 +7470,7 @@
       <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -7503,7 +7512,7 @@
       <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
@@ -7545,7 +7554,7 @@
       <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
@@ -7587,7 +7596,7 @@
       <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -7629,7 +7638,7 @@
       <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7755,7 +7764,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -7781,7 +7790,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -7807,7 +7816,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
@@ -7833,7 +7842,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -7859,7 +7868,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -7885,7 +7894,7 @@
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7942,7 +7951,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
@@ -7958,7 +7967,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
@@ -7974,7 +7983,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
@@ -7990,7 +7999,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
@@ -8006,7 +8015,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
@@ -8022,7 +8031,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
@@ -8038,7 +8047,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
@@ -8054,7 +8063,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
@@ -8066,7 +8075,7 @@
       <c r="D21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
@@ -8078,7 +8087,7 @@
       <c r="D22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
@@ -8090,7 +8099,7 @@
       <c r="D23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
@@ -8102,7 +8111,7 @@
       <c r="D24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
@@ -8163,12 +8172,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -8181,12 +8190,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
@@ -8199,12 +8208,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -8217,12 +8226,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
@@ -8235,12 +8244,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -8253,12 +8262,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
@@ -8271,12 +8280,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
@@ -8289,12 +8298,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
@@ -8307,12 +8316,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
@@ -8325,12 +8334,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
@@ -8343,12 +8352,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
@@ -8361,12 +8370,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
@@ -8379,12 +8388,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
@@ -8397,12 +8406,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
@@ -8415,12 +8424,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
@@ -8433,12 +8442,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
@@ -8451,12 +8460,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -8469,12 +8478,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
@@ -8487,12 +8496,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
@@ -8505,12 +8514,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
@@ -8523,12 +8532,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -8541,12 +8550,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
@@ -8559,12 +8568,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
@@ -8577,12 +8586,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -8595,12 +8604,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
@@ -8613,12 +8622,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
@@ -8631,12 +8640,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
@@ -8649,12 +8658,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
@@ -8667,12 +8676,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B32" s="34" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
@@ -8685,12 +8694,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -8703,12 +8712,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B34" s="34" t="inlineStr">
+      <c r="B34" s="37" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
@@ -8721,12 +8730,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
@@ -8739,12 +8748,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
@@ -8757,12 +8766,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
@@ -8775,12 +8784,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -8793,12 +8802,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
@@ -8811,12 +8820,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
@@ -8829,12 +8838,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
@@ -8847,12 +8856,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="B42" s="37" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
@@ -8865,12 +8874,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -8883,12 +8892,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B44" s="34" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
@@ -8901,12 +8910,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B45" s="34" t="inlineStr">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
@@ -8919,12 +8928,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B46" s="34" t="inlineStr">
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
@@ -8937,12 +8946,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B47" s="34" t="inlineStr">
+      <c r="B47" s="37" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
@@ -8955,12 +8964,12 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B48" s="34" t="inlineStr">
+      <c r="B48" s="37" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
@@ -8973,12 +8982,12 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="34" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B49" s="34" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
@@ -8991,12 +9000,12 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="A50" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B50" s="34" t="inlineStr">
+      <c r="B50" s="37" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
@@ -9009,12 +9018,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="34" t="inlineStr">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B51" s="34" t="inlineStr">
+      <c r="B51" s="37" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
@@ -9027,12 +9036,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="34" t="inlineStr">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B52" s="34" t="inlineStr">
+      <c r="B52" s="37" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
@@ -9045,12 +9054,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="34" t="inlineStr">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B53" s="34" t="inlineStr">
+      <c r="B53" s="37" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
@@ -9063,12 +9072,12 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B54" s="34" t="inlineStr">
+      <c r="B54" s="37" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
@@ -9081,12 +9090,12 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B55" s="34" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
@@ -9099,12 +9108,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="34" t="inlineStr">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B56" s="34" t="inlineStr">
+      <c r="B56" s="37" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
@@ -9117,12 +9126,12 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="34" t="inlineStr">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B57" s="34" t="inlineStr">
+      <c r="B57" s="37" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
@@ -9135,12 +9144,12 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="34" t="inlineStr">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B58" s="34" t="inlineStr">
+      <c r="B58" s="37" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
@@ -9153,12 +9162,12 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="34" t="inlineStr">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B59" s="34" t="inlineStr">
+      <c r="B59" s="37" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
@@ -9171,12 +9180,12 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="34" t="inlineStr">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B60" s="34" t="inlineStr">
+      <c r="B60" s="37" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
@@ -9189,12 +9198,12 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="34" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B61" s="34" t="inlineStr">
+      <c r="B61" s="37" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
@@ -9207,12 +9216,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="34" t="inlineStr">
+      <c r="A62" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B62" s="34" t="inlineStr">
+      <c r="B62" s="37" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
@@ -9225,12 +9234,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="34" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B63" s="34" t="inlineStr">
+      <c r="B63" s="37" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
@@ -9243,12 +9252,12 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="A64" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B64" s="34" t="inlineStr">
+      <c r="B64" s="37" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
@@ -9261,12 +9270,12 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="34" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B65" s="34" t="inlineStr">
+      <c r="B65" s="37" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
@@ -9279,12 +9288,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="34" t="inlineStr">
+      <c r="A66" s="37" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B66" s="34" t="inlineStr">
+      <c r="B66" s="37" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -9297,12 +9306,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="35" t="inlineStr">
+      <c r="A67" s="38" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B67" s="35" t="inlineStr">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -9315,12 +9324,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="36" t="inlineStr">
+      <c r="A68" s="39" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B68" s="36" t="inlineStr"/>
+      <c r="B68" s="39" t="inlineStr"/>
       <c r="C68" s="14" t="n">
         <v>69794048.05</v>
       </c>
@@ -9370,7 +9379,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -9378,14 +9387,14 @@
       <c r="B4" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Ремонт Самокатная 1 стр12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -9393,14 +9402,14 @@
       <c r="B5" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -9408,14 +9417,14 @@
       <c r="B6" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -9423,14 +9432,14 @@
       <c r="B7" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -9438,14 +9447,14 @@
       <c r="B8" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -9453,14 +9462,14 @@
       <c r="B9" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -9468,14 +9477,14 @@
       <c r="B10" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -9483,14 +9492,14 @@
       <c r="B11" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -9498,14 +9507,14 @@
       <c r="B12" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -9513,14 +9522,14 @@
       <c r="B13" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -9528,14 +9537,14 @@
       <c r="B14" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -9543,14 +9552,14 @@
       <c r="B15" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -9558,14 +9567,14 @@
       <c r="B16" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -9573,14 +9582,14 @@
       <c r="B17" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -9588,14 +9597,14 @@
       <c r="B18" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -9603,14 +9612,14 @@
       <c r="B19" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -9618,14 +9627,14 @@
       <c r="B20" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -9633,14 +9642,14 @@
       <c r="B21" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -9648,14 +9657,14 @@
       <c r="B22" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -9663,14 +9672,14 @@
       <c r="B23" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -9678,14 +9687,14 @@
       <c r="B24" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -9693,14 +9702,14 @@
       <c r="B25" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -9708,14 +9717,14 @@
       <c r="B26" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -9723,14 +9732,14 @@
       <c r="B27" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -9738,14 +9747,14 @@
       <c r="B28" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -9753,14 +9762,14 @@
       <c r="B29" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -9768,14 +9777,14 @@
       <c r="B30" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -9783,14 +9792,14 @@
       <c r="B31" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -9798,14 +9807,14 @@
       <c r="B32" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -9813,14 +9822,14 @@
       <c r="B33" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -9828,14 +9837,14 @@
       <c r="B34" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -9843,14 +9852,14 @@
       <c r="B35" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -9858,14 +9867,14 @@
       <c r="B36" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -9873,14 +9882,14 @@
       <c r="B37" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -9888,14 +9897,14 @@
       <c r="B38" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -9903,14 +9912,14 @@
       <c r="B39" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -9918,14 +9927,14 @@
       <c r="B40" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -9933,14 +9942,14 @@
       <c r="B41" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -9948,14 +9957,14 @@
       <c r="B42" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -9963,14 +9972,14 @@
       <c r="B43" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -9978,14 +9987,14 @@
       <c r="B44" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C44" s="34" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -9993,14 +10002,14 @@
       <c r="B45" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -10008,14 +10017,14 @@
       <c r="B46" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C46" s="34" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -10023,14 +10032,14 @@
       <c r="B47" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -10038,14 +10047,14 @@
       <c r="B48" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="34" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -10053,14 +10062,14 @@
       <c r="B49" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="A50" s="37" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -10068,14 +10077,14 @@
       <c r="B50" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="34" t="inlineStr">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -10083,14 +10092,14 @@
       <c r="B51" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C51" s="34" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="34" t="inlineStr">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -10098,14 +10107,14 @@
       <c r="B52" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="34" t="inlineStr">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -10113,14 +10122,14 @@
       <c r="B53" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -10128,14 +10137,14 @@
       <c r="B54" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C54" s="34" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -10143,14 +10152,14 @@
       <c r="B55" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C55" s="34" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="34" t="inlineStr">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -10158,14 +10167,14 @@
       <c r="B56" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C56" s="34" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="34" t="inlineStr">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -10173,14 +10182,14 @@
       <c r="B57" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C57" s="34" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="34" t="inlineStr">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -10188,14 +10197,14 @@
       <c r="B58" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C58" s="34" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="34" t="inlineStr">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -10203,14 +10212,14 @@
       <c r="B59" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C59" s="34" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="34" t="inlineStr">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -10218,14 +10227,14 @@
       <c r="B60" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C60" s="34" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="34" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -10233,14 +10242,14 @@
       <c r="B61" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C61" s="34" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="34" t="inlineStr">
+      <c r="A62" s="37" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -10248,14 +10257,14 @@
       <c r="B62" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C62" s="34" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="34" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -10263,14 +10272,14 @@
       <c r="B63" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C63" s="34" t="inlineStr">
+      <c r="C63" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="A64" s="37" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -10278,14 +10287,14 @@
       <c r="B64" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C64" s="34" t="inlineStr">
+      <c r="C64" s="37" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="34" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -10293,14 +10302,14 @@
       <c r="B65" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="C65" s="37" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="34" t="inlineStr">
+      <c r="A66" s="37" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -10308,14 +10317,14 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="34" t="inlineStr">
+      <c r="C66" s="37" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="34" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -10323,14 +10332,14 @@
       <c r="B67" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C67" s="34" t="inlineStr">
+      <c r="C67" s="37" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="34" t="inlineStr">
+      <c r="A68" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -10338,14 +10347,14 @@
       <c r="B68" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C68" s="34" t="inlineStr">
+      <c r="C68" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="34" t="inlineStr">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -10353,14 +10362,14 @@
       <c r="B69" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C69" s="34" t="inlineStr">
+      <c r="C69" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="34" t="inlineStr">
+      <c r="A70" s="37" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -10368,14 +10377,14 @@
       <c r="B70" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C70" s="34" t="inlineStr">
+      <c r="C70" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="34" t="inlineStr">
+      <c r="A71" s="37" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -10383,14 +10392,14 @@
       <c r="B71" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C71" s="34" t="inlineStr">
+      <c r="C71" s="37" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="34" t="inlineStr">
+      <c r="A72" s="37" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -10398,14 +10407,14 @@
       <c r="B72" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C72" s="34" t="inlineStr">
+      <c r="C72" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="34" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -10413,14 +10422,14 @@
       <c r="B73" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C73" s="34" t="inlineStr">
+      <c r="C73" s="37" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="34" t="inlineStr">
+      <c r="A74" s="37" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -10428,14 +10437,14 @@
       <c r="B74" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C74" s="34" t="inlineStr">
+      <c r="C74" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="34" t="inlineStr">
+      <c r="A75" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -10443,14 +10452,14 @@
       <c r="B75" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C75" s="34" t="inlineStr">
+      <c r="C75" s="37" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="34" t="inlineStr">
+      <c r="A76" s="37" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -10458,14 +10467,14 @@
       <c r="B76" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C76" s="34" t="inlineStr">
+      <c r="C76" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="34" t="inlineStr">
+      <c r="A77" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -10473,14 +10482,14 @@
       <c r="B77" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C77" s="34" t="inlineStr">
+      <c r="C77" s="37" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="34" t="inlineStr">
+      <c r="A78" s="37" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -10488,14 +10497,14 @@
       <c r="B78" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C78" s="34" t="inlineStr">
+      <c r="C78" s="37" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="34" t="inlineStr">
+      <c r="A79" s="37" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -10503,14 +10512,14 @@
       <c r="B79" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C79" s="34" t="inlineStr">
+      <c r="C79" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="34" t="inlineStr">
+      <c r="A80" s="37" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -10518,14 +10527,14 @@
       <c r="B80" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C80" s="34" t="inlineStr">
+      <c r="C80" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="34" t="inlineStr">
+      <c r="A81" s="37" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -10533,14 +10542,14 @@
       <c r="B81" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C81" s="34" t="inlineStr">
+      <c r="C81" s="37" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="34" t="inlineStr">
+      <c r="A82" s="37" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -10548,14 +10557,14 @@
       <c r="B82" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C82" s="34" t="inlineStr">
+      <c r="C82" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="34" t="inlineStr">
+      <c r="A83" s="37" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -10563,14 +10572,14 @@
       <c r="B83" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C83" s="34" t="inlineStr">
+      <c r="C83" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="34" t="inlineStr">
+      <c r="A84" s="37" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -10578,14 +10587,14 @@
       <c r="B84" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C84" s="34" t="inlineStr">
+      <c r="C84" s="37" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="34" t="inlineStr">
+      <c r="A85" s="37" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -10593,14 +10602,14 @@
       <c r="B85" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C85" s="34" t="inlineStr">
+      <c r="C85" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="34" t="inlineStr">
+      <c r="A86" s="37" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -10608,14 +10617,14 @@
       <c r="B86" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C86" s="34" t="inlineStr">
+      <c r="C86" s="37" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="34" t="inlineStr">
+      <c r="A87" s="37" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -10623,14 +10632,14 @@
       <c r="B87" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C87" s="34" t="inlineStr">
+      <c r="C87" s="37" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="34" t="inlineStr">
+      <c r="A88" s="37" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -10638,14 +10647,14 @@
       <c r="B88" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C88" s="34" t="inlineStr">
+      <c r="C88" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="34" t="inlineStr">
+      <c r="A89" s="37" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -10653,14 +10662,14 @@
       <c r="B89" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C89" s="34" t="inlineStr">
+      <c r="C89" s="37" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="34" t="inlineStr">
+      <c r="A90" s="37" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -10668,14 +10677,14 @@
       <c r="B90" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C90" s="34" t="inlineStr">
+      <c r="C90" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="34" t="inlineStr">
+      <c r="A91" s="37" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -10683,14 +10692,14 @@
       <c r="B91" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C91" s="34" t="inlineStr">
+      <c r="C91" s="37" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="34" t="inlineStr">
+      <c r="A92" s="37" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -10698,14 +10707,14 @@
       <c r="B92" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C92" s="34" t="inlineStr">
+      <c r="C92" s="37" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="34" t="inlineStr">
+      <c r="A93" s="37" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -10713,14 +10722,14 @@
       <c r="B93" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C93" s="34" t="inlineStr">
+      <c r="C93" s="37" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="34" t="inlineStr">
+      <c r="A94" s="37" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -10728,14 +10737,14 @@
       <c r="B94" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C94" s="34" t="inlineStr">
+      <c r="C94" s="37" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="34" t="inlineStr">
+      <c r="A95" s="37" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -10743,14 +10752,14 @@
       <c r="B95" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C95" s="34" t="inlineStr">
+      <c r="C95" s="37" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="34" t="inlineStr">
+      <c r="A96" s="37" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -10758,14 +10767,14 @@
       <c r="B96" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C96" s="34" t="inlineStr">
+      <c r="C96" s="37" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="34" t="inlineStr">
+      <c r="A97" s="37" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -10773,14 +10782,14 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="34" t="inlineStr">
+      <c r="C97" s="37" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="34" t="inlineStr">
+      <c r="A98" s="37" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -10788,14 +10797,14 @@
       <c r="B98" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C98" s="34" t="inlineStr">
+      <c r="C98" s="37" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="34" t="inlineStr">
+      <c r="A99" s="37" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -10803,14 +10812,14 @@
       <c r="B99" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C99" s="34" t="inlineStr">
+      <c r="C99" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="34" t="inlineStr">
+      <c r="A100" s="37" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -10818,14 +10827,14 @@
       <c r="B100" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C100" s="34" t="inlineStr">
+      <c r="C100" s="37" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="34" t="inlineStr">
+      <c r="A101" s="37" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -10833,14 +10842,14 @@
       <c r="B101" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C101" s="34" t="inlineStr">
+      <c r="C101" s="37" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="34" t="inlineStr">
+      <c r="A102" s="37" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -10848,14 +10857,14 @@
       <c r="B102" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C102" s="34" t="inlineStr">
+      <c r="C102" s="37" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="34" t="inlineStr">
+      <c r="A103" s="37" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -10863,14 +10872,14 @@
       <c r="B103" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C103" s="34" t="inlineStr">
+      <c r="C103" s="37" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="34" t="inlineStr">
+      <c r="A104" s="37" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -10878,14 +10887,14 @@
       <c r="B104" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C104" s="34" t="inlineStr">
+      <c r="C104" s="37" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="34" t="inlineStr">
+      <c r="A105" s="37" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -10893,14 +10902,14 @@
       <c r="B105" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C105" s="34" t="inlineStr">
+      <c r="C105" s="37" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="34" t="inlineStr">
+      <c r="A106" s="37" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -10908,14 +10917,14 @@
       <c r="B106" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C106" s="34" t="inlineStr">
+      <c r="C106" s="37" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="34" t="inlineStr">
+      <c r="A107" s="37" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -10923,14 +10932,14 @@
       <c r="B107" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C107" s="34" t="inlineStr">
+      <c r="C107" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="34" t="inlineStr">
+      <c r="A108" s="37" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -10938,14 +10947,14 @@
       <c r="B108" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C108" s="34" t="inlineStr">
+      <c r="C108" s="37" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="34" t="inlineStr">
+      <c r="A109" s="37" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -10953,14 +10962,14 @@
       <c r="B109" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C109" s="34" t="inlineStr">
+      <c r="C109" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="34" t="inlineStr">
+      <c r="A110" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -10968,14 +10977,14 @@
       <c r="B110" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C110" s="34" t="inlineStr">
+      <c r="C110" s="37" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="34" t="inlineStr">
+      <c r="A111" s="37" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -10983,14 +10992,14 @@
       <c r="B111" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C111" s="34" t="inlineStr">
+      <c r="C111" s="37" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="34" t="inlineStr">
+      <c r="A112" s="37" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -10998,14 +11007,14 @@
       <c r="B112" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C112" s="34" t="inlineStr">
+      <c r="C112" s="37" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="34" t="inlineStr">
+      <c r="A113" s="37" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -11013,14 +11022,14 @@
       <c r="B113" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C113" s="34" t="inlineStr">
+      <c r="C113" s="37" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="34" t="inlineStr">
+      <c r="A114" s="37" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -11028,14 +11037,14 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="34" t="inlineStr">
+      <c r="C114" s="37" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="34" t="inlineStr">
+      <c r="A115" s="37" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -11043,14 +11052,14 @@
       <c r="B115" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C115" s="34" t="inlineStr">
+      <c r="C115" s="37" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="34" t="inlineStr">
+      <c r="A116" s="37" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -11058,14 +11067,14 @@
       <c r="B116" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C116" s="34" t="inlineStr">
+      <c r="C116" s="37" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="34" t="inlineStr">
+      <c r="A117" s="37" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -11073,14 +11082,14 @@
       <c r="B117" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C117" s="34" t="inlineStr">
+      <c r="C117" s="37" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="34" t="inlineStr">
+      <c r="A118" s="37" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -11088,14 +11097,14 @@
       <c r="B118" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C118" s="34" t="inlineStr">
+      <c r="C118" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="34" t="inlineStr">
+      <c r="A119" s="37" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -11103,14 +11112,14 @@
       <c r="B119" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C119" s="34" t="inlineStr">
+      <c r="C119" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="34" t="inlineStr">
+      <c r="A120" s="37" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -11118,14 +11127,14 @@
       <c r="B120" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C120" s="34" t="inlineStr">
+      <c r="C120" s="37" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="34" t="inlineStr">
+      <c r="A121" s="37" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -11133,14 +11142,14 @@
       <c r="B121" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C121" s="34" t="inlineStr">
+      <c r="C121" s="37" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="34" t="inlineStr">
+      <c r="A122" s="37" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -11148,14 +11157,14 @@
       <c r="B122" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C122" s="34" t="inlineStr">
+      <c r="C122" s="37" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="34" t="inlineStr">
+      <c r="A123" s="37" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -11163,14 +11172,14 @@
       <c r="B123" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C123" s="34" t="inlineStr">
+      <c r="C123" s="37" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="34" t="inlineStr">
+      <c r="A124" s="37" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -11178,14 +11187,14 @@
       <c r="B124" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C124" s="34" t="inlineStr">
+      <c r="C124" s="37" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="34" t="inlineStr">
+      <c r="A125" s="37" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -11193,14 +11202,14 @@
       <c r="B125" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C125" s="34" t="inlineStr">
+      <c r="C125" s="37" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="35" t="inlineStr">
+      <c r="A126" s="38" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -11208,7 +11217,7 @@
       <c r="B126" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C126" s="35" t="inlineStr"/>
+      <c r="C126" s="38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11260,7 +11269,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Начальное сальдо</t>
         </is>
@@ -11272,7 +11281,7 @@
       <c r="D4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Возврат средств с депозитов</t>
         </is>
@@ -11288,7 +11297,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Инкассация и эквайринг</t>
         </is>
@@ -11304,7 +11313,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Возвраты от поставщиков</t>
         </is>
@@ -11320,7 +11329,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Кредит банка</t>
         </is>
@@ -11336,7 +11345,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
@@ -11352,7 +11361,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -11368,7 +11377,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Размещение на депозиты</t>
         </is>
@@ -11384,7 +11393,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Переводы между счетами</t>
         </is>
@@ -11400,7 +11409,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Оплаты поставщикам и подрядчикам</t>
         </is>
@@ -11416,7 +11425,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
@@ -11432,7 +11441,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
@@ -11448,7 +11457,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>Страховые взносы</t>
         </is>
@@ -11464,7 +11473,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -11480,7 +11489,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Выплата дивидендов</t>
         </is>
@@ -11496,7 +11505,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -11512,7 +11521,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -11528,7 +11537,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>Оборот за месяц</t>
         </is>
@@ -11542,7 +11551,7 @@
       <c r="D21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>Конечное сальдо</t>
         </is>
@@ -11626,12 +11635,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Личная выручка (свои операции)</t>
         </is>
@@ -11652,12 +11661,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>+ ½ выручки других хирургов</t>
         </is>
@@ -11678,12 +11687,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>+ ½ косметологии</t>
         </is>
@@ -11704,12 +11713,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>+ ½ прочих доходов</t>
         </is>
@@ -11730,12 +11739,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>+ ½ процентов по депозитам</t>
         </is>
@@ -11782,8 +11791,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr"/>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr"/>
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      налоги с ФОТ (68.90 + 69)</t>
         </is>
@@ -11800,8 +11809,8 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr"/>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr"/>
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      зарплата по банку</t>
         </is>
@@ -11818,8 +11827,8 @@
       <c r="F12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr"/>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr"/>
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      расходы по кассе</t>
         </is>
@@ -11836,8 +11845,8 @@
       <c r="F13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr"/>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr"/>
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      услуги банка (общие)</t>
         </is>
@@ -11854,8 +11863,8 @@
       <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr"/>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr"/>
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      услуги банка (эквайринг, персонально)</t>
         </is>
@@ -11872,8 +11881,8 @@
       <c r="F15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr"/>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr"/>
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      алименты (удержание из ЗП)</t>
         </is>
@@ -11890,8 +11899,8 @@
       <c r="F16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr"/>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr"/>
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      дополнительные корректировки</t>
         </is>
@@ -11908,8 +11917,8 @@
       <c r="F17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr"/>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr"/>
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">      поставщики (счёт 60) + Халва</t>
         </is>
@@ -11926,12 +11935,12 @@
       <c r="F18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
@@ -11952,12 +11961,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>+ Остаток с прошлого месяца</t>
         </is>
@@ -11978,12 +11987,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>− Выплачены дивиденды</t>
         </is>
@@ -12004,12 +12013,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
@@ -12092,10 +12101,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="n">
+      <c r="A5" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -12111,10 +12120,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -12130,10 +12139,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="n">
+      <c r="A7" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Медицинские расходы</t>
         </is>
@@ -12149,10 +12158,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>ФОТ, налоги, алименты</t>
         </is>
@@ -12168,10 +12177,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="n">
+      <c r="A9" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -12187,10 +12196,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Ремонт нового корпуса</t>
         </is>
@@ -12206,10 +12215,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="n">
+      <c r="A11" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -12225,10 +12234,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n">
+      <c r="A12" s="38" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -12244,10 +12253,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>Доход месяца</t>
         </is>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +175,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -638,108 +647,108 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>01 Цифры отчёта</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Каждая цифра из HTML-отчёта: значение, формула, источник. Главный лист расшифровки.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>02 Выручка по дням</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Дневная выручка по группам врачей и каналам оплаты + сверка с онлайн-кассой.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>03 Выручка структура</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Итоги по группам врачей и каналам поступления, доли в выручке, комиссия эквайринга.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>04 Расходы категории</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Счёт 60 в разрезе статей: медицинские + ИП и управленческие.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>05 Расходы контрагенты</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Счёт 60 построчно по контрагентам с назначением платежа.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>06 ДДС сч.51</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Обороты расчётного счёта: поступления и списания по корреспондирующим счетам.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>07 Учредители</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Методика 50/50 по шагам: выручка, доли расходов, доход, остаток, резерв, к выплате.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>08 Водопад</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>От выручки к доходу месяца — те же шаги, что на графике «Куда уходит выручка».</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>09 Контроль</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Контрольные равенства: сходится ли отчёт сам с собой и с данными бухгалтерии.</t>
         </is>
@@ -842,7 +851,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Сумма выручки по группам = итог выручки</t>
         </is>
@@ -864,7 +873,7 @@
       <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Касса + эквайринг + р/с физлиц − возвраты = итог выручки</t>
         </is>
@@ -886,7 +895,7 @@
       <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Сумма шагов водопада = доход месяца</t>
         </is>
@@ -912,7 +921,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Доход Маланичева + Погосяна = доход компании</t>
         </is>
@@ -934,7 +943,7 @@
       <c r="F8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Расходы 60: медицинские + управленческие = итог по счёту</t>
         </is>
@@ -956,7 +965,7 @@
       <c r="F9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Расходы 60: сумма по контрагентам = итог по счёту</t>
         </is>
@@ -982,7 +991,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>ДДС: сальдо нач. + приход − расход = сальдо кон.</t>
         </is>
@@ -1004,7 +1013,7 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Выручка (отчёт) vs выручка кассовым методом (график динамики)</t>
         </is>
@@ -1092,7 +1101,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -1100,7 +1109,7 @@
       <c r="B5" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1117,7 +1126,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -1125,7 +1134,7 @@
       <c r="B6" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1142,7 +1151,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -1150,7 +1159,7 @@
       <c r="B7" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1167,7 +1176,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -1175,7 +1184,7 @@
       <c r="B8" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1192,7 +1201,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -1200,7 +1209,7 @@
       <c r="B9" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1217,7 +1226,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -1225,7 +1234,7 @@
       <c r="B10" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1242,7 +1251,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -1250,7 +1259,7 @@
       <c r="B11" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1267,7 +1276,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -1275,7 +1284,7 @@
       <c r="B12" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1292,7 +1301,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -1300,7 +1309,7 @@
       <c r="B13" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1317,7 +1326,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -1325,7 +1334,7 @@
       <c r="B14" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C14" s="40" t="inlineStr">
+      <c r="C14" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1342,7 +1351,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -1350,7 +1359,7 @@
       <c r="B15" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1367,7 +1376,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -1375,7 +1384,7 @@
       <c r="B16" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1392,7 +1401,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -1400,7 +1409,7 @@
       <c r="B17" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1417,7 +1426,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -1425,7 +1434,7 @@
       <c r="B18" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1442,7 +1451,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -1450,7 +1459,7 @@
       <c r="B19" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1467,7 +1476,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -1475,7 +1484,7 @@
       <c r="B20" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C20" s="40" t="inlineStr">
+      <c r="C20" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1492,7 +1501,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -1500,7 +1509,7 @@
       <c r="B21" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1517,7 +1526,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -1525,7 +1534,7 @@
       <c r="B22" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1542,7 +1551,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -1550,7 +1559,7 @@
       <c r="B23" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1567,7 +1576,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="43" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -1575,7 +1584,7 @@
       <c r="B24" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C24" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1592,7 +1601,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="43" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -1600,7 +1609,7 @@
       <c r="B25" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1617,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -1625,7 +1634,7 @@
       <c r="B26" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1642,7 +1651,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -1650,7 +1659,7 @@
       <c r="B27" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1667,7 +1676,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="inlineStr">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -1675,7 +1684,7 @@
       <c r="B28" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1692,7 +1701,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="inlineStr">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -1700,7 +1709,7 @@
       <c r="B29" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C29" s="40" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1717,7 +1726,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="inlineStr">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -1725,7 +1734,7 @@
       <c r="B30" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C30" s="40" t="inlineStr">
+      <c r="C30" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1742,7 +1751,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="inlineStr">
+      <c r="A31" s="43" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -1750,7 +1759,7 @@
       <c r="B31" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C31" s="40" t="inlineStr">
+      <c r="C31" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1767,7 +1776,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="inlineStr">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -1775,7 +1784,7 @@
       <c r="B32" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1792,7 +1801,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -1800,7 +1809,7 @@
       <c r="B33" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1817,7 +1826,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="inlineStr">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -1825,7 +1834,7 @@
       <c r="B34" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C34" s="40" t="inlineStr">
+      <c r="C34" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1842,7 +1851,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="43" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -1850,7 +1859,7 @@
       <c r="B35" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C35" s="40" t="inlineStr">
+      <c r="C35" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1867,7 +1876,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="43" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -1875,7 +1884,7 @@
       <c r="B36" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C36" s="40" t="inlineStr">
+      <c r="C36" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1892,7 +1901,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="43" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -1900,7 +1909,7 @@
       <c r="B37" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C37" s="40" t="inlineStr">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1917,7 +1926,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40" t="inlineStr">
+      <c r="A38" s="43" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -1925,7 +1934,7 @@
       <c r="B38" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C38" s="40" t="inlineStr">
+      <c r="C38" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1942,7 +1951,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="40" t="inlineStr">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -1950,7 +1959,7 @@
       <c r="B39" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C39" s="40" t="inlineStr">
+      <c r="C39" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1967,7 +1976,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="40" t="inlineStr">
+      <c r="A40" s="43" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -1975,7 +1984,7 @@
       <c r="B40" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C40" s="40" t="inlineStr">
+      <c r="C40" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1992,7 +2001,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="43" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -2000,7 +2009,7 @@
       <c r="B41" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C41" s="40" t="inlineStr">
+      <c r="C41" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2017,7 +2026,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="A42" s="43" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -2025,7 +2034,7 @@
       <c r="B42" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C42" s="40" t="inlineStr">
+      <c r="C42" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2042,7 +2051,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="40" t="inlineStr">
+      <c r="A43" s="43" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -2050,7 +2059,7 @@
       <c r="B43" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C43" s="40" t="inlineStr">
+      <c r="C43" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2067,7 +2076,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="40" t="inlineStr">
+      <c r="A44" s="43" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -2075,7 +2084,7 @@
       <c r="B44" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C44" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2092,7 +2101,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="40" t="inlineStr">
+      <c r="A45" s="43" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -2100,7 +2109,7 @@
       <c r="B45" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C45" s="40" t="inlineStr">
+      <c r="C45" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2117,7 +2126,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="40" t="inlineStr">
+      <c r="A46" s="43" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -2125,7 +2134,7 @@
       <c r="B46" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C46" s="40" t="inlineStr">
+      <c r="C46" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2142,7 +2151,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="40" t="inlineStr">
+      <c r="A47" s="43" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -2150,7 +2159,7 @@
       <c r="B47" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C47" s="40" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2167,7 +2176,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="40" t="inlineStr">
+      <c r="A48" s="43" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -2175,7 +2184,7 @@
       <c r="B48" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C48" s="40" t="inlineStr">
+      <c r="C48" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2192,7 +2201,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="40" t="inlineStr">
+      <c r="A49" s="43" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -2200,7 +2209,7 @@
       <c r="B49" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C49" s="40" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2217,7 +2226,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="40" t="inlineStr">
+      <c r="A50" s="43" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -2225,7 +2234,7 @@
       <c r="B50" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C50" s="40" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2242,7 +2251,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40" t="inlineStr">
+      <c r="A51" s="43" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -2250,7 +2259,7 @@
       <c r="B51" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C51" s="40" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2267,7 +2276,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="40" t="inlineStr">
+      <c r="A52" s="43" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -2275,7 +2284,7 @@
       <c r="B52" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C52" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2292,7 +2301,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="40" t="inlineStr">
+      <c r="A53" s="43" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -2300,7 +2309,7 @@
       <c r="B53" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C53" s="40" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2317,7 +2326,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="40" t="inlineStr">
+      <c r="A54" s="43" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -2325,7 +2334,7 @@
       <c r="B54" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C54" s="40" t="inlineStr">
+      <c r="C54" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2342,7 +2351,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="40" t="inlineStr">
+      <c r="A55" s="43" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -2350,7 +2359,7 @@
       <c r="B55" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C55" s="40" t="inlineStr">
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2367,7 +2376,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="40" t="inlineStr">
+      <c r="A56" s="43" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -2375,7 +2384,7 @@
       <c r="B56" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C56" s="40" t="inlineStr">
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2392,7 +2401,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="40" t="inlineStr">
+      <c r="A57" s="43" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -2400,7 +2409,7 @@
       <c r="B57" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C57" s="40" t="inlineStr">
+      <c r="C57" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2417,7 +2426,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="40" t="inlineStr">
+      <c r="A58" s="43" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -2425,7 +2434,7 @@
       <c r="B58" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C58" s="40" t="inlineStr">
+      <c r="C58" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2442,7 +2451,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="40" t="inlineStr">
+      <c r="A59" s="43" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -2450,7 +2459,7 @@
       <c r="B59" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C59" s="40" t="inlineStr">
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2467,7 +2476,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="40" t="inlineStr">
+      <c r="A60" s="43" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -2475,7 +2484,7 @@
       <c r="B60" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C60" s="40" t="inlineStr">
+      <c r="C60" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2492,7 +2501,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="40" t="inlineStr">
+      <c r="A61" s="43" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -2500,7 +2509,7 @@
       <c r="B61" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C61" s="40" t="inlineStr">
+      <c r="C61" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2517,7 +2526,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="40" t="inlineStr">
+      <c r="A62" s="43" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -2525,7 +2534,7 @@
       <c r="B62" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C62" s="40" t="inlineStr">
+      <c r="C62" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2542,7 +2551,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="40" t="inlineStr">
+      <c r="A63" s="43" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -2550,7 +2559,7 @@
       <c r="B63" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C63" s="40" t="inlineStr">
+      <c r="C63" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2567,7 +2576,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="40" t="inlineStr">
+      <c r="A64" s="43" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -2575,7 +2584,7 @@
       <c r="B64" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C64" s="40" t="inlineStr">
+      <c r="C64" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2592,7 +2601,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="40" t="inlineStr">
+      <c r="A65" s="43" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -2600,7 +2609,7 @@
       <c r="B65" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C65" s="40" t="inlineStr">
+      <c r="C65" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2617,7 +2626,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="40" t="inlineStr">
+      <c r="A66" s="43" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -2625,7 +2634,7 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="40" t="inlineStr">
+      <c r="C66" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2642,7 +2651,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="40" t="inlineStr">
+      <c r="A67" s="43" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -2650,7 +2659,7 @@
       <c r="B67" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C67" s="40" t="inlineStr">
+      <c r="C67" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2667,7 +2676,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="40" t="inlineStr">
+      <c r="A68" s="43" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -2675,7 +2684,7 @@
       <c r="B68" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C68" s="40" t="inlineStr">
+      <c r="C68" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2692,7 +2701,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="40" t="inlineStr">
+      <c r="A69" s="43" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -2700,7 +2709,7 @@
       <c r="B69" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C69" s="40" t="inlineStr">
+      <c r="C69" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2717,7 +2726,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="40" t="inlineStr">
+      <c r="A70" s="43" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -2725,7 +2734,7 @@
       <c r="B70" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C70" s="40" t="inlineStr">
+      <c r="C70" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2742,7 +2751,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="40" t="inlineStr">
+      <c r="A71" s="43" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -2750,7 +2759,7 @@
       <c r="B71" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C71" s="40" t="inlineStr">
+      <c r="C71" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2767,7 +2776,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="40" t="inlineStr">
+      <c r="A72" s="43" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -2775,7 +2784,7 @@
       <c r="B72" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C72" s="40" t="inlineStr">
+      <c r="C72" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2792,7 +2801,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="40" t="inlineStr">
+      <c r="A73" s="43" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -2800,7 +2809,7 @@
       <c r="B73" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C73" s="40" t="inlineStr">
+      <c r="C73" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2817,7 +2826,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="40" t="inlineStr">
+      <c r="A74" s="43" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -2825,7 +2834,7 @@
       <c r="B74" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C74" s="40" t="inlineStr">
+      <c r="C74" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2842,7 +2851,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="40" t="inlineStr">
+      <c r="A75" s="43" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -2850,7 +2859,7 @@
       <c r="B75" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C75" s="40" t="inlineStr">
+      <c r="C75" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2867,7 +2876,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="40" t="inlineStr">
+      <c r="A76" s="43" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -2875,7 +2884,7 @@
       <c r="B76" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C76" s="40" t="inlineStr">
+      <c r="C76" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2892,7 +2901,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="40" t="inlineStr">
+      <c r="A77" s="43" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -2900,7 +2909,7 @@
       <c r="B77" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C77" s="40" t="inlineStr">
+      <c r="C77" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2917,7 +2926,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="40" t="inlineStr">
+      <c r="A78" s="43" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -2925,7 +2934,7 @@
       <c r="B78" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C78" s="40" t="inlineStr">
+      <c r="C78" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2942,7 +2951,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="40" t="inlineStr">
+      <c r="A79" s="43" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -2950,7 +2959,7 @@
       <c r="B79" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C79" s="40" t="inlineStr">
+      <c r="C79" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2967,7 +2976,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="40" t="inlineStr">
+      <c r="A80" s="43" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -2975,7 +2984,7 @@
       <c r="B80" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C80" s="40" t="inlineStr">
+      <c r="C80" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2992,7 +3001,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="40" t="inlineStr">
+      <c r="A81" s="43" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -3000,7 +3009,7 @@
       <c r="B81" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C81" s="40" t="inlineStr">
+      <c r="C81" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3017,7 +3026,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="40" t="inlineStr">
+      <c r="A82" s="43" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -3025,7 +3034,7 @@
       <c r="B82" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C82" s="40" t="inlineStr">
+      <c r="C82" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3042,7 +3051,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="40" t="inlineStr">
+      <c r="A83" s="43" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -3050,7 +3059,7 @@
       <c r="B83" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C83" s="40" t="inlineStr">
+      <c r="C83" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3067,7 +3076,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="40" t="inlineStr">
+      <c r="A84" s="43" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -3075,7 +3084,7 @@
       <c r="B84" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C84" s="40" t="inlineStr">
+      <c r="C84" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3092,7 +3101,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="40" t="inlineStr">
+      <c r="A85" s="43" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -3100,7 +3109,7 @@
       <c r="B85" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C85" s="40" t="inlineStr">
+      <c r="C85" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3117,7 +3126,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="40" t="inlineStr">
+      <c r="A86" s="43" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -3125,7 +3134,7 @@
       <c r="B86" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C86" s="40" t="inlineStr">
+      <c r="C86" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3142,7 +3151,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="40" t="inlineStr">
+      <c r="A87" s="43" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -3150,7 +3159,7 @@
       <c r="B87" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C87" s="40" t="inlineStr">
+      <c r="C87" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3167,7 +3176,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="40" t="inlineStr">
+      <c r="A88" s="43" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -3175,7 +3184,7 @@
       <c r="B88" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C88" s="40" t="inlineStr">
+      <c r="C88" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3192,7 +3201,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="40" t="inlineStr">
+      <c r="A89" s="43" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -3200,7 +3209,7 @@
       <c r="B89" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C89" s="40" t="inlineStr">
+      <c r="C89" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3217,7 +3226,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="40" t="inlineStr">
+      <c r="A90" s="43" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -3225,7 +3234,7 @@
       <c r="B90" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C90" s="40" t="inlineStr">
+      <c r="C90" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3242,7 +3251,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="40" t="inlineStr">
+      <c r="A91" s="43" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -3250,7 +3259,7 @@
       <c r="B91" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C91" s="40" t="inlineStr">
+      <c r="C91" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3267,7 +3276,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="40" t="inlineStr">
+      <c r="A92" s="43" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -3275,7 +3284,7 @@
       <c r="B92" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C92" s="40" t="inlineStr">
+      <c r="C92" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3292,7 +3301,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="40" t="inlineStr">
+      <c r="A93" s="43" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -3300,7 +3309,7 @@
       <c r="B93" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C93" s="40" t="inlineStr">
+      <c r="C93" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3317,7 +3326,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="40" t="inlineStr">
+      <c r="A94" s="43" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -3325,7 +3334,7 @@
       <c r="B94" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C94" s="40" t="inlineStr">
+      <c r="C94" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3342,7 +3351,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="40" t="inlineStr">
+      <c r="A95" s="43" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -3350,7 +3359,7 @@
       <c r="B95" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C95" s="40" t="inlineStr">
+      <c r="C95" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3367,7 +3376,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="40" t="inlineStr">
+      <c r="A96" s="43" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -3375,7 +3384,7 @@
       <c r="B96" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C96" s="40" t="inlineStr">
+      <c r="C96" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3392,7 +3401,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="40" t="inlineStr">
+      <c r="A97" s="43" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -3400,7 +3409,7 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="40" t="inlineStr">
+      <c r="C97" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3417,7 +3426,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="40" t="inlineStr">
+      <c r="A98" s="43" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -3425,7 +3434,7 @@
       <c r="B98" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C98" s="40" t="inlineStr">
+      <c r="C98" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3442,7 +3451,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="40" t="inlineStr">
+      <c r="A99" s="43" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -3450,7 +3459,7 @@
       <c r="B99" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C99" s="40" t="inlineStr">
+      <c r="C99" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3467,7 +3476,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="40" t="inlineStr">
+      <c r="A100" s="43" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -3475,7 +3484,7 @@
       <c r="B100" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C100" s="40" t="inlineStr">
+      <c r="C100" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3492,7 +3501,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="40" t="inlineStr">
+      <c r="A101" s="43" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -3500,7 +3509,7 @@
       <c r="B101" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C101" s="40" t="inlineStr">
+      <c r="C101" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3517,7 +3526,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="40" t="inlineStr">
+      <c r="A102" s="43" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -3525,7 +3534,7 @@
       <c r="B102" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C102" s="40" t="inlineStr">
+      <c r="C102" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3542,7 +3551,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="40" t="inlineStr">
+      <c r="A103" s="43" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -3550,7 +3559,7 @@
       <c r="B103" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C103" s="40" t="inlineStr">
+      <c r="C103" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3567,7 +3576,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="40" t="inlineStr">
+      <c r="A104" s="43" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -3575,7 +3584,7 @@
       <c r="B104" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C104" s="40" t="inlineStr">
+      <c r="C104" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3592,7 +3601,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="40" t="inlineStr">
+      <c r="A105" s="43" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -3600,7 +3609,7 @@
       <c r="B105" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C105" s="40" t="inlineStr">
+      <c r="C105" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3617,7 +3626,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="40" t="inlineStr">
+      <c r="A106" s="43" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -3625,7 +3634,7 @@
       <c r="B106" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C106" s="40" t="inlineStr">
+      <c r="C106" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3642,7 +3651,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="40" t="inlineStr">
+      <c r="A107" s="43" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -3650,7 +3659,7 @@
       <c r="B107" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C107" s="40" t="inlineStr">
+      <c r="C107" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3667,7 +3676,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="40" t="inlineStr">
+      <c r="A108" s="43" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -3675,7 +3684,7 @@
       <c r="B108" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C108" s="40" t="inlineStr">
+      <c r="C108" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3692,7 +3701,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="40" t="inlineStr">
+      <c r="A109" s="43" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -3700,7 +3709,7 @@
       <c r="B109" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C109" s="40" t="inlineStr">
+      <c r="C109" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3717,7 +3726,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="40" t="inlineStr">
+      <c r="A110" s="43" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -3725,7 +3734,7 @@
       <c r="B110" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C110" s="40" t="inlineStr">
+      <c r="C110" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3742,7 +3751,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="40" t="inlineStr">
+      <c r="A111" s="43" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -3750,7 +3759,7 @@
       <c r="B111" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C111" s="40" t="inlineStr">
+      <c r="C111" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3767,7 +3776,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="40" t="inlineStr">
+      <c r="A112" s="43" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -3775,7 +3784,7 @@
       <c r="B112" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C112" s="40" t="inlineStr">
+      <c r="C112" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3792,7 +3801,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="40" t="inlineStr">
+      <c r="A113" s="43" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -3800,7 +3809,7 @@
       <c r="B113" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C113" s="40" t="inlineStr">
+      <c r="C113" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3817,7 +3826,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="40" t="inlineStr">
+      <c r="A114" s="43" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -3825,7 +3834,7 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="40" t="inlineStr">
+      <c r="C114" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3842,7 +3851,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="40" t="inlineStr">
+      <c r="A115" s="43" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -3850,7 +3859,7 @@
       <c r="B115" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C115" s="40" t="inlineStr">
+      <c r="C115" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3867,7 +3876,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="40" t="inlineStr">
+      <c r="A116" s="43" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -3875,7 +3884,7 @@
       <c r="B116" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C116" s="40" t="inlineStr">
+      <c r="C116" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3892,7 +3901,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="40" t="inlineStr">
+      <c r="A117" s="43" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -3900,7 +3909,7 @@
       <c r="B117" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C117" s="40" t="inlineStr">
+      <c r="C117" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3917,7 +3926,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="40" t="inlineStr">
+      <c r="A118" s="43" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -3925,7 +3934,7 @@
       <c r="B118" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C118" s="40" t="inlineStr">
+      <c r="C118" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3942,7 +3951,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="40" t="inlineStr">
+      <c r="A119" s="43" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -3950,7 +3959,7 @@
       <c r="B119" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C119" s="40" t="inlineStr">
+      <c r="C119" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3967,7 +3976,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="40" t="inlineStr">
+      <c r="A120" s="43" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -3975,7 +3984,7 @@
       <c r="B120" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C120" s="40" t="inlineStr">
+      <c r="C120" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3992,7 +4001,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="40" t="inlineStr">
+      <c r="A121" s="43" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -4000,7 +4009,7 @@
       <c r="B121" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C121" s="40" t="inlineStr">
+      <c r="C121" s="43" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -4017,7 +4026,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="40" t="inlineStr">
+      <c r="A122" s="43" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -4025,7 +4034,7 @@
       <c r="B122" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C122" s="40" t="inlineStr">
+      <c r="C122" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4042,7 +4051,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="40" t="inlineStr">
+      <c r="A123" s="43" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -4050,7 +4059,7 @@
       <c r="B123" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C123" s="40" t="inlineStr">
+      <c r="C123" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4067,7 +4076,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="40" t="inlineStr">
+      <c r="A124" s="43" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -4075,7 +4084,7 @@
       <c r="B124" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C124" s="40" t="inlineStr">
+      <c r="C124" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4092,7 +4101,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="40" t="inlineStr">
+      <c r="A125" s="43" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -4100,7 +4109,7 @@
       <c r="B125" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C125" s="40" t="inlineStr">
+      <c r="C125" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4117,7 +4126,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="40" t="inlineStr">
+      <c r="A126" s="43" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -4125,7 +4134,7 @@
       <c r="B126" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C126" s="40" t="inlineStr">
+      <c r="C126" s="43" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4142,7 +4151,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="41" t="inlineStr">
+      <c r="A127" s="44" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4150,7 +4159,7 @@
       <c r="B127" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C127" s="41" t="inlineStr"/>
+      <c r="C127" s="44" t="inlineStr"/>
       <c r="D127" s="16" t="inlineStr"/>
       <c r="E127" s="16" t="inlineStr"/>
     </row>
@@ -4211,7 +4220,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -4227,7 +4236,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Налоги с ФОТ</t>
         </is>
@@ -4243,7 +4252,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -4259,7 +4268,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>Расходы по кассе</t>
         </is>
@@ -4275,7 +4284,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Услуги банка (общие)</t>
         </is>
@@ -4291,7 +4300,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Эквайринг (персонально)</t>
         </is>
@@ -4307,7 +4316,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -4323,7 +4332,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>% по кредиту</t>
         </is>
@@ -4332,14 +4341,14 @@
         <v>151764.47</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0</v>
+        <v>204388.93</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>-151764.47</v>
+        <v>52624.46</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Поставщики (счёт 60)</t>
         </is>
@@ -4355,7 +4364,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
@@ -4364,14 +4373,14 @@
         <v>72553130.98</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>88974077.06999999</v>
+        <v>89178466</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>16420946.09</v>
+        <v>16625335.02</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>ДОХОД (выручка − расходы)</t>
         </is>
@@ -4380,10 +4389,10 @@
         <v>35573284.74</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>7977776.92</v>
+        <v>7773387.99</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>-27595507.82</v>
+        <v>-27799896.75</v>
       </c>
     </row>
     <row r="17">
@@ -4416,7 +4425,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -4432,7 +4441,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр.1</t>
         </is>
@@ -4448,7 +4457,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
@@ -4464,7 +4473,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>Досудебный спор</t>
         </is>
@@ -4480,7 +4489,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>Прочие поставщики</t>
         </is>
@@ -4496,7 +4505,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4564,7 +4573,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>01–10.08, старая управленка</t>
         </is>
@@ -4572,14 +4581,14 @@
       <c r="B5" s="6" t="n">
         <v>31613514</v>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>реестр «Оплаты от пациента» без двух документов, помеченных на удаление; сходится с «Ежедневным отчётом по кассам»</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>11–31.08, новая управленка</t>
         </is>
@@ -4587,14 +4596,14 @@
       <c r="B6" s="6" t="n">
         <v>66058340</v>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными», уже за вычетом возвратов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Возвраты пациентам, 01–10.08</t>
         </is>
@@ -4602,14 +4611,14 @@
       <c r="B7" s="6" t="n">
         <v>-720000</v>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>колонка «Возврат денег» «Ежедневного отчёта по кассам»</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
@@ -4617,19 +4626,19 @@
       <c r="B8" s="9" t="n">
         <v>96951854</v>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>деньги, поступившие за месяц</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr"/>
+      <c r="A9" s="43" t="inlineStr"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="40" t="inlineStr"/>
+      <c r="C9" s="43" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>01–10.08: платежи с указанным специалистом</t>
         </is>
@@ -4637,14 +4646,14 @@
       <c r="B10" s="6" t="n">
         <v>30904014</v>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>колонка «Специалист» реестра платежей</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>01–10.08: без специалиста</t>
         </is>
@@ -4652,14 +4661,14 @@
       <c r="B11" s="6" t="n">
         <v>709500</v>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>разнесены по врачам того же пациента, остаток — пропорционально</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>11–31.08: привязано к врачу напрямую</t>
         </is>
@@ -4667,14 +4676,14 @@
       <c r="B12" s="6" t="n">
         <v>46401840</v>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>документы «Оказание услуг» — врач указан в документе</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>11–31.08: авансы, разнесённые через пациента</t>
         </is>
@@ -4682,14 +4691,14 @@
       <c r="B13" s="6" t="n">
         <v>14588000</v>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>оплата картой и кассовые ордера</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>11–31.08: авансы без совпадения по пациенту</t>
         </is>
@@ -4697,7 +4706,7 @@
       <c r="B14" s="6" t="n">
         <v>5068500</v>
       </c>
-      <c r="C14" s="40" t="inlineStr">
+      <c r="C14" s="43" t="inlineStr">
         <is>
           <t>разнесены пропорционально; пациентов нет в реестре услуг августа</t>
         </is>
@@ -4731,7 +4740,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -4750,7 +4759,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -4769,7 +4778,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
@@ -4788,7 +4797,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -4807,7 +4816,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -4826,7 +4835,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="41" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4906,12 +4915,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Выручка за месяц</t>
         </is>
@@ -4936,12 +4945,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Доход учредителей за месяц</t>
         </is>
@@ -4966,12 +4975,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
@@ -4996,12 +5005,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Рост выручки с начала года</t>
         </is>
@@ -5024,12 +5033,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Выручка месяца, год к году</t>
         </is>
@@ -5052,12 +5061,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Выручка с начала года</t>
         </is>
@@ -5082,12 +5091,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Средняя выручка в день</t>
         </is>
@@ -5112,12 +5121,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Оплаты поставщикам (сч. 60)</t>
         </is>
@@ -5142,12 +5151,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>ФОТ с налогами по банку</t>
         </is>
@@ -5172,12 +5181,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
@@ -5202,12 +5211,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Касса (наличные)</t>
         </is>
@@ -5232,12 +5241,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>Эквайринг (карты)</t>
         </is>
@@ -5262,12 +5271,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Оплаты физлиц на р/с</t>
         </is>
@@ -5292,12 +5301,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
@@ -5322,12 +5331,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Комиссия эквайринга</t>
         </is>
@@ -5352,12 +5361,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>Медицинские расходы + ИП</t>
         </is>
@@ -5382,12 +5391,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -5412,12 +5421,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>в т.ч. гонорары ИП хирургов</t>
         </is>
@@ -5442,12 +5451,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>в т.ч. ремонт нового корпуса</t>
         </is>
@@ -5472,12 +5481,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Экономика</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>Доход месяца (итог водопада)</t>
         </is>
@@ -5502,12 +5511,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>Остаток на начало месяца</t>
         </is>
@@ -5532,12 +5541,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>Поступления за месяц</t>
         </is>
@@ -5562,12 +5571,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Списания за месяц</t>
         </is>
@@ -5592,12 +5601,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>Остаток на конец месяца</t>
         </is>
@@ -5622,12 +5631,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>Маланичев: личная выручка</t>
         </is>
@@ -5652,12 +5661,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Маланичев: ½ выручки других хирургов</t>
         </is>
@@ -5682,12 +5691,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>Маланичев: ½ косметологии и прочего</t>
         </is>
@@ -5712,12 +5721,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>Маланичев: доля расходов</t>
         </is>
@@ -5742,12 +5751,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B32" s="37" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>Маланичев: доход за месяц</t>
         </is>
@@ -5772,12 +5781,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>Маланичев: остаток с прошлого месяца</t>
         </is>
@@ -5802,12 +5811,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>Маланичев: удержано в резерв (аренда)</t>
         </is>
@@ -5832,12 +5841,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>Маланичев: к выплате на конец месяца</t>
         </is>
@@ -5862,12 +5871,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B36" s="37" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Погосян: личная выручка</t>
         </is>
@@ -5892,12 +5901,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>Погосян: ½ выручки других хирургов</t>
         </is>
@@ -5922,12 +5931,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>Погосян: ½ косметологии и прочего</t>
         </is>
@@ -5952,12 +5961,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>Погосян: доля расходов</t>
         </is>
@@ -5982,12 +5991,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>Погосян: доход за месяц</t>
         </is>
@@ -6012,12 +6021,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>Погосян: остаток с прошлого месяца</t>
         </is>
@@ -6042,12 +6051,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="37" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>Погосян: удержано в резерв (аренда)</t>
         </is>
@@ -6072,12 +6081,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>Погосян: к выплате на конец месяца</t>
         </is>
@@ -6102,12 +6111,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>Долг по кредитной линии</t>
         </is>
@@ -6132,12 +6141,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="37" t="inlineStr">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>Остаток наличных в кассе</t>
         </is>
@@ -6160,12 +6169,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="37" t="inlineStr">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B46" s="37" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -6190,12 +6199,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="37" t="inlineStr">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>Зарезервировано на аренду (всего)</t>
         </is>
@@ -6336,7 +6345,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
@@ -6378,7 +6387,7 @@
       <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -6420,7 +6429,7 @@
       <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
@@ -6462,7 +6471,7 @@
       <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
@@ -6504,7 +6513,7 @@
       <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -6546,7 +6555,7 @@
       <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
@@ -6588,7 +6597,7 @@
       <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -6630,7 +6639,7 @@
       <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
@@ -6672,7 +6681,7 @@
       <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
@@ -6714,7 +6723,7 @@
       <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
@@ -6756,7 +6765,7 @@
       <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
@@ -6798,7 +6807,7 @@
       <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -6840,7 +6849,7 @@
       <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
@@ -6882,7 +6891,7 @@
       <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
@@ -6924,7 +6933,7 @@
       <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -6966,7 +6975,7 @@
       <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
@@ -7008,7 +7017,7 @@
       <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
@@ -7050,7 +7059,7 @@
       <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -7092,7 +7101,7 @@
       <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7134,7 +7143,7 @@
       <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -7176,7 +7185,7 @@
       <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
@@ -7218,7 +7227,7 @@
       <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
@@ -7260,7 +7269,7 @@
       <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
@@ -7302,7 +7311,7 @@
       <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -7344,7 +7353,7 @@
       <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -7386,7 +7395,7 @@
       <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
@@ -7428,7 +7437,7 @@
       <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -7470,7 +7479,7 @@
       <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -7512,7 +7521,7 @@
       <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
@@ -7554,7 +7563,7 @@
       <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
@@ -7596,7 +7605,7 @@
       <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -7638,7 +7647,7 @@
       <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="inlineStr">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7764,7 +7773,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -7790,7 +7799,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -7816,7 +7825,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
@@ -7842,7 +7851,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -7868,7 +7877,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -7894,7 +7903,7 @@
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7951,7 +7960,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
@@ -7967,7 +7976,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
@@ -7983,7 +7992,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
@@ -7999,7 +8008,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
@@ -8015,7 +8024,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
@@ -8031,7 +8040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
@@ -8047,7 +8056,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
@@ -8063,7 +8072,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
@@ -8075,7 +8084,7 @@
       <c r="D21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
@@ -8087,7 +8096,7 @@
       <c r="D22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
@@ -8099,7 +8108,7 @@
       <c r="D23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
@@ -8111,7 +8120,7 @@
       <c r="D24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
@@ -8172,12 +8181,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -8190,12 +8199,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
@@ -8208,12 +8217,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -8226,12 +8235,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
@@ -8244,12 +8253,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -8262,12 +8271,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
@@ -8280,12 +8289,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
@@ -8298,12 +8307,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
@@ -8316,12 +8325,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
@@ -8334,12 +8343,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
@@ -8352,12 +8361,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
@@ -8370,12 +8379,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
@@ -8388,12 +8397,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
@@ -8406,12 +8415,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
@@ -8424,12 +8433,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
@@ -8442,12 +8451,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
@@ -8460,12 +8469,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -8478,12 +8487,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
@@ -8496,12 +8505,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
@@ -8514,12 +8523,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
@@ -8532,12 +8541,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -8550,12 +8559,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
@@ -8568,12 +8577,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
@@ -8586,12 +8595,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -8604,12 +8613,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
@@ -8622,12 +8631,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
@@ -8640,12 +8649,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
@@ -8658,12 +8667,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
@@ -8676,12 +8685,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B32" s="37" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
@@ -8694,12 +8703,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -8712,12 +8721,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
@@ -8730,12 +8739,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
@@ -8748,12 +8757,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B36" s="37" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
@@ -8766,12 +8775,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
@@ -8784,12 +8793,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -8802,12 +8811,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
@@ -8820,12 +8829,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
@@ -8838,12 +8847,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
@@ -8856,12 +8865,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="37" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
@@ -8874,12 +8883,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -8892,12 +8901,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
@@ -8910,12 +8919,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="37" t="inlineStr">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
@@ -8928,12 +8937,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="37" t="inlineStr">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B46" s="37" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
@@ -8946,12 +8955,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="37" t="inlineStr">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
@@ -8964,12 +8973,12 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="37" t="inlineStr">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B48" s="37" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
@@ -8982,12 +8991,12 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="37" t="inlineStr">
+      <c r="A49" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
@@ -9000,12 +9009,12 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="37" t="inlineStr">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B50" s="37" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
@@ -9018,12 +9027,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="37" t="inlineStr">
+      <c r="A51" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B51" s="37" t="inlineStr">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
@@ -9036,12 +9045,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="37" t="inlineStr">
+      <c r="A52" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B52" s="37" t="inlineStr">
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
@@ -9054,12 +9063,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="37" t="inlineStr">
+      <c r="A53" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
@@ -9072,12 +9081,12 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="37" t="inlineStr">
+      <c r="A54" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
@@ -9090,12 +9099,12 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="37" t="inlineStr">
+      <c r="A55" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B55" s="37" t="inlineStr">
+      <c r="B55" s="40" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
@@ -9108,12 +9117,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="37" t="inlineStr">
+      <c r="A56" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B56" s="37" t="inlineStr">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
@@ -9126,12 +9135,12 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="37" t="inlineStr">
+      <c r="A57" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B57" s="37" t="inlineStr">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
@@ -9144,12 +9153,12 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="37" t="inlineStr">
+      <c r="A58" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B58" s="37" t="inlineStr">
+      <c r="B58" s="40" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
@@ -9162,12 +9171,12 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="37" t="inlineStr">
+      <c r="A59" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B59" s="37" t="inlineStr">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
@@ -9180,12 +9189,12 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="37" t="inlineStr">
+      <c r="A60" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B60" s="37" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
@@ -9198,12 +9207,12 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="37" t="inlineStr">
+      <c r="A61" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B61" s="37" t="inlineStr">
+      <c r="B61" s="40" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
@@ -9216,12 +9225,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="37" t="inlineStr">
+      <c r="A62" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B62" s="37" t="inlineStr">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
@@ -9234,12 +9243,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="37" t="inlineStr">
+      <c r="A63" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B63" s="37" t="inlineStr">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
@@ -9252,12 +9261,12 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="37" t="inlineStr">
+      <c r="A64" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B64" s="37" t="inlineStr">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
@@ -9270,12 +9279,12 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="37" t="inlineStr">
+      <c r="A65" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B65" s="37" t="inlineStr">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
@@ -9288,12 +9297,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="37" t="inlineStr">
+      <c r="A66" s="40" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B66" s="37" t="inlineStr">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -9306,12 +9315,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="38" t="inlineStr">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B67" s="38" t="inlineStr">
+      <c r="B67" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -9324,12 +9333,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="39" t="inlineStr">
+      <c r="A68" s="42" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B68" s="39" t="inlineStr"/>
+      <c r="B68" s="42" t="inlineStr"/>
       <c r="C68" s="14" t="n">
         <v>69794048.05</v>
       </c>
@@ -9379,7 +9388,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -9387,14 +9396,14 @@
       <c r="B4" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Ремонт Самокатная 1 стр12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -9402,14 +9411,14 @@
       <c r="B5" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -9417,14 +9426,14 @@
       <c r="B6" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -9432,14 +9441,14 @@
       <c r="B7" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -9447,14 +9456,14 @@
       <c r="B8" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -9462,14 +9471,14 @@
       <c r="B9" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -9477,14 +9486,14 @@
       <c r="B10" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -9492,14 +9501,14 @@
       <c r="B11" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -9507,14 +9516,14 @@
       <c r="B12" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -9522,14 +9531,14 @@
       <c r="B13" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -9537,14 +9546,14 @@
       <c r="B14" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -9552,14 +9561,14 @@
       <c r="B15" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -9567,14 +9576,14 @@
       <c r="B16" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -9582,14 +9591,14 @@
       <c r="B17" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -9597,14 +9606,14 @@
       <c r="B18" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -9612,14 +9621,14 @@
       <c r="B19" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -9627,14 +9636,14 @@
       <c r="B20" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -9642,14 +9651,14 @@
       <c r="B21" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -9657,14 +9666,14 @@
       <c r="B22" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C22" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -9672,14 +9681,14 @@
       <c r="B23" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -9687,14 +9696,14 @@
       <c r="B24" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -9702,14 +9711,14 @@
       <c r="B25" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -9717,14 +9726,14 @@
       <c r="B26" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="40" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -9732,14 +9741,14 @@
       <c r="B27" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -9747,14 +9756,14 @@
       <c r="B28" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="40" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -9762,14 +9771,14 @@
       <c r="B29" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -9777,14 +9786,14 @@
       <c r="B30" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="40" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -9792,14 +9801,14 @@
       <c r="B31" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="40" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -9807,14 +9816,14 @@
       <c r="B32" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C32" s="37" t="inlineStr">
+      <c r="C32" s="40" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -9822,14 +9831,14 @@
       <c r="B33" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C33" s="40" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -9837,14 +9846,14 @@
       <c r="B34" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="40" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -9852,14 +9861,14 @@
       <c r="B35" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C35" s="40" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -9867,14 +9876,14 @@
       <c r="B36" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C36" s="37" t="inlineStr">
+      <c r="C36" s="40" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -9882,14 +9891,14 @@
       <c r="B37" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -9897,14 +9906,14 @@
       <c r="B38" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C38" s="40" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -9912,14 +9921,14 @@
       <c r="B39" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -9927,14 +9936,14 @@
       <c r="B40" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="40" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -9942,14 +9951,14 @@
       <c r="B41" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="37" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -9957,14 +9966,14 @@
       <c r="B42" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="40" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -9972,14 +9981,14 @@
       <c r="B43" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -9987,14 +9996,14 @@
       <c r="B44" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="40" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="37" t="inlineStr">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -10002,14 +10011,14 @@
       <c r="B45" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="37" t="inlineStr">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -10017,14 +10026,14 @@
       <c r="B46" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C46" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="37" t="inlineStr">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -10032,14 +10041,14 @@
       <c r="B47" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C47" s="37" t="inlineStr">
+      <c r="C47" s="40" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="37" t="inlineStr">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -10047,14 +10056,14 @@
       <c r="B48" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C48" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="37" t="inlineStr">
+      <c r="A49" s="40" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -10062,14 +10071,14 @@
       <c r="B49" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" s="40" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="37" t="inlineStr">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -10077,14 +10086,14 @@
       <c r="B50" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C50" s="37" t="inlineStr">
+      <c r="C50" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="37" t="inlineStr">
+      <c r="A51" s="40" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -10092,14 +10101,14 @@
       <c r="B51" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C51" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="37" t="inlineStr">
+      <c r="A52" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -10107,14 +10116,14 @@
       <c r="B52" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C52" s="40" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="37" t="inlineStr">
+      <c r="A53" s="40" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -10122,14 +10131,14 @@
       <c r="B53" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="40" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="37" t="inlineStr">
+      <c r="A54" s="40" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -10137,14 +10146,14 @@
       <c r="B54" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="40" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="37" t="inlineStr">
+      <c r="A55" s="40" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -10152,14 +10161,14 @@
       <c r="B55" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C55" s="37" t="inlineStr">
+      <c r="C55" s="40" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="37" t="inlineStr">
+      <c r="A56" s="40" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -10167,14 +10176,14 @@
       <c r="B56" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C56" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="37" t="inlineStr">
+      <c r="A57" s="40" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -10182,14 +10191,14 @@
       <c r="B57" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C57" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="37" t="inlineStr">
+      <c r="A58" s="40" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -10197,14 +10206,14 @@
       <c r="B58" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C58" s="37" t="inlineStr">
+      <c r="C58" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="37" t="inlineStr">
+      <c r="A59" s="40" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -10212,14 +10221,14 @@
       <c r="B59" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C59" s="37" t="inlineStr">
+      <c r="C59" s="40" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="37" t="inlineStr">
+      <c r="A60" s="40" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -10227,14 +10236,14 @@
       <c r="B60" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C60" s="37" t="inlineStr">
+      <c r="C60" s="40" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="37" t="inlineStr">
+      <c r="A61" s="40" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -10242,14 +10251,14 @@
       <c r="B61" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="40" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="37" t="inlineStr">
+      <c r="A62" s="40" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -10257,14 +10266,14 @@
       <c r="B62" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C62" s="40" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="37" t="inlineStr">
+      <c r="A63" s="40" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -10272,14 +10281,14 @@
       <c r="B63" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C63" s="37" t="inlineStr">
+      <c r="C63" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="37" t="inlineStr">
+      <c r="A64" s="40" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -10287,14 +10296,14 @@
       <c r="B64" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C64" s="37" t="inlineStr">
+      <c r="C64" s="40" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="37" t="inlineStr">
+      <c r="A65" s="40" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -10302,14 +10311,14 @@
       <c r="B65" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C65" s="37" t="inlineStr">
+      <c r="C65" s="40" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="37" t="inlineStr">
+      <c r="A66" s="40" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -10317,14 +10326,14 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="37" t="inlineStr">
+      <c r="C66" s="40" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="37" t="inlineStr">
+      <c r="A67" s="40" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -10332,14 +10341,14 @@
       <c r="B67" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C67" s="37" t="inlineStr">
+      <c r="C67" s="40" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="37" t="inlineStr">
+      <c r="A68" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -10347,14 +10356,14 @@
       <c r="B68" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C68" s="37" t="inlineStr">
+      <c r="C68" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="A69" s="40" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -10362,14 +10371,14 @@
       <c r="B69" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C69" s="37" t="inlineStr">
+      <c r="C69" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="37" t="inlineStr">
+      <c r="A70" s="40" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -10377,14 +10386,14 @@
       <c r="B70" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C70" s="37" t="inlineStr">
+      <c r="C70" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="37" t="inlineStr">
+      <c r="A71" s="40" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -10392,14 +10401,14 @@
       <c r="B71" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C71" s="37" t="inlineStr">
+      <c r="C71" s="40" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="37" t="inlineStr">
+      <c r="A72" s="40" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -10407,14 +10416,14 @@
       <c r="B72" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C72" s="37" t="inlineStr">
+      <c r="C72" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="37" t="inlineStr">
+      <c r="A73" s="40" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -10422,14 +10431,14 @@
       <c r="B73" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C73" s="37" t="inlineStr">
+      <c r="C73" s="40" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="37" t="inlineStr">
+      <c r="A74" s="40" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -10437,14 +10446,14 @@
       <c r="B74" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C74" s="37" t="inlineStr">
+      <c r="C74" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="37" t="inlineStr">
+      <c r="A75" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -10452,14 +10461,14 @@
       <c r="B75" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C75" s="37" t="inlineStr">
+      <c r="C75" s="40" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="37" t="inlineStr">
+      <c r="A76" s="40" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -10467,14 +10476,14 @@
       <c r="B76" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C76" s="37" t="inlineStr">
+      <c r="C76" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="37" t="inlineStr">
+      <c r="A77" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -10482,14 +10491,14 @@
       <c r="B77" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C77" s="37" t="inlineStr">
+      <c r="C77" s="40" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="37" t="inlineStr">
+      <c r="A78" s="40" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -10497,14 +10506,14 @@
       <c r="B78" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C78" s="37" t="inlineStr">
+      <c r="C78" s="40" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="37" t="inlineStr">
+      <c r="A79" s="40" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -10512,14 +10521,14 @@
       <c r="B79" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C79" s="37" t="inlineStr">
+      <c r="C79" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="37" t="inlineStr">
+      <c r="A80" s="40" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -10527,14 +10536,14 @@
       <c r="B80" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C80" s="37" t="inlineStr">
+      <c r="C80" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="37" t="inlineStr">
+      <c r="A81" s="40" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -10542,14 +10551,14 @@
       <c r="B81" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C81" s="37" t="inlineStr">
+      <c r="C81" s="40" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="37" t="inlineStr">
+      <c r="A82" s="40" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -10557,14 +10566,14 @@
       <c r="B82" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C82" s="37" t="inlineStr">
+      <c r="C82" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="37" t="inlineStr">
+      <c r="A83" s="40" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -10572,14 +10581,14 @@
       <c r="B83" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C83" s="37" t="inlineStr">
+      <c r="C83" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="37" t="inlineStr">
+      <c r="A84" s="40" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -10587,14 +10596,14 @@
       <c r="B84" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C84" s="37" t="inlineStr">
+      <c r="C84" s="40" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="37" t="inlineStr">
+      <c r="A85" s="40" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -10602,14 +10611,14 @@
       <c r="B85" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C85" s="37" t="inlineStr">
+      <c r="C85" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="37" t="inlineStr">
+      <c r="A86" s="40" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -10617,14 +10626,14 @@
       <c r="B86" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C86" s="37" t="inlineStr">
+      <c r="C86" s="40" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="37" t="inlineStr">
+      <c r="A87" s="40" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -10632,14 +10641,14 @@
       <c r="B87" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C87" s="37" t="inlineStr">
+      <c r="C87" s="40" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="37" t="inlineStr">
+      <c r="A88" s="40" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -10647,14 +10656,14 @@
       <c r="B88" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C88" s="37" t="inlineStr">
+      <c r="C88" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="37" t="inlineStr">
+      <c r="A89" s="40" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -10662,14 +10671,14 @@
       <c r="B89" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C89" s="37" t="inlineStr">
+      <c r="C89" s="40" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="37" t="inlineStr">
+      <c r="A90" s="40" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -10677,14 +10686,14 @@
       <c r="B90" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C90" s="37" t="inlineStr">
+      <c r="C90" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="37" t="inlineStr">
+      <c r="A91" s="40" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -10692,14 +10701,14 @@
       <c r="B91" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C91" s="37" t="inlineStr">
+      <c r="C91" s="40" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="37" t="inlineStr">
+      <c r="A92" s="40" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -10707,14 +10716,14 @@
       <c r="B92" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C92" s="37" t="inlineStr">
+      <c r="C92" s="40" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="37" t="inlineStr">
+      <c r="A93" s="40" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -10722,14 +10731,14 @@
       <c r="B93" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C93" s="37" t="inlineStr">
+      <c r="C93" s="40" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="37" t="inlineStr">
+      <c r="A94" s="40" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -10737,14 +10746,14 @@
       <c r="B94" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C94" s="37" t="inlineStr">
+      <c r="C94" s="40" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="37" t="inlineStr">
+      <c r="A95" s="40" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -10752,14 +10761,14 @@
       <c r="B95" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C95" s="37" t="inlineStr">
+      <c r="C95" s="40" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="37" t="inlineStr">
+      <c r="A96" s="40" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -10767,14 +10776,14 @@
       <c r="B96" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C96" s="37" t="inlineStr">
+      <c r="C96" s="40" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="37" t="inlineStr">
+      <c r="A97" s="40" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -10782,14 +10791,14 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="37" t="inlineStr">
+      <c r="C97" s="40" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="37" t="inlineStr">
+      <c r="A98" s="40" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -10797,14 +10806,14 @@
       <c r="B98" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C98" s="37" t="inlineStr">
+      <c r="C98" s="40" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="37" t="inlineStr">
+      <c r="A99" s="40" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -10812,14 +10821,14 @@
       <c r="B99" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C99" s="37" t="inlineStr">
+      <c r="C99" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="37" t="inlineStr">
+      <c r="A100" s="40" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -10827,14 +10836,14 @@
       <c r="B100" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C100" s="37" t="inlineStr">
+      <c r="C100" s="40" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="37" t="inlineStr">
+      <c r="A101" s="40" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -10842,14 +10851,14 @@
       <c r="B101" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C101" s="37" t="inlineStr">
+      <c r="C101" s="40" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="37" t="inlineStr">
+      <c r="A102" s="40" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -10857,14 +10866,14 @@
       <c r="B102" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C102" s="37" t="inlineStr">
+      <c r="C102" s="40" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="37" t="inlineStr">
+      <c r="A103" s="40" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -10872,14 +10881,14 @@
       <c r="B103" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C103" s="37" t="inlineStr">
+      <c r="C103" s="40" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="37" t="inlineStr">
+      <c r="A104" s="40" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -10887,14 +10896,14 @@
       <c r="B104" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C104" s="37" t="inlineStr">
+      <c r="C104" s="40" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="37" t="inlineStr">
+      <c r="A105" s="40" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -10902,14 +10911,14 @@
       <c r="B105" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C105" s="37" t="inlineStr">
+      <c r="C105" s="40" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="37" t="inlineStr">
+      <c r="A106" s="40" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -10917,14 +10926,14 @@
       <c r="B106" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C106" s="37" t="inlineStr">
+      <c r="C106" s="40" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="37" t="inlineStr">
+      <c r="A107" s="40" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -10932,14 +10941,14 @@
       <c r="B107" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C107" s="37" t="inlineStr">
+      <c r="C107" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="37" t="inlineStr">
+      <c r="A108" s="40" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -10947,14 +10956,14 @@
       <c r="B108" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C108" s="37" t="inlineStr">
+      <c r="C108" s="40" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="37" t="inlineStr">
+      <c r="A109" s="40" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -10962,14 +10971,14 @@
       <c r="B109" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C109" s="37" t="inlineStr">
+      <c r="C109" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="37" t="inlineStr">
+      <c r="A110" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -10977,14 +10986,14 @@
       <c r="B110" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C110" s="37" t="inlineStr">
+      <c r="C110" s="40" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="37" t="inlineStr">
+      <c r="A111" s="40" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -10992,14 +11001,14 @@
       <c r="B111" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C111" s="37" t="inlineStr">
+      <c r="C111" s="40" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="37" t="inlineStr">
+      <c r="A112" s="40" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -11007,14 +11016,14 @@
       <c r="B112" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C112" s="37" t="inlineStr">
+      <c r="C112" s="40" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="37" t="inlineStr">
+      <c r="A113" s="40" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -11022,14 +11031,14 @@
       <c r="B113" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C113" s="37" t="inlineStr">
+      <c r="C113" s="40" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="37" t="inlineStr">
+      <c r="A114" s="40" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -11037,14 +11046,14 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="37" t="inlineStr">
+      <c r="C114" s="40" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="37" t="inlineStr">
+      <c r="A115" s="40" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -11052,14 +11061,14 @@
       <c r="B115" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C115" s="37" t="inlineStr">
+      <c r="C115" s="40" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="37" t="inlineStr">
+      <c r="A116" s="40" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -11067,14 +11076,14 @@
       <c r="B116" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C116" s="37" t="inlineStr">
+      <c r="C116" s="40" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="37" t="inlineStr">
+      <c r="A117" s="40" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -11082,14 +11091,14 @@
       <c r="B117" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C117" s="37" t="inlineStr">
+      <c r="C117" s="40" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="37" t="inlineStr">
+      <c r="A118" s="40" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -11097,14 +11106,14 @@
       <c r="B118" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C118" s="37" t="inlineStr">
+      <c r="C118" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="37" t="inlineStr">
+      <c r="A119" s="40" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -11112,14 +11121,14 @@
       <c r="B119" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C119" s="37" t="inlineStr">
+      <c r="C119" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="37" t="inlineStr">
+      <c r="A120" s="40" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -11127,14 +11136,14 @@
       <c r="B120" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C120" s="37" t="inlineStr">
+      <c r="C120" s="40" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="37" t="inlineStr">
+      <c r="A121" s="40" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -11142,14 +11151,14 @@
       <c r="B121" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C121" s="37" t="inlineStr">
+      <c r="C121" s="40" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="37" t="inlineStr">
+      <c r="A122" s="40" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -11157,14 +11166,14 @@
       <c r="B122" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C122" s="37" t="inlineStr">
+      <c r="C122" s="40" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="37" t="inlineStr">
+      <c r="A123" s="40" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -11172,14 +11181,14 @@
       <c r="B123" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C123" s="37" t="inlineStr">
+      <c r="C123" s="40" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="37" t="inlineStr">
+      <c r="A124" s="40" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -11187,14 +11196,14 @@
       <c r="B124" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C124" s="37" t="inlineStr">
+      <c r="C124" s="40" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="37" t="inlineStr">
+      <c r="A125" s="40" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -11202,14 +11211,14 @@
       <c r="B125" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C125" s="37" t="inlineStr">
+      <c r="C125" s="40" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="38" t="inlineStr">
+      <c r="A126" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -11217,7 +11226,7 @@
       <c r="B126" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C126" s="38" t="inlineStr"/>
+      <c r="C126" s="41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11269,7 +11278,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Начальное сальдо</t>
         </is>
@@ -11281,7 +11290,7 @@
       <c r="D4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Возврат средств с депозитов</t>
         </is>
@@ -11297,7 +11306,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Инкассация и эквайринг</t>
         </is>
@@ -11313,7 +11322,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Возвраты от поставщиков</t>
         </is>
@@ -11329,7 +11338,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Кредит банка</t>
         </is>
@@ -11345,7 +11354,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
@@ -11361,7 +11370,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -11377,7 +11386,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Размещение на депозиты</t>
         </is>
@@ -11393,7 +11402,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Переводы между счетами</t>
         </is>
@@ -11409,7 +11418,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Оплаты поставщикам и подрядчикам</t>
         </is>
@@ -11425,7 +11434,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
@@ -11441,7 +11450,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
@@ -11457,7 +11466,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Страховые взносы</t>
         </is>
@@ -11473,7 +11482,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -11489,7 +11498,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Выплата дивидендов</t>
         </is>
@@ -11505,7 +11514,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -11521,7 +11530,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -11537,7 +11546,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Оборот за месяц</t>
         </is>
@@ -11551,7 +11560,7 @@
       <c r="D21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>Конечное сальдо</t>
         </is>
@@ -11635,12 +11644,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Личная выручка (свои операции)</t>
         </is>
@@ -11661,12 +11670,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>+ ½ выручки других хирургов</t>
         </is>
@@ -11687,12 +11696,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>+ ½ косметологии</t>
         </is>
@@ -11713,12 +11722,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>+ ½ прочих доходов</t>
         </is>
@@ -11739,12 +11748,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>+ ½ процентов по депозитам</t>
         </is>
@@ -11791,8 +11800,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr"/>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr"/>
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      налоги с ФОТ (68.90 + 69)</t>
         </is>
@@ -11809,8 +11818,8 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr"/>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr"/>
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      зарплата по банку</t>
         </is>
@@ -11827,8 +11836,8 @@
       <c r="F12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr"/>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr"/>
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      расходы по кассе</t>
         </is>
@@ -11845,8 +11854,8 @@
       <c r="F13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr"/>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr"/>
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      услуги банка (общие)</t>
         </is>
@@ -11863,8 +11872,8 @@
       <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr"/>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr"/>
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      услуги банка (эквайринг, персонально)</t>
         </is>
@@ -11881,8 +11890,8 @@
       <c r="F15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr"/>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr"/>
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      алименты (удержание из ЗП)</t>
         </is>
@@ -11899,8 +11908,8 @@
       <c r="F16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr"/>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr"/>
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      дополнительные корректировки</t>
         </is>
@@ -11917,8 +11926,8 @@
       <c r="F17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="inlineStr"/>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr"/>
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">      поставщики (счёт 60) + Халва</t>
         </is>
@@ -11935,12 +11944,12 @@
       <c r="F18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
@@ -11961,12 +11970,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>+ Остаток с прошлого месяца</t>
         </is>
@@ -11987,12 +11996,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>− Выплачены дивиденды</t>
         </is>
@@ -12013,12 +12022,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
@@ -12101,10 +12110,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="n">
+      <c r="A5" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -12120,10 +12129,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="n">
+      <c r="A6" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -12139,10 +12148,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Медицинские расходы</t>
         </is>
@@ -12158,10 +12167,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>ФОТ, налоги, алименты</t>
         </is>
@@ -12177,10 +12186,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -12196,10 +12205,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Ремонт нового корпуса</t>
         </is>
@@ -12215,10 +12224,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -12234,10 +12243,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -12253,10 +12262,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Доход месяца</t>
         </is>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,69 +175,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -647,108 +584,108 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>01 Цифры отчёта</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Каждая цифра из HTML-отчёта: значение, формула, источник. Главный лист расшифровки.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>02 Выручка по дням</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Дневная выручка по группам врачей и каналам оплаты + сверка с онлайн-кассой.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>03 Выручка структура</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Итоги по группам врачей и каналам поступления, доли в выручке, комиссия эквайринга.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>04 Расходы категории</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Счёт 60 в разрезе статей: медицинские + ИП и управленческие.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>05 Расходы контрагенты</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Счёт 60 построчно по контрагентам с назначением платежа.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>06 ДДС сч.51</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Обороты расчётного счёта: поступления и списания по корреспондирующим счетам.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>07 Учредители</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Методика 50/50 по шагам: выручка, доли расходов, доход, остаток, резерв, к выплате.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>08 Водопад</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>От выручки к доходу месяца — те же шаги, что на графике «Куда уходит выручка».</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>09 Контроль</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Контрольные равенства: сходится ли отчёт сам с собой и с данными бухгалтерии.</t>
         </is>
@@ -851,16 +788,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Сумма выручки по группам = итог выручки</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -873,19 +810,19 @@
       <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Касса + эквайринг + р/с физлиц − возвраты = итог выручки</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>97707434</v>
+        <v>96951854</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
@@ -895,16 +832,16 @@
       <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Сумма шагов водопада = доход месяца</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9129603.779999999</v>
+        <v>8169725.23</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9129603.800000001</v>
+        <v>8169725.25</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>-0.02</v>
@@ -921,16 +858,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Доход Маланичева + Погосяна = доход компании</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>9129603.800000001</v>
+        <v>8169725.25</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>9129603.800000001</v>
+        <v>8169725.25</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -943,7 +880,7 @@
       <c r="F8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Расходы 60: медицинские + управленческие = итог по счёту</t>
         </is>
@@ -965,7 +902,7 @@
       <c r="F9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Расходы 60: сумма по контрагентам = итог по счёту</t>
         </is>
@@ -991,16 +928,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ДДС: сальдо нач. + приход − расход = сальдо кон.</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>19042449.94</v>
+        <v>19035318.76</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>19042449.94</v>
+        <v>19035318.76</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -1013,16 +950,16 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Выручка (отчёт) vs выручка кассовым методом (график динамики)</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -1101,7 +1038,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -1109,7 +1046,7 @@
       <c r="B5" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1126,7 +1063,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -1134,7 +1071,7 @@
       <c r="B6" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1151,7 +1088,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -1159,7 +1096,7 @@
       <c r="B7" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1176,7 +1113,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -1184,7 +1121,7 @@
       <c r="B8" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1201,7 +1138,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -1209,7 +1146,7 @@
       <c r="B9" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1226,7 +1163,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -1234,7 +1171,7 @@
       <c r="B10" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1251,7 +1188,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -1259,7 +1196,7 @@
       <c r="B11" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1276,7 +1213,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -1284,7 +1221,7 @@
       <c r="B12" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1301,7 +1238,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -1309,7 +1246,7 @@
       <c r="B13" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1326,7 +1263,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -1334,7 +1271,7 @@
       <c r="B14" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1351,7 +1288,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -1359,7 +1296,7 @@
       <c r="B15" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1376,7 +1313,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -1384,7 +1321,7 @@
       <c r="B16" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1401,7 +1338,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -1409,7 +1346,7 @@
       <c r="B17" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1426,7 +1363,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -1434,7 +1371,7 @@
       <c r="B18" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1451,7 +1388,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -1459,7 +1396,7 @@
       <c r="B19" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1476,7 +1413,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -1484,7 +1421,7 @@
       <c r="B20" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1501,7 +1438,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -1509,7 +1446,7 @@
       <c r="B21" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1526,7 +1463,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -1534,7 +1471,7 @@
       <c r="B22" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1551,7 +1488,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -1559,7 +1496,7 @@
       <c r="B23" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1576,7 +1513,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -1584,7 +1521,7 @@
       <c r="B24" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1601,7 +1538,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -1609,7 +1546,7 @@
       <c r="B25" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1626,7 +1563,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -1634,7 +1571,7 @@
       <c r="B26" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1651,7 +1588,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -1659,7 +1596,7 @@
       <c r="B27" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1676,7 +1613,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -1684,7 +1621,7 @@
       <c r="B28" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1701,7 +1638,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -1709,7 +1646,7 @@
       <c r="B29" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1726,7 +1663,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -1734,7 +1671,7 @@
       <c r="B30" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1751,7 +1688,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -1759,7 +1696,7 @@
       <c r="B31" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1776,7 +1713,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -1784,7 +1721,7 @@
       <c r="B32" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1801,7 +1738,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -1809,7 +1746,7 @@
       <c r="B33" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1826,7 +1763,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -1834,7 +1771,7 @@
       <c r="B34" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1851,7 +1788,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -1859,7 +1796,7 @@
       <c r="B35" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1876,7 +1813,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -1884,7 +1821,7 @@
       <c r="B36" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1901,7 +1838,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="43" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -1909,7 +1846,7 @@
       <c r="B37" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1926,7 +1863,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -1934,7 +1871,7 @@
       <c r="B38" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C38" s="43" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1951,7 +1888,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -1959,7 +1896,7 @@
       <c r="B39" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1976,7 +1913,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -1984,7 +1921,7 @@
       <c r="B40" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C40" s="43" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2001,7 +1938,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="43" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -2009,7 +1946,7 @@
       <c r="B41" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C41" s="43" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2026,7 +1963,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="43" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -2034,7 +1971,7 @@
       <c r="B42" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C42" s="43" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2051,7 +1988,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="43" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -2059,7 +1996,7 @@
       <c r="B43" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C43" s="43" t="inlineStr">
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2076,7 +2013,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -2084,7 +2021,7 @@
       <c r="B44" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C44" s="43" t="inlineStr">
+      <c r="C44" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2101,7 +2038,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="43" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -2109,7 +2046,7 @@
       <c r="B45" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C45" s="43" t="inlineStr">
+      <c r="C45" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2126,7 +2063,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -2134,7 +2071,7 @@
       <c r="B46" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C46" s="43" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2151,7 +2088,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -2159,7 +2096,7 @@
       <c r="B47" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2176,7 +2113,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -2184,7 +2121,7 @@
       <c r="B48" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C48" s="43" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2201,7 +2138,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -2209,7 +2146,7 @@
       <c r="B49" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2226,7 +2163,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="43" t="inlineStr">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -2234,7 +2171,7 @@
       <c r="B50" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C50" s="43" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2251,7 +2188,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="43" t="inlineStr">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -2259,7 +2196,7 @@
       <c r="B51" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C51" s="43" t="inlineStr">
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2276,7 +2213,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="43" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -2284,7 +2221,7 @@
       <c r="B52" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C52" s="43" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2301,7 +2238,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="43" t="inlineStr">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -2309,7 +2246,7 @@
       <c r="B53" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2326,7 +2263,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="43" t="inlineStr">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -2334,7 +2271,7 @@
       <c r="B54" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2351,7 +2288,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="43" t="inlineStr">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -2359,7 +2296,7 @@
       <c r="B55" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2376,7 +2313,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="43" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -2384,7 +2321,7 @@
       <c r="B56" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C56" s="43" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2401,7 +2338,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="43" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -2409,7 +2346,7 @@
       <c r="B57" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C57" s="43" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2426,7 +2363,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="43" t="inlineStr">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -2434,7 +2371,7 @@
       <c r="B58" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C58" s="43" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2451,7 +2388,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="43" t="inlineStr">
+      <c r="A59" s="22" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -2459,7 +2396,7 @@
       <c r="B59" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C59" s="43" t="inlineStr">
+      <c r="C59" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2476,7 +2413,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="43" t="inlineStr">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -2484,7 +2421,7 @@
       <c r="B60" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C60" s="43" t="inlineStr">
+      <c r="C60" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2501,7 +2438,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -2509,7 +2446,7 @@
       <c r="B61" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C61" s="43" t="inlineStr">
+      <c r="C61" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2526,7 +2463,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="43" t="inlineStr">
+      <c r="A62" s="22" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -2534,7 +2471,7 @@
       <c r="B62" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C62" s="43" t="inlineStr">
+      <c r="C62" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2551,7 +2488,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="43" t="inlineStr">
+      <c r="A63" s="22" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -2559,7 +2496,7 @@
       <c r="B63" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C63" s="43" t="inlineStr">
+      <c r="C63" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2576,7 +2513,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="43" t="inlineStr">
+      <c r="A64" s="22" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -2584,7 +2521,7 @@
       <c r="B64" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C64" s="43" t="inlineStr">
+      <c r="C64" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2601,7 +2538,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="43" t="inlineStr">
+      <c r="A65" s="22" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -2609,7 +2546,7 @@
       <c r="B65" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C65" s="43" t="inlineStr">
+      <c r="C65" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2626,7 +2563,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="43" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -2634,7 +2571,7 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="43" t="inlineStr">
+      <c r="C66" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2651,7 +2588,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="43" t="inlineStr">
+      <c r="A67" s="22" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -2659,7 +2596,7 @@
       <c r="B67" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C67" s="43" t="inlineStr">
+      <c r="C67" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2676,7 +2613,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="43" t="inlineStr">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -2684,7 +2621,7 @@
       <c r="B68" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C68" s="43" t="inlineStr">
+      <c r="C68" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2701,7 +2638,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="43" t="inlineStr">
+      <c r="A69" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -2709,7 +2646,7 @@
       <c r="B69" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C69" s="43" t="inlineStr">
+      <c r="C69" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2726,7 +2663,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="43" t="inlineStr">
+      <c r="A70" s="22" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -2734,7 +2671,7 @@
       <c r="B70" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C70" s="43" t="inlineStr">
+      <c r="C70" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2751,7 +2688,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="43" t="inlineStr">
+      <c r="A71" s="22" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -2759,7 +2696,7 @@
       <c r="B71" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C71" s="43" t="inlineStr">
+      <c r="C71" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2776,7 +2713,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="43" t="inlineStr">
+      <c r="A72" s="22" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -2784,7 +2721,7 @@
       <c r="B72" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C72" s="43" t="inlineStr">
+      <c r="C72" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2801,7 +2738,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="43" t="inlineStr">
+      <c r="A73" s="22" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -2809,7 +2746,7 @@
       <c r="B73" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C73" s="43" t="inlineStr">
+      <c r="C73" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2826,7 +2763,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="43" t="inlineStr">
+      <c r="A74" s="22" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -2834,7 +2771,7 @@
       <c r="B74" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C74" s="43" t="inlineStr">
+      <c r="C74" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2851,7 +2788,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="43" t="inlineStr">
+      <c r="A75" s="22" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -2859,7 +2796,7 @@
       <c r="B75" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C75" s="43" t="inlineStr">
+      <c r="C75" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2876,7 +2813,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="43" t="inlineStr">
+      <c r="A76" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -2884,7 +2821,7 @@
       <c r="B76" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C76" s="43" t="inlineStr">
+      <c r="C76" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2901,7 +2838,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="43" t="inlineStr">
+      <c r="A77" s="22" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -2909,7 +2846,7 @@
       <c r="B77" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C77" s="43" t="inlineStr">
+      <c r="C77" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2926,7 +2863,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="43" t="inlineStr">
+      <c r="A78" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -2934,7 +2871,7 @@
       <c r="B78" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C78" s="43" t="inlineStr">
+      <c r="C78" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2951,7 +2888,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="43" t="inlineStr">
+      <c r="A79" s="22" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -2959,7 +2896,7 @@
       <c r="B79" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C79" s="43" t="inlineStr">
+      <c r="C79" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2976,7 +2913,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="43" t="inlineStr">
+      <c r="A80" s="22" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -2984,7 +2921,7 @@
       <c r="B80" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C80" s="43" t="inlineStr">
+      <c r="C80" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3001,7 +2938,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="43" t="inlineStr">
+      <c r="A81" s="22" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -3009,7 +2946,7 @@
       <c r="B81" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C81" s="43" t="inlineStr">
+      <c r="C81" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3026,7 +2963,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="43" t="inlineStr">
+      <c r="A82" s="22" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -3034,7 +2971,7 @@
       <c r="B82" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C82" s="43" t="inlineStr">
+      <c r="C82" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3051,7 +2988,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="43" t="inlineStr">
+      <c r="A83" s="22" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -3059,7 +2996,7 @@
       <c r="B83" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C83" s="43" t="inlineStr">
+      <c r="C83" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3076,7 +3013,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="43" t="inlineStr">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -3084,7 +3021,7 @@
       <c r="B84" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C84" s="43" t="inlineStr">
+      <c r="C84" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3101,7 +3038,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="43" t="inlineStr">
+      <c r="A85" s="22" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -3109,7 +3046,7 @@
       <c r="B85" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C85" s="43" t="inlineStr">
+      <c r="C85" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3126,7 +3063,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="43" t="inlineStr">
+      <c r="A86" s="22" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -3134,7 +3071,7 @@
       <c r="B86" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C86" s="43" t="inlineStr">
+      <c r="C86" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3151,7 +3088,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="43" t="inlineStr">
+      <c r="A87" s="22" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -3159,7 +3096,7 @@
       <c r="B87" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C87" s="43" t="inlineStr">
+      <c r="C87" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3176,7 +3113,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="43" t="inlineStr">
+      <c r="A88" s="22" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -3184,7 +3121,7 @@
       <c r="B88" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C88" s="43" t="inlineStr">
+      <c r="C88" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3201,7 +3138,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="43" t="inlineStr">
+      <c r="A89" s="22" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -3209,7 +3146,7 @@
       <c r="B89" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C89" s="43" t="inlineStr">
+      <c r="C89" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3226,7 +3163,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="43" t="inlineStr">
+      <c r="A90" s="22" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -3234,7 +3171,7 @@
       <c r="B90" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C90" s="43" t="inlineStr">
+      <c r="C90" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3251,7 +3188,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="43" t="inlineStr">
+      <c r="A91" s="22" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -3259,7 +3196,7 @@
       <c r="B91" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C91" s="43" t="inlineStr">
+      <c r="C91" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3276,7 +3213,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="43" t="inlineStr">
+      <c r="A92" s="22" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -3284,7 +3221,7 @@
       <c r="B92" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C92" s="43" t="inlineStr">
+      <c r="C92" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3301,7 +3238,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="43" t="inlineStr">
+      <c r="A93" s="22" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -3309,7 +3246,7 @@
       <c r="B93" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C93" s="43" t="inlineStr">
+      <c r="C93" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3326,7 +3263,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="43" t="inlineStr">
+      <c r="A94" s="22" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -3334,7 +3271,7 @@
       <c r="B94" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C94" s="43" t="inlineStr">
+      <c r="C94" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3351,7 +3288,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="43" t="inlineStr">
+      <c r="A95" s="22" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -3359,7 +3296,7 @@
       <c r="B95" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C95" s="43" t="inlineStr">
+      <c r="C95" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3376,7 +3313,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="43" t="inlineStr">
+      <c r="A96" s="22" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -3384,7 +3321,7 @@
       <c r="B96" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C96" s="43" t="inlineStr">
+      <c r="C96" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3401,7 +3338,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="43" t="inlineStr">
+      <c r="A97" s="22" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -3409,7 +3346,7 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="43" t="inlineStr">
+      <c r="C97" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3426,7 +3363,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="43" t="inlineStr">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -3434,7 +3371,7 @@
       <c r="B98" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C98" s="43" t="inlineStr">
+      <c r="C98" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3451,7 +3388,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="43" t="inlineStr">
+      <c r="A99" s="22" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -3459,7 +3396,7 @@
       <c r="B99" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C99" s="43" t="inlineStr">
+      <c r="C99" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3476,7 +3413,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="43" t="inlineStr">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -3484,7 +3421,7 @@
       <c r="B100" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C100" s="43" t="inlineStr">
+      <c r="C100" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3501,7 +3438,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="43" t="inlineStr">
+      <c r="A101" s="22" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -3509,7 +3446,7 @@
       <c r="B101" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C101" s="43" t="inlineStr">
+      <c r="C101" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3526,7 +3463,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="43" t="inlineStr">
+      <c r="A102" s="22" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -3534,7 +3471,7 @@
       <c r="B102" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C102" s="43" t="inlineStr">
+      <c r="C102" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3551,7 +3488,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="43" t="inlineStr">
+      <c r="A103" s="22" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -3559,7 +3496,7 @@
       <c r="B103" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C103" s="43" t="inlineStr">
+      <c r="C103" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3576,7 +3513,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="43" t="inlineStr">
+      <c r="A104" s="22" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -3584,7 +3521,7 @@
       <c r="B104" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C104" s="43" t="inlineStr">
+      <c r="C104" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3601,7 +3538,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="43" t="inlineStr">
+      <c r="A105" s="22" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -3609,7 +3546,7 @@
       <c r="B105" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C105" s="43" t="inlineStr">
+      <c r="C105" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3626,7 +3563,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="43" t="inlineStr">
+      <c r="A106" s="22" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -3634,7 +3571,7 @@
       <c r="B106" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C106" s="43" t="inlineStr">
+      <c r="C106" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3651,7 +3588,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="43" t="inlineStr">
+      <c r="A107" s="22" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -3659,7 +3596,7 @@
       <c r="B107" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C107" s="43" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3676,7 +3613,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="43" t="inlineStr">
+      <c r="A108" s="22" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -3684,7 +3621,7 @@
       <c r="B108" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C108" s="43" t="inlineStr">
+      <c r="C108" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3701,7 +3638,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="43" t="inlineStr">
+      <c r="A109" s="22" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -3709,7 +3646,7 @@
       <c r="B109" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C109" s="43" t="inlineStr">
+      <c r="C109" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3726,7 +3663,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="43" t="inlineStr">
+      <c r="A110" s="22" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -3734,7 +3671,7 @@
       <c r="B110" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C110" s="43" t="inlineStr">
+      <c r="C110" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3751,7 +3688,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="43" t="inlineStr">
+      <c r="A111" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -3759,7 +3696,7 @@
       <c r="B111" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C111" s="43" t="inlineStr">
+      <c r="C111" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3776,7 +3713,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="43" t="inlineStr">
+      <c r="A112" s="22" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -3784,7 +3721,7 @@
       <c r="B112" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C112" s="43" t="inlineStr">
+      <c r="C112" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3801,7 +3738,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="43" t="inlineStr">
+      <c r="A113" s="22" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -3809,7 +3746,7 @@
       <c r="B113" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C113" s="43" t="inlineStr">
+      <c r="C113" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3826,7 +3763,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="43" t="inlineStr">
+      <c r="A114" s="22" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -3834,7 +3771,7 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="43" t="inlineStr">
+      <c r="C114" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3851,7 +3788,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="43" t="inlineStr">
+      <c r="A115" s="22" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -3859,7 +3796,7 @@
       <c r="B115" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C115" s="43" t="inlineStr">
+      <c r="C115" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3876,7 +3813,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="43" t="inlineStr">
+      <c r="A116" s="22" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -3884,7 +3821,7 @@
       <c r="B116" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C116" s="43" t="inlineStr">
+      <c r="C116" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3901,7 +3838,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="43" t="inlineStr">
+      <c r="A117" s="22" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -3909,7 +3846,7 @@
       <c r="B117" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C117" s="43" t="inlineStr">
+      <c r="C117" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3926,7 +3863,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="43" t="inlineStr">
+      <c r="A118" s="22" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -3934,7 +3871,7 @@
       <c r="B118" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C118" s="43" t="inlineStr">
+      <c r="C118" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3951,7 +3888,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="43" t="inlineStr">
+      <c r="A119" s="22" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -3959,7 +3896,7 @@
       <c r="B119" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C119" s="43" t="inlineStr">
+      <c r="C119" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3976,7 +3913,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="43" t="inlineStr">
+      <c r="A120" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -3984,7 +3921,7 @@
       <c r="B120" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C120" s="43" t="inlineStr">
+      <c r="C120" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4001,7 +3938,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="43" t="inlineStr">
+      <c r="A121" s="22" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -4009,7 +3946,7 @@
       <c r="B121" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C121" s="43" t="inlineStr">
+      <c r="C121" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -4026,7 +3963,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="43" t="inlineStr">
+      <c r="A122" s="22" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -4034,7 +3971,7 @@
       <c r="B122" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C122" s="43" t="inlineStr">
+      <c r="C122" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4051,7 +3988,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="43" t="inlineStr">
+      <c r="A123" s="22" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -4059,7 +3996,7 @@
       <c r="B123" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C123" s="43" t="inlineStr">
+      <c r="C123" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4076,7 +4013,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="43" t="inlineStr">
+      <c r="A124" s="22" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -4084,7 +4021,7 @@
       <c r="B124" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C124" s="43" t="inlineStr">
+      <c r="C124" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4101,7 +4038,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="43" t="inlineStr">
+      <c r="A125" s="22" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -4109,7 +4046,7 @@
       <c r="B125" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C125" s="43" t="inlineStr">
+      <c r="C125" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4126,7 +4063,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="43" t="inlineStr">
+      <c r="A126" s="22" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -4134,7 +4071,7 @@
       <c r="B126" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C126" s="43" t="inlineStr">
+      <c r="C126" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4151,7 +4088,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="44" t="inlineStr">
+      <c r="A127" s="23" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4159,7 +4096,7 @@
       <c r="B127" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C127" s="44" t="inlineStr"/>
+      <c r="C127" s="23" t="inlineStr"/>
       <c r="D127" s="16" t="inlineStr"/>
       <c r="E127" s="16" t="inlineStr"/>
     </row>
@@ -4220,7 +4157,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -4236,7 +4173,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Налоги с ФОТ</t>
         </is>
@@ -4252,7 +4189,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -4268,7 +4205,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Расходы по кассе</t>
         </is>
@@ -4284,7 +4221,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Услуги банка (общие)</t>
         </is>
@@ -4300,9 +4237,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Эквайринг (персонально)</t>
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Эквайринг</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
@@ -4316,7 +4253,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -4332,7 +4269,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>% по кредиту</t>
         </is>
@@ -4348,7 +4285,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Поставщики (счёт 60)</t>
         </is>
@@ -4364,7 +4301,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
@@ -4380,7 +4317,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>ДОХОД (выручка − расходы)</t>
         </is>
@@ -4425,7 +4362,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -4441,7 +4378,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр.1</t>
         </is>
@@ -4457,7 +4394,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
@@ -4473,7 +4410,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Досудебный спор</t>
         </is>
@@ -4489,7 +4426,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Прочие поставщики</t>
         </is>
@@ -4505,7 +4442,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4573,7 +4510,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>01–10.08, старая управленка</t>
         </is>
@@ -4581,14 +4518,14 @@
       <c r="B5" s="6" t="n">
         <v>31613514</v>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>реестр «Оплаты от пациента» без двух документов, помеченных на удаление; сходится с «Ежедневным отчётом по кассам»</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>11–31.08, новая управленка</t>
         </is>
@@ -4596,14 +4533,14 @@
       <c r="B6" s="6" t="n">
         <v>66058340</v>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными», уже за вычетом возвратов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Возвраты пациентам, 01–10.08</t>
         </is>
@@ -4611,14 +4548,14 @@
       <c r="B7" s="6" t="n">
         <v>-720000</v>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>колонка «Возврат денег» «Ежедневного отчёта по кассам»</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
@@ -4626,19 +4563,19 @@
       <c r="B8" s="9" t="n">
         <v>96951854</v>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>деньги, поступившие за месяц</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr"/>
+      <c r="A9" s="22" t="inlineStr"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="43" t="inlineStr"/>
+      <c r="C9" s="22" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>01–10.08: платежи с указанным специалистом</t>
         </is>
@@ -4646,14 +4583,14 @@
       <c r="B10" s="6" t="n">
         <v>30904014</v>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>колонка «Специалист» реестра платежей</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>01–10.08: без специалиста</t>
         </is>
@@ -4661,14 +4598,14 @@
       <c r="B11" s="6" t="n">
         <v>709500</v>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>разнесены по врачам того же пациента, остаток — пропорционально</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>11–31.08: привязано к врачу напрямую</t>
         </is>
@@ -4676,14 +4613,14 @@
       <c r="B12" s="6" t="n">
         <v>46401840</v>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>документы «Оказание услуг» — врач указан в документе</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>11–31.08: авансы, разнесённые через пациента</t>
         </is>
@@ -4691,14 +4628,14 @@
       <c r="B13" s="6" t="n">
         <v>14588000</v>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>оплата картой и кассовые ордера</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>11–31.08: авансы без совпадения по пациенту</t>
         </is>
@@ -4706,7 +4643,7 @@
       <c r="B14" s="6" t="n">
         <v>5068500</v>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>разнесены пропорционально; пациентов нет в реестре услуг августа</t>
         </is>
@@ -4740,7 +4677,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -4759,7 +4696,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -4778,7 +4715,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
@@ -4797,7 +4734,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -4816,7 +4753,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -4835,7 +4772,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4915,18 +4852,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Выручка за месяц</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -4945,18 +4882,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Доход учредителей за месяц</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>9129603.800000001</v>
+        <v>8169725.25</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -4975,18 +4912,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>19042449.94</v>
+        <v>19035318.76</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -5005,12 +4942,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Титул</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Рост выручки с начала года</t>
         </is>
@@ -5033,12 +4970,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Выручка месяца, год к году</t>
         </is>
@@ -5061,12 +4998,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Выручка с начала года</t>
         </is>
@@ -5091,18 +5028,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Средняя выручка в день</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3151852.71</v>
+        <v>3150704.97</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -5121,12 +5058,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Оплаты поставщикам (сч. 60)</t>
         </is>
@@ -5151,12 +5088,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ФОТ с налогами по банку</t>
         </is>
@@ -5181,18 +5118,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Остаток на р/с на конец месяца</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>19042449.94</v>
+        <v>19035318.76</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -5211,12 +5148,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Касса (наличные)</t>
         </is>
@@ -5241,12 +5178,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Эквайринг (карты)</t>
         </is>
@@ -5271,18 +5208,18 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Оплаты физлиц на р/с</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1071080</v>
+        <v>1035500</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -5301,18 +5238,18 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0</v>
+        <v>-720000</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -5331,12 +5268,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Структура</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Комиссия эквайринга</t>
         </is>
@@ -5361,12 +5298,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Медицинские расходы + ИП</t>
         </is>
@@ -5391,12 +5328,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -5421,12 +5358,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>в т.ч. гонорары ИП хирургов</t>
         </is>
@@ -5451,12 +5388,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Расходы</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>в т.ч. ремонт нового корпуса</t>
         </is>
@@ -5481,18 +5418,18 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Экономика</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Доход месяца (итог водопада)</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>9129603.779999999</v>
+        <v>8169725.23</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -5511,12 +5448,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Остаток на начало месяца</t>
         </is>
@@ -5541,18 +5478,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Поступления за месяц</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>674731579.65</v>
+        <v>674932579.65</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -5571,18 +5508,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Списания за месяц</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>658380332.66</v>
+        <v>658588463.84</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -5601,18 +5538,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>ДДС</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Остаток на конец месяца</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>19042449.94</v>
+        <v>19035318.76</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -5631,12 +5568,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Маланичев: личная выручка</t>
         </is>
@@ -5661,18 +5598,18 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Маланичев: ½ выручки других хирургов</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>38625305.81</v>
+        <v>38247989.88</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5691,18 +5628,18 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Маланичев: ½ косметологии и прочего</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1610689.35</v>
+        <v>1610215.29</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -5721,18 +5658,18 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Маланичев: доля расходов</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-44487083.72</v>
+        <v>-44598418.99</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -5741,7 +5678,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>½ общих расходов + персональные (эквайринг, операционные своих пациентов)</t>
+          <t>½ всех расходов месяца + личные анализы учредителя</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -5751,18 +5688,18 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B32" s="40" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Маланичев: доход за месяц</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>127861.52</v>
+        <v>-361263.75</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -5781,12 +5718,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B33" s="40" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Маланичев: остаток с прошлого месяца</t>
         </is>
@@ -5811,12 +5748,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B34" s="40" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Маланичев: удержано в резерв (аренда)</t>
         </is>
@@ -5841,18 +5778,18 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Маланичев: к выплате на конец месяца</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>24904404.54</v>
+        <v>24415279.27</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -5871,12 +5808,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Погосян: личная выручка</t>
         </is>
@@ -5901,18 +5838,18 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Погосян: ½ выручки других хирургов</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>38625305.81</v>
+        <v>38247989.88</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5931,18 +5868,18 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B38" s="40" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Погосян: ½ косметологии и прочего</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1610689.35</v>
+        <v>1610215.29</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -5961,18 +5898,18 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="40" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Погосян: доля расходов</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>-44487083.72</v>
+        <v>-44580046.99</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -5981,7 +5918,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>½ общих расходов + персональные (эквайринг, операционные своих пациентов)</t>
+          <t>½ всех расходов месяца + личные анализы учредителя</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -5991,18 +5928,18 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B40" s="40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Погосян: доход за месяц</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>9001742.27</v>
+        <v>8530989</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -6021,12 +5958,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B41" s="40" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Погосян: остаток с прошлого месяца</t>
         </is>
@@ -6051,12 +5988,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B42" s="40" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Погосян: удержано в резерв (аренда)</t>
         </is>
@@ -6081,18 +6018,18 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="40" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Учредители</t>
         </is>
       </c>
-      <c r="B43" s="40" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Погосян: к выплате на конец месяца</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>48395361.48</v>
+        <v>47924608.21</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -6111,12 +6048,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="40" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B44" s="40" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Долг по кредитной линии</t>
         </is>
@@ -6141,12 +6078,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="40" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B45" s="40" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Остаток наличных в кассе</t>
         </is>
@@ -6169,12 +6106,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="40" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B46" s="40" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -6199,12 +6136,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="40" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Справочно</t>
         </is>
       </c>
-      <c r="B47" s="40" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Зарезервировано на аренду (всего)</t>
         </is>
@@ -6345,7 +6282,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
@@ -6387,7 +6324,7 @@
       <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -6429,7 +6366,7 @@
       <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
@@ -6471,7 +6408,7 @@
       <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
@@ -6513,7 +6450,7 @@
       <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -6549,13 +6486,13 @@
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>2728594</v>
+        <v>2698594</v>
       </c>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
@@ -6597,7 +6534,7 @@
       <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -6639,7 +6576,7 @@
       <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
@@ -6675,13 +6612,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>3852280</v>
+        <v>3846700</v>
       </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
@@ -6723,7 +6660,7 @@
       <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
@@ -6765,7 +6702,7 @@
       <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
@@ -6807,7 +6744,7 @@
       <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -6849,7 +6786,7 @@
       <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
@@ -6891,7 +6828,7 @@
       <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
@@ -6933,7 +6870,7 @@
       <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -6975,7 +6912,7 @@
       <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
@@ -7017,7 +6954,7 @@
       <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
@@ -7059,7 +6996,7 @@
       <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -7101,7 +7038,7 @@
       <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7143,7 +7080,7 @@
       <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -7185,7 +7122,7 @@
       <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
@@ -7227,7 +7164,7 @@
       <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
@@ -7269,7 +7206,7 @@
       <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
@@ -7311,7 +7248,7 @@
       <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -7353,7 +7290,7 @@
       <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -7395,7 +7332,7 @@
       <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
@@ -7437,7 +7374,7 @@
       <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -7479,7 +7416,7 @@
       <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -7521,7 +7458,7 @@
       <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
@@ -7563,7 +7500,7 @@
       <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
@@ -7605,7 +7542,7 @@
       <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -7647,7 +7584,7 @@
       <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="41" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7683,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>97707434</v>
+        <v>97671854</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0</v>
@@ -7773,7 +7710,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -7799,7 +7736,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -7825,7 +7762,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
@@ -7840,10 +7777,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>-720000</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>77250611.63</v>
+        <v>76495979.75</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.79</v>
@@ -7851,7 +7788,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -7877,7 +7814,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -7895,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2960140.06</v>
+        <v>2959191.93</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.03</v>
@@ -7903,7 +7840,7 @@
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -7915,13 +7852,13 @@
         <v>61654454</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1071080</v>
+        <v>1035500</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0</v>
+        <v>-720000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>1</v>
@@ -7960,7 +7897,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
@@ -7976,7 +7913,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
@@ -7992,7 +7929,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
@@ -8008,7 +7945,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
@@ -8024,7 +7961,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
@@ -8040,7 +7977,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
@@ -8056,7 +7993,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
@@ -8072,7 +8009,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
@@ -8084,7 +8021,7 @@
       <c r="D21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
@@ -8096,7 +8033,7 @@
       <c r="D22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
@@ -8108,7 +8045,7 @@
       <c r="D23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
@@ -8120,7 +8057,7 @@
       <c r="D24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
@@ -8181,12 +8118,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -8199,12 +8136,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
@@ -8217,12 +8154,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -8235,12 +8172,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
@@ -8253,12 +8190,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -8271,12 +8208,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
@@ -8289,12 +8226,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
@@ -8307,12 +8244,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
@@ -8325,12 +8262,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
@@ -8343,12 +8280,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
@@ -8361,12 +8298,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
@@ -8379,12 +8316,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
@@ -8397,12 +8334,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
@@ -8415,12 +8352,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
@@ -8433,12 +8370,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
@@ -8451,12 +8388,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
@@ -8469,12 +8406,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -8487,12 +8424,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
@@ -8505,12 +8442,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
@@ -8523,12 +8460,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
@@ -8541,12 +8478,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -8559,12 +8496,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
@@ -8577,12 +8514,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
@@ -8595,12 +8532,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -8613,12 +8550,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
@@ -8631,12 +8568,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
@@ -8649,12 +8586,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
@@ -8667,12 +8604,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
@@ -8685,12 +8622,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B32" s="40" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
@@ -8703,12 +8640,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B33" s="40" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -8721,12 +8658,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B34" s="40" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
@@ -8739,12 +8676,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
@@ -8757,12 +8694,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
@@ -8775,12 +8712,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
@@ -8793,12 +8730,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B38" s="40" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -8811,12 +8748,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="40" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
@@ -8829,12 +8766,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B40" s="40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
@@ -8847,12 +8784,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B41" s="40" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
@@ -8865,12 +8802,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B42" s="40" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
@@ -8883,12 +8820,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="40" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B43" s="40" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -8901,12 +8838,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="40" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B44" s="40" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
@@ -8919,12 +8856,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="40" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B45" s="40" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
@@ -8937,12 +8874,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="40" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B46" s="40" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
@@ -8955,12 +8892,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="40" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B47" s="40" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
@@ -8973,12 +8910,12 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="40" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B48" s="40" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
@@ -8991,12 +8928,12 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="40" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B49" s="40" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
@@ -9009,12 +8946,12 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="40" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B50" s="40" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
@@ -9027,12 +8964,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B51" s="40" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
@@ -9045,12 +8982,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="40" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B52" s="40" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
@@ -9063,12 +9000,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="40" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B53" s="40" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
@@ -9081,12 +9018,12 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="40" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B54" s="40" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
@@ -9099,12 +9036,12 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="40" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B55" s="40" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
@@ -9117,12 +9054,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="40" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B56" s="40" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
@@ -9135,12 +9072,12 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="40" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B57" s="40" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
@@ -9153,12 +9090,12 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="40" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B58" s="40" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
@@ -9171,12 +9108,12 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="40" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B59" s="40" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
@@ -9189,12 +9126,12 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="40" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B60" s="40" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
@@ -9207,12 +9144,12 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="40" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B61" s="40" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
@@ -9225,12 +9162,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="40" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B62" s="40" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
@@ -9243,12 +9180,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="40" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B63" s="40" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
@@ -9261,12 +9198,12 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="40" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B64" s="40" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
@@ -9279,12 +9216,12 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="40" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B65" s="40" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
@@ -9297,12 +9234,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="40" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B66" s="40" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
@@ -9315,12 +9252,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="41" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B67" s="41" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -9333,12 +9270,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="42" t="inlineStr">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B68" s="42" t="inlineStr"/>
+      <c r="B68" s="13" t="inlineStr"/>
       <c r="C68" s="14" t="n">
         <v>69794048.05</v>
       </c>
@@ -9388,7 +9325,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -9396,14 +9333,14 @@
       <c r="B4" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Ремонт Самокатная 1 стр12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -9411,14 +9348,14 @@
       <c r="B5" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -9426,14 +9363,14 @@
       <c r="B6" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -9441,14 +9378,14 @@
       <c r="B7" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -9456,14 +9393,14 @@
       <c r="B8" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -9471,14 +9408,14 @@
       <c r="B9" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -9486,14 +9423,14 @@
       <c r="B10" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -9501,14 +9438,14 @@
       <c r="B11" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -9516,14 +9453,14 @@
       <c r="B12" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -9531,14 +9468,14 @@
       <c r="B13" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -9546,14 +9483,14 @@
       <c r="B14" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C14" s="40" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -9561,14 +9498,14 @@
       <c r="B15" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -9576,14 +9513,14 @@
       <c r="B16" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -9591,14 +9528,14 @@
       <c r="B17" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -9606,14 +9543,14 @@
       <c r="B18" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -9621,14 +9558,14 @@
       <c r="B19" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -9636,14 +9573,14 @@
       <c r="B20" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C20" s="40" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -9651,14 +9588,14 @@
       <c r="B21" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -9666,14 +9603,14 @@
       <c r="B22" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -9681,14 +9618,14 @@
       <c r="B23" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -9696,14 +9633,14 @@
       <c r="B24" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -9711,14 +9648,14 @@
       <c r="B25" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -9726,14 +9663,14 @@
       <c r="B26" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -9741,14 +9678,14 @@
       <c r="B27" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -9756,14 +9693,14 @@
       <c r="B28" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -9771,14 +9708,14 @@
       <c r="B29" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C29" s="40" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -9786,14 +9723,14 @@
       <c r="B30" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C30" s="40" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -9801,14 +9738,14 @@
       <c r="B31" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C31" s="40" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -9816,14 +9753,14 @@
       <c r="B32" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -9831,14 +9768,14 @@
       <c r="B33" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -9846,14 +9783,14 @@
       <c r="B34" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C34" s="40" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -9861,14 +9798,14 @@
       <c r="B35" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C35" s="40" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -9876,14 +9813,14 @@
       <c r="B36" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C36" s="40" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -9891,14 +9828,14 @@
       <c r="B37" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C37" s="40" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -9906,14 +9843,14 @@
       <c r="B38" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C38" s="40" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="40" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -9921,14 +9858,14 @@
       <c r="B39" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C39" s="40" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -9936,14 +9873,14 @@
       <c r="B40" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C40" s="40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -9951,14 +9888,14 @@
       <c r="B41" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C41" s="40" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -9966,14 +9903,14 @@
       <c r="B42" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C42" s="40" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="40" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -9981,14 +9918,14 @@
       <c r="B43" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C43" s="40" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="40" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -9996,14 +9933,14 @@
       <c r="B44" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="40" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -10011,14 +9948,14 @@
       <c r="B45" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C45" s="40" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="40" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -10026,14 +9963,14 @@
       <c r="B46" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C46" s="40" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="40" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -10041,14 +9978,14 @@
       <c r="B47" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C47" s="40" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="40" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -10056,14 +9993,14 @@
       <c r="B48" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C48" s="40" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="40" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -10071,14 +10008,14 @@
       <c r="B49" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C49" s="40" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="40" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -10086,14 +10023,14 @@
       <c r="B50" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C50" s="40" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -10101,14 +10038,14 @@
       <c r="B51" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C51" s="40" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="40" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -10116,14 +10053,14 @@
       <c r="B52" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="40" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -10131,14 +10068,14 @@
       <c r="B53" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C53" s="40" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="40" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -10146,14 +10083,14 @@
       <c r="B54" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C54" s="40" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="40" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -10161,14 +10098,14 @@
       <c r="B55" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C55" s="40" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="40" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -10176,14 +10113,14 @@
       <c r="B56" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C56" s="40" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="40" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -10191,14 +10128,14 @@
       <c r="B57" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C57" s="40" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="40" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -10206,14 +10143,14 @@
       <c r="B58" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C58" s="40" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="40" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -10221,14 +10158,14 @@
       <c r="B59" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C59" s="40" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="40" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -10236,14 +10173,14 @@
       <c r="B60" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C60" s="40" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="40" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -10251,14 +10188,14 @@
       <c r="B61" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C61" s="40" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="40" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -10266,14 +10203,14 @@
       <c r="B62" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C62" s="40" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="40" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -10281,14 +10218,14 @@
       <c r="B63" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C63" s="40" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="40" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -10296,14 +10233,14 @@
       <c r="B64" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C64" s="40" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="40" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -10311,14 +10248,14 @@
       <c r="B65" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C65" s="40" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="40" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -10326,14 +10263,14 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="40" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="40" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -10341,14 +10278,14 @@
       <c r="B67" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C67" s="40" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="40" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -10356,14 +10293,14 @@
       <c r="B68" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C68" s="40" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="40" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -10371,14 +10308,14 @@
       <c r="B69" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C69" s="40" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="40" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -10386,14 +10323,14 @@
       <c r="B70" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C70" s="40" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="40" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -10401,14 +10338,14 @@
       <c r="B71" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C71" s="40" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="40" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -10416,14 +10353,14 @@
       <c r="B72" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C72" s="40" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="40" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -10431,14 +10368,14 @@
       <c r="B73" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C73" s="40" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="40" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -10446,14 +10383,14 @@
       <c r="B74" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C74" s="40" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="40" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -10461,14 +10398,14 @@
       <c r="B75" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C75" s="40" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="40" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -10476,14 +10413,14 @@
       <c r="B76" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C76" s="40" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="40" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -10491,14 +10428,14 @@
       <c r="B77" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C77" s="40" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="40" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -10506,14 +10443,14 @@
       <c r="B78" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C78" s="40" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="40" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -10521,14 +10458,14 @@
       <c r="B79" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C79" s="40" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="40" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -10536,14 +10473,14 @@
       <c r="B80" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C80" s="40" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="40" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -10551,14 +10488,14 @@
       <c r="B81" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C81" s="40" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="40" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -10566,14 +10503,14 @@
       <c r="B82" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C82" s="40" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="40" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -10581,14 +10518,14 @@
       <c r="B83" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C83" s="40" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="40" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -10596,14 +10533,14 @@
       <c r="B84" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C84" s="40" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="40" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -10611,14 +10548,14 @@
       <c r="B85" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C85" s="40" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="40" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -10626,14 +10563,14 @@
       <c r="B86" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C86" s="40" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="40" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -10641,14 +10578,14 @@
       <c r="B87" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C87" s="40" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="40" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -10656,14 +10593,14 @@
       <c r="B88" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C88" s="40" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="40" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -10671,14 +10608,14 @@
       <c r="B89" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C89" s="40" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="40" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -10686,14 +10623,14 @@
       <c r="B90" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C90" s="40" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="40" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -10701,14 +10638,14 @@
       <c r="B91" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C91" s="40" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="40" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -10716,14 +10653,14 @@
       <c r="B92" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C92" s="40" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="40" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -10731,14 +10668,14 @@
       <c r="B93" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C93" s="40" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="40" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -10746,14 +10683,14 @@
       <c r="B94" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C94" s="40" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="40" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -10761,14 +10698,14 @@
       <c r="B95" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C95" s="40" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="40" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -10776,14 +10713,14 @@
       <c r="B96" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C96" s="40" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="40" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -10791,14 +10728,14 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="40" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="40" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -10806,14 +10743,14 @@
       <c r="B98" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C98" s="40" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="40" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -10821,14 +10758,14 @@
       <c r="B99" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C99" s="40" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="40" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -10836,14 +10773,14 @@
       <c r="B100" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C100" s="40" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="40" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -10851,14 +10788,14 @@
       <c r="B101" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C101" s="40" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="40" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -10866,14 +10803,14 @@
       <c r="B102" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C102" s="40" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="40" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -10881,14 +10818,14 @@
       <c r="B103" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C103" s="40" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="40" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -10896,14 +10833,14 @@
       <c r="B104" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C104" s="40" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="40" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -10911,14 +10848,14 @@
       <c r="B105" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C105" s="40" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="40" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -10926,14 +10863,14 @@
       <c r="B106" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C106" s="40" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="40" t="inlineStr">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -10941,14 +10878,14 @@
       <c r="B107" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C107" s="40" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="40" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -10956,14 +10893,14 @@
       <c r="B108" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C108" s="40" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="40" t="inlineStr">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -10971,14 +10908,14 @@
       <c r="B109" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C109" s="40" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="40" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -10986,14 +10923,14 @@
       <c r="B110" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C110" s="40" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="40" t="inlineStr">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -11001,14 +10938,14 @@
       <c r="B111" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C111" s="40" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="40" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -11016,14 +10953,14 @@
       <c r="B112" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C112" s="40" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="40" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -11031,14 +10968,14 @@
       <c r="B113" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C113" s="40" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="40" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -11046,14 +10983,14 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="40" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="40" t="inlineStr">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -11061,14 +10998,14 @@
       <c r="B115" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C115" s="40" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="40" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -11076,14 +11013,14 @@
       <c r="B116" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C116" s="40" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="40" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -11091,14 +11028,14 @@
       <c r="B117" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C117" s="40" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="40" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -11106,14 +11043,14 @@
       <c r="B118" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C118" s="40" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="40" t="inlineStr">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -11121,14 +11058,14 @@
       <c r="B119" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C119" s="40" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="40" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -11136,14 +11073,14 @@
       <c r="B120" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C120" s="40" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="40" t="inlineStr">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -11151,14 +11088,14 @@
       <c r="B121" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C121" s="40" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="40" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -11166,14 +11103,14 @@
       <c r="B122" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C122" s="40" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="40" t="inlineStr">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -11181,14 +11118,14 @@
       <c r="B123" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C123" s="40" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="40" t="inlineStr">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -11196,14 +11133,14 @@
       <c r="B124" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C124" s="40" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="40" t="inlineStr">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -11211,14 +11148,14 @@
       <c r="B125" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C125" s="40" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="41" t="inlineStr">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -11226,7 +11163,7 @@
       <c r="B126" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C126" s="41" t="inlineStr"/>
+      <c r="C126" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11239,7 +11176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11278,7 +11215,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Начальное сальдо</t>
         </is>
@@ -11290,7 +11227,7 @@
       <c r="D4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Возврат средств с депозитов</t>
         </is>
@@ -11306,13 +11243,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Инкассация и эквайринг</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>153295343.14</v>
+        <v>153496343.14</v>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="7" t="inlineStr">
@@ -11322,7 +11259,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Возвраты от поставщиков</t>
         </is>
@@ -11338,7 +11275,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Кредит банка</t>
         </is>
@@ -11354,7 +11291,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
@@ -11370,7 +11307,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -11386,7 +11323,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Размещение на депозиты</t>
         </is>
@@ -11402,7 +11339,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Переводы между счетами</t>
         </is>
@@ -11418,7 +11355,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Оплаты поставщикам и подрядчикам</t>
         </is>
@@ -11434,7 +11371,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Возвраты пациентам</t>
         </is>
@@ -11450,126 +11387,142 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>Налоги</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Погашение кредита</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n">
-        <v>7871244.91</v>
+        <v>204388.93</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>кор. счёт 68</t>
+          <t>кор. счёт 67</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>Страховые взносы</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Налоги</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n">
-        <v>29253.37</v>
+        <v>7871244.91</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>кор. счёт 69</t>
+          <t>кор. счёт 68</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
-        <is>
-          <t>Зарплата</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Страховые взносы</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n">
-        <v>12490831.85</v>
+        <v>29253.37</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>кор. счёт 70</t>
+          <t>кор. счёт 69</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>Выплата дивидендов</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Зарплата</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n">
-        <v>10000000</v>
+        <v>12490831.85</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>кор. счёт 75</t>
+          <t>кор. счёт 70</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
-        <is>
-          <t>Алименты</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Выплата дивидендов</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n">
-        <v>38726.66</v>
+        <v>10000000</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>кор. счёт 76</t>
+          <t>кор. счёт 75</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
-        <is>
-          <t>Услуги банка</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Алименты</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n">
-        <v>137448.82</v>
+        <v>38726.66</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
+          <t>кор. счёт 76</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Услуги банка</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>141191.07</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
           <t>кор. счёт 91</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="41" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Оборот за месяц</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
-        <v>674731579.65</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>658380332.66</v>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="B22" s="9" t="n">
+        <v>674932579.65</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>658588463.84</v>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Конечное сальдо</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>19042449.94</v>
-      </c>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="B23" s="14" t="n">
+        <v>19035318.76</v>
+      </c>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>'= начальное + поступления − списания</t>
         </is>
@@ -11586,7 +11539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11644,12 +11597,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Личная выручка (свои операции)</t>
         </is>
@@ -11670,24 +11623,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>+ ½ выручки других хирургов</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>38625305.81</v>
+        <v>38247989.88</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>38625305.81</v>
+        <v>38247989.88</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>77250611.63</v>
+        <v>76495979.75</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -11696,24 +11649,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>+ ½ косметологии</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1480070.03</v>
+        <v>1479595.97</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1480070.03</v>
+        <v>1479595.97</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2960140.06</v>
+        <v>2959191.93</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -11722,12 +11675,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>+ ½ прочих доходов</t>
         </is>
@@ -11748,12 +11701,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>+ ½ процентов по депозитам</t>
         </is>
@@ -11785,23 +11738,23 @@
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>-44487083.72</v>
+        <v>-44598418.99</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>-44487083.72</v>
+        <v>-44580046.99</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-88974167.44</v>
+        <v>-89178465.98</v>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>½ общих + персональные</t>
+          <t>½ всех расходов + личные анализы</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr"/>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">      налоги с ФОТ (68.90 + 69)</t>
         </is>
@@ -11818,8 +11771,8 @@
       <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr"/>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">      зарплата по банку</t>
         </is>
@@ -11836,8 +11789,8 @@
       <c r="F12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr"/>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">      расходы по кассе</t>
         </is>
@@ -11854,28 +11807,28 @@
       <c r="F13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr"/>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">      услуги банка (общие)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-70640.73</v>
+        <v>-70595.53999999999</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-70640.73</v>
+        <v>-70595.53999999999</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-141281.46</v>
+        <v>-141191.08</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr"/>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      услуги банка (эквайринг, персонально)</t>
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      услуги банка (эквайринг)</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -11890,8 +11843,8 @@
       <c r="F15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr"/>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">      алименты (удержание из ЗП)</t>
         </is>
@@ -11908,140 +11861,180 @@
       <c r="F16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr"/>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      проценты по кредитной линии</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-102194.46</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-102194.46</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-204388.92</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">      дополнительные корректировки</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="40" t="inlineStr"/>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="C18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">      поставщики (счёт 60) + Халва</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C19" s="6" t="n">
         <v>-34897024.02</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D19" s="6" t="n">
         <v>-34897024.02</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>-69794048.04000001</v>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      личные анализы (сверх деления 50/50)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-9186</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>9186</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>лист «Расходы врачей»: Маланичев 30 620, Погосян 12 248</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>127861.52</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>9001742.27</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>9129603.800000001</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="C21" s="9" t="n">
+        <v>-361263.75</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>8530989</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>8169725.25</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>сумма шагов выше</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>+ Остаток с прошлого месяца</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C22" s="6" t="n">
         <v>30658896.02</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D22" s="6" t="n">
         <v>45275972.21</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E22" s="6" t="n">
         <v>75934868.23</v>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>− Выплачены дивиденды</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C23" s="6" t="n">
         <v>-5882353</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D23" s="6" t="n">
         <v>-5882353</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>-11764706</v>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="41" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="41" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
-        <v>24904404.54</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>48395361.48</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>73299766.03</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="C24" s="9" t="n">
+        <v>24415279.27</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>47924608.21</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>72339887.48</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>доход + остаток − дивиденды − резерв</t>
         </is>
@@ -12110,29 +12103,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="n">
+      <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>97707434</v>
+        <v>96951853.98999999</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -12141,17 +12134,17 @@
         <v>-39819623</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>57887811</v>
+        <v>57132230.99</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>40.8</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="n">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Медицинские расходы</t>
         </is>
@@ -12160,17 +12153,17 @@
         <v>-16182175.49</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>41705635.51</v>
+        <v>40950055.5</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="n">
+      <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ФОТ, налоги, алименты</t>
         </is>
@@ -12179,17 +12172,17 @@
         <v>-18665350.79</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>23040284.72</v>
+        <v>22284704.71</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="n">
+      <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Управленческие расходы</t>
         </is>
@@ -12198,17 +12191,17 @@
         <v>-13276249.56</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9764035.16</v>
+        <v>9008455.15</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="n">
+      <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Ремонт нового корпуса</t>
         </is>
@@ -12217,36 +12210,36 @@
         <v>-516000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9248035.16</v>
+        <v>8492455.15</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="n">
+      <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Услуги банка</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>-514768.62</v>
+        <v>-719067.16</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8733266.539999999</v>
+        <v>7773387.99</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Проценты по депозитам</t>
         </is>
@@ -12255,29 +12248,29 @@
         <v>396337.24</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>9129603.779999999</v>
+        <v>8169725.23</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Доход месяца</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>9129603.779999999</v>
+        <v>8169725.23</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>9129603.779999999</v>
+        <v>8169725.23</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>31613514</v>
+        <v>31243514</v>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-720000</v>
+        <v>-350000</v>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>30904014</v>
+        <v>30534014</v>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>29889933.64</v>
+        <v>29889660.71</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>46606046.11</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>76495979.75</v>
+        <v>76495706.81999999</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0.79</v>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1003580.36</v>
+        <v>1003853.29</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1955611.58</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2959191.93</v>
+        <v>2959464.86</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0.03</v>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3150704.97</v>
+        <v>3138769.48</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>61654454</v>
+        <v>61284454</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>-720000</v>
+        <v>-350000</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>38247989.88</v>
+        <v>38247853.41</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1610215.29</v>
+        <v>1610351.75</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>38247989.88</v>
+        <v>38247853.41</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1610215.29</v>
+        <v>1610351.75</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>4277000</v>
+        <v>3907000</v>
       </c>
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>97671854</v>
+        <v>97301854</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0</v>
@@ -7777,10 +7777,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-720000</v>
+        <v>-350000</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>76495979.75</v>
+        <v>76495706.81999999</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.79</v>
@@ -7832,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2959191.93</v>
+        <v>2959464.86</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.03</v>
@@ -7849,13 +7849,13 @@
         <v>34981900</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>61654454</v>
+        <v>61284454</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>1035500</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-720000</v>
+        <v>-350000</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>96951853.98999999</v>
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>38247989.88</v>
+        <v>38247853.41</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>38247989.88</v>
+        <v>38247853.41</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>76495979.75</v>
+        <v>76495706.81999999</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -11660,13 +11660,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1479595.97</v>
+        <v>1479732.43</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1479595.97</v>
+        <v>1479732.43</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2959191.93</v>
+        <v>2959464.86</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -4053,7 +4053,7 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Услуги банка</t>
+          <t>Услуги банка (через счёт 60)</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Услуги банка</t>
+          <t>Услуги банка (через счёт 60)</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Услуги банка</t>
+          <t>Услуги банка (через счёт 60)</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Услуги банка</t>
+          <t>Услуги банка (через счёт 60)</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Услуги банка</t>
+          <t>Услуги банка (через счёт 60)</t>
         </is>
       </c>
     </row>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>96951854</v>
+        <v>96941854</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0.01</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8169725.23</v>
+        <v>8159725.23</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8169725.25</v>
+        <v>8159725.25</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>-0.02</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>8169725.25</v>
+        <v>8159725.25</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8169725.25</v>
+        <v>8159725.25</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -4166,10 +4166,10 @@
         <v>108126415.72</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-11174561.73</v>
+        <v>-11184561.73</v>
       </c>
     </row>
     <row r="6">
@@ -4326,10 +4326,10 @@
         <v>35573284.74</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>7773387.99</v>
+        <v>7763387.99</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>-27799896.75</v>
+        <v>-27809896.75</v>
       </c>
     </row>
     <row r="17">
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-350000</v>
+        <v>-360000</v>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>96951854</v>
+        <v>96941854</v>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>29889660.71</v>
+        <v>29879660.71</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>46606046.11</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>76495706.81999999</v>
+        <v>76485706.81999999</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0.79</v>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>30893514</v>
+        <v>30883514</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>66058340</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>1</v>
@@ -4801,7 +4801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>касса + эквайринг + оплаты физлиц на р/с − возвраты</t>
+          <t>касса + эквайринг − возвраты</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8169725.25</v>
+        <v>8159725.25</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -5185,11 +5185,11 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Эквайринг (карты)</t>
+          <t>Эквайринг (карты и онлайн-оплаты)</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>61284454</v>
+        <v>62319954</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>оборот сч. 57.03 / строка «банк»</t>
+          <t>оборот сч. 57.03: розница и интернет-эквайринг</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -5215,11 +5215,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Оплаты физлиц на р/с</t>
+          <t>Возвраты пациентам</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1035500</v>
+        <v>-360000</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>оборот сч. 62 (дебет), физлица</t>
+          <t>строка «возврат пациенту ч/з банк и кассу»</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -5245,11 +5245,11 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Возвраты пациентам</t>
+          <t>Комиссия эквайринга</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>-350000</v>
+        <v>373487.16</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -5258,28 +5258,28 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>строка «возврат пациенту ч/з банк и кассу»</t>
+          <t>сумма комиссий по группам врачей</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>ВЫРУЧКА, лист «Август 2026», справочный блок «услуги Банка в Отчет»</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Структура</t>
+          <t>Расходы</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
+          <t>Медицинские расходы + ИП</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>373487.16</v>
+        <v>56001798.49</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>сумма комиссий по группам врачей</t>
+          <t>итог блока «МЕДИЦИНСКИЕ РАСХОДЫ+ИП»</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>ВЫРУЧКА, лист «Август 2026», справочный блок «услуги Банка в Отчет»</t>
+          <t>РАСХОДЫ (Обороты сч. 60), лист 1, колонки E–F</t>
         </is>
       </c>
     </row>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Медицинские расходы + ИП</t>
+          <t>Управленческие расходы</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>56001798.49</v>
+        <v>13792249.56</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>итог блока «МЕДИЦИНСКИЕ РАСХОДЫ+ИП»</t>
+          <t>итог блока «УПРАВЛЕНЧЕСКИЕ РАСХОДЫ»</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -5335,11 +5335,11 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Управленческие расходы</t>
+          <t>в т.ч. гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>13792249.56</v>
+        <v>39819623</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -5348,12 +5348,12 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>итог блока «УПРАВЛЕНЧЕСКИЕ РАСХОДЫ»</t>
+          <t>статья «ИП хирурги» медицинского блока</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>РАСХОДЫ (Обороты сч. 60), лист 1, колонки E–F</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5365,11 +5365,11 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>в т.ч. гонорары ИП хирургов</t>
+          <t>в т.ч. ремонт нового корпуса</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>39819623</v>
+        <v>516000</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -5378,28 +5378,28 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>статья «ИП хирурги» медицинского блока</t>
+          <t>статья «Ремонт Самокатная 1 стр.12»</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>РАСХОДЫ (Обороты сч. 60), лист 1, управленческий блок</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Расходы</t>
+          <t>Экономика</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>в т.ч. ремонт нового корпуса</t>
+          <t>Доход месяца (итог водопада)</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>516000</v>
+        <v>8159725.23</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -5408,28 +5408,28 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>статья «Ремонт Самокатная 1 стр.12»</t>
+          <t>выручка − все статьи расходов по шагам водопада</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>РАСХОДЫ (Обороты сч. 60), лист 1, управленческий блок</t>
+          <t>лист «08 Водопад»</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>ДДС</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Доход месяца (итог водопада)</t>
+          <t>Остаток на начало месяца</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>8169725.23</v>
+        <v>2691202.95</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -5438,12 +5438,12 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>выручка − все статьи расходов по шагам водопада</t>
+          <t>начальное сальдо сч. 51</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>лист «08 Водопад»</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5455,11 +5455,11 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Остаток на начало месяца</t>
+          <t>Поступления за месяц</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>2691202.95</v>
+        <v>674932579.65</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>начальное сальдо сч. 51</t>
+          <t>оборот по дебету сч. 51</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Поступления за месяц</t>
+          <t>Списания за месяц</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>674932579.65</v>
+        <v>658588463.84</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>оборот по дебету сч. 51</t>
+          <t>оборот по кредиту сч. 51</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -5515,11 +5515,11 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Списания за месяц</t>
+          <t>Остаток на конец месяца</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>658588463.84</v>
+        <v>19035318.76</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>оборот по кредиту сч. 51</t>
+          <t>конечное сальдо сч. 51</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -5540,16 +5540,16 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>ДДС</t>
+          <t>Учредители</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Остаток на конец месяца</t>
+          <t>Маланичев: личная выручка</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>19035318.76</v>
+        <v>4180781.46</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>конечное сальдо сч. 51</t>
+          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -5575,11 +5575,11 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: личная выручка</t>
+          <t>Маланичев: ½ выручки других хирургов</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>4180781.46</v>
+        <v>38242853.41</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
+          <t>выручка «Другие хирурги» / 2</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -5605,11 +5605,11 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: ½ выручки других хирургов</t>
+          <t>Маланичев: ½ косметологии и прочего</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>38247853.41</v>
+        <v>1610351.75</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>выручка «Другие хирурги» / 2</t>
+          <t>(косметология + прочие доходы) / 2</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -5635,11 +5635,11 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: ½ косметологии и прочего</t>
+          <t>Маланичев: доля расходов</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1610351.75</v>
+        <v>-44598418.99</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>(косметология + прочие доходы) / 2</t>
+          <t>½ всех расходов месяца + личные анализы учредителя</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -5665,11 +5665,11 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: доля расходов</t>
+          <t>Маланичев: доход за месяц</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-44598418.99</v>
+        <v>-366263.75</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -5678,12 +5678,12 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>½ всех расходов месяца + личные анализы учредителя</t>
+          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>лист «07 Учредители»</t>
         </is>
       </c>
     </row>
@@ -5695,11 +5695,11 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: доход за месяц</t>
+          <t>Маланичев: остаток с прошлого месяца</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-361263.75</v>
+        <v>30658896.02</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -5708,12 +5708,12 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
+          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>лист «07 Учредители»</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
         </is>
       </c>
     </row>
@@ -5725,11 +5725,11 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: остаток с прошлого месяца</t>
+          <t>Маланичев: удержано в резерв (аренда)</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>30658896.02</v>
+        <v>0</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
+          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5755,11 +5755,11 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: удержано в резерв (аренда)</t>
+          <t>Маланичев: к выплате на конец месяца</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>0</v>
+        <v>24410279.27</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
+          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: к выплате на конец месяца</t>
+          <t>Погосян: личная выручка</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>24415279.27</v>
+        <v>13054662.21</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
+          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -5815,11 +5815,11 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Погосян: личная выручка</t>
+          <t>Погосян: ½ выручки других хирургов</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>13054662.21</v>
+        <v>38242853.41</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
+          <t>выручка «Другие хирурги» / 2</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Погосян: ½ выручки других хирургов</t>
+          <t>Погосян: ½ косметологии и прочего</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>38247853.41</v>
+        <v>1610351.75</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>выручка «Другие хирурги» / 2</t>
+          <t>(косметология + прочие доходы) / 2</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -5875,11 +5875,11 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Погосян: ½ косметологии и прочего</t>
+          <t>Погосян: доля расходов</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1610351.75</v>
+        <v>-44580046.99</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>(косметология + прочие доходы) / 2</t>
+          <t>½ всех расходов месяца + личные анализы учредителя</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -5905,11 +5905,11 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Погосян: доля расходов</t>
+          <t>Погосян: доход за месяц</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>-44580046.99</v>
+        <v>8525989</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -5918,12 +5918,12 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>½ всех расходов месяца + личные анализы учредителя</t>
+          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>лист «07 Учредители»</t>
         </is>
       </c>
     </row>
@@ -5935,11 +5935,11 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Погосян: доход за месяц</t>
+          <t>Погосян: остаток с прошлого месяца</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>8530989</v>
+        <v>45275972.21</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
+          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>лист «07 Учредители»</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
         </is>
       </c>
     </row>
@@ -5965,11 +5965,11 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Погосян: остаток с прошлого месяца</t>
+          <t>Погосян: удержано в резерв (аренда)</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>45275972.21</v>
+        <v>0</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
+          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5995,11 +5995,11 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Погосян: удержано в резерв (аренда)</t>
+          <t>Погосян: к выплате на конец месяца</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>0</v>
+        <v>47919608.21</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
+          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -6020,16 +6020,16 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Учредители</t>
+          <t>Справочно</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Погосян: к выплате на конец месяца</t>
+          <t>Долг по кредитной линии</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>47924608.21</v>
+        <v>27545367</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
+          <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -6055,12 +6055,10 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Долг по кредитной линии</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>27545367</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
           <t>₽</t>
@@ -6085,10 +6083,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n"/>
+          <t>Проценты по депозитам</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>396337.24</v>
+      </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
           <t>₽</t>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии</t>
+          <t>оборот сч. 91.01 «% по депозитам»</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -6113,11 +6113,11 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Проценты по депозитам</t>
+          <t>Зарезервировано на аренду (всего)</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>396337.24</v>
+        <v>0</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
@@ -6126,40 +6126,10 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>оборот сч. 91.01 «% по депозитам»</t>
+          <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Справочно</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Зарезервировано на аренду (всего)</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>₽</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
@@ -7640,17 +7610,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7663,7 +7630,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Итог = касса + эквайринг + оплаты физлиц на р/с − возвраты</t>
+          <t>Итог = касса + эквайринг (карты и онлайн-оплаты) − возвраты</t>
         </is>
       </c>
     </row>
@@ -7675,35 +7642,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Касса</t>
+          <t>Возвраты</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
+          <t>Итого</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Оплаты на р/с</t>
+          <t>Доля</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Возвраты</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Доля</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Комиссия эквайринга</t>
         </is>
@@ -7719,21 +7671,12 @@
         <v>0</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6" t="n">
         <v>4180781.46</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="D5" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7745,21 +7688,12 @@
         <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6" t="n">
         <v>13054662.21</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.13</v>
       </c>
-      <c r="H6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7768,24 +7702,15 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0</v>
+        <v>-360000</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>76495706.81999999</v>
-      </c>
-      <c r="G7" s="10" t="n">
+        <v>76485706.81999999</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>0.79</v>
       </c>
-      <c r="H7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -7797,21 +7722,12 @@
         <v>0</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6" t="n">
         <v>261238.64</v>
       </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7823,21 +7739,12 @@
         <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
         <v>2959464.86</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="D9" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="H9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7846,227 +7753,298 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>34981900</v>
+        <v>-360000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>61284454</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1035500</v>
+        <v>96941853.98999999</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>96951853.98999999</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9" t="n">
         <v>373487.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Динамика по месяцам (база: строка «Выручка за месяц», кассовый метод)</t>
+          <t>Каналы поступления</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Месяц</t>
+          <t>Канал</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Сумма</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Изменение</t>
+          <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Январь</t>
+          <t>Наличными</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>65706942</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>95732197.48999999</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>0.46</v>
+        <v>34981900</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>касса клиники</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Февраль</t>
+          <t>Безналичными</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>74025535</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>99580226.87</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>0.35</v>
+        <v>62319954</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>карты и онлайн-оплаты (в т.ч. онлайн-оплаты через сайт 1 035 500 ₽)</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Март</t>
+          <t>Возвраты пациентам</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>82158176</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>114153459.7</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>0.39</v>
+        <v>-360000</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>вычитаются из выручки</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Апрель</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>84678135</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>115281361.15</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Май</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>79591558</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>79719174.69</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>96941853.98999999</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Июнь</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>72223764</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>84057781.89</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>69118798.5</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>108126415.72</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>0.5600000000000001</v>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Динамика по месяцам (база: строка «Выручка за месяц», кассовый метод)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Изменение</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
+          <t>Январь</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>65706942</v>
+      </c>
       <c r="C21" s="6" t="n">
-        <v>97707434</v>
-      </c>
-      <c r="D21" s="12" t="n"/>
+        <v>95732197.48999999</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Сентябрь</t>
+          <t>Февраль</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>81488546.61</v>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="12" t="n"/>
+        <v>74025535</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>99580226.87</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Октябрь</t>
+          <t>Март</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>112251113</v>
-      </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="12" t="n"/>
+        <v>82158176</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>114153459.7</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>0.39</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Ноябрь</t>
+          <t>Апрель</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>99764489.61</v>
-      </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="12" t="n"/>
+        <v>84678135</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>115281361.15</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>79591558</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>79719174.69</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>72223764</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>84057781.89</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>69118798.5</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>108126415.72</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n">
+        <v>97707434</v>
+      </c>
+      <c r="D28" s="12" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Сентябрь</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>81488546.61</v>
+      </c>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="12" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Октябрь</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>112251113</v>
+      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ноябрь</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>99764489.61</v>
+      </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B32" s="6" t="n">
         <v>86073459.34</v>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11539,7 +11517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11634,13 +11612,13 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>38247853.41</v>
+        <v>38242853.41</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>38247853.41</v>
+        <v>38242853.41</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>76495706.81999999</v>
+        <v>76485706.81999999</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -11748,7 +11726,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>½ всех расходов + личные анализы</t>
+          <t>½ всех расходов месяца; личные анализы (Маланичев 30 620, Погосян 12 248) каждый несёт полностью — переносится половина разницы</t>
         </is>
       </c>
     </row>
@@ -11915,72 +11893,76 @@
       <c r="F19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      личные анализы (сверх деления 50/50)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>-9186</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>9186</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>лист «Расходы врачей»: Маланичев 30 620, Погосян 12 248</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>ДОХОД ЗА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>-366263.75</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>8525989</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>8159725.25</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>сумма шагов выше</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>ДОХОД ЗА МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>-361263.75</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>8530989</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>8169725.25</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>сумма шагов выше</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>+ Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>45275972.21</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>75934868.23</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>+ Остаток с прошлого месяца</t>
+          <t>− Выплачены дивиденды</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>30658896.02</v>
+        <v>-5882353</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>45275972.21</v>
+        <v>-5882353</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>75934868.23</v>
+        <v>-11764706</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -11989,52 +11971,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>− Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>-11764706</v>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
-        <v>24415279.27</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>47924608.21</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>72339887.48</v>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="C23" s="9" t="n">
+        <v>24410279.27</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>47919608.21</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>72329887.48</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>доход + остаток − дивиденды − резерв</t>
         </is>
@@ -12112,10 +12068,10 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>96951853.98999999</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>100</v>
@@ -12134,7 +12090,7 @@
         <v>-39819623</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>57132230.99</v>
+        <v>57122230.99</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>41.1</v>
@@ -12153,7 +12109,7 @@
         <v>-16182175.49</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>40950055.5</v>
+        <v>40940055.5</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>16.7</v>
@@ -12172,7 +12128,7 @@
         <v>-18665350.79</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>22284704.71</v>
+        <v>22274704.71</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>19.3</v>
@@ -12191,7 +12147,7 @@
         <v>-13276249.56</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9008455.15</v>
+        <v>8998455.15</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>13.7</v>
@@ -12210,7 +12166,7 @@
         <v>-516000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>8492455.15</v>
+        <v>8482455.15</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0.5</v>
@@ -12229,7 +12185,7 @@
         <v>-719067.16</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>7773387.99</v>
+        <v>7763387.99</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0.7</v>
@@ -12248,7 +12204,7 @@
         <v>396337.24</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8169725.23</v>
+        <v>8159725.23</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>0.4</v>
@@ -12264,10 +12220,10 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>8169725.23</v>
+        <v>8159725.23</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>8169725.23</v>
+        <v>8159725.23</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>8.4</v>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,12 +141,18 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -802,7 +808,7 @@
       <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -824,7 +830,7 @@
       <c r="D6" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -846,7 +852,7 @@
       <c r="D7" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -872,7 +878,7 @@
       <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -894,7 +900,7 @@
       <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -916,7 +922,7 @@
       <c r="D10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -942,7 +948,7 @@
       <c r="D11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -964,7 +970,7 @@
       <c r="D12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>справочно</t>
         </is>
@@ -1038,7 +1044,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -1046,7 +1052,7 @@
       <c r="B5" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1063,7 +1069,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -1071,7 +1077,7 @@
       <c r="B6" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1088,7 +1094,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -1096,7 +1102,7 @@
       <c r="B7" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1113,7 +1119,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -1121,7 +1127,7 @@
       <c r="B8" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1138,7 +1144,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -1146,7 +1152,7 @@
       <c r="B9" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1163,7 +1169,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -1171,7 +1177,7 @@
       <c r="B10" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1188,7 +1194,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -1196,7 +1202,7 @@
       <c r="B11" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1213,7 +1219,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -1221,7 +1227,7 @@
       <c r="B12" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1238,7 +1244,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -1246,7 +1252,7 @@
       <c r="B13" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1263,7 +1269,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -1271,7 +1277,7 @@
       <c r="B14" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1288,7 +1294,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -1296,7 +1302,7 @@
       <c r="B15" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1313,7 +1319,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -1321,7 +1327,7 @@
       <c r="B16" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1338,7 +1344,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -1346,7 +1352,7 @@
       <c r="B17" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1363,7 +1369,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -1371,7 +1377,7 @@
       <c r="B18" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1388,7 +1394,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -1396,7 +1402,7 @@
       <c r="B19" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1413,7 +1419,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -1421,7 +1427,7 @@
       <c r="B20" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1438,7 +1444,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -1446,7 +1452,7 @@
       <c r="B21" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1463,7 +1469,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -1471,7 +1477,7 @@
       <c r="B22" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1488,7 +1494,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -1496,7 +1502,7 @@
       <c r="B23" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1513,7 +1519,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -1521,7 +1527,7 @@
       <c r="B24" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1538,7 +1544,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -1546,7 +1552,7 @@
       <c r="B25" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1563,7 +1569,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -1571,7 +1577,7 @@
       <c r="B26" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1588,7 +1594,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -1596,7 +1602,7 @@
       <c r="B27" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1613,7 +1619,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -1621,7 +1627,7 @@
       <c r="B28" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1638,7 +1644,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -1646,7 +1652,7 @@
       <c r="B29" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1663,7 +1669,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -1671,7 +1677,7 @@
       <c r="B30" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1688,7 +1694,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -1696,7 +1702,7 @@
       <c r="B31" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1713,7 +1719,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -1721,7 +1727,7 @@
       <c r="B32" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1738,7 +1744,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -1746,7 +1752,7 @@
       <c r="B33" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1763,7 +1769,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -1771,7 +1777,7 @@
       <c r="B34" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1788,7 +1794,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -1796,7 +1802,7 @@
       <c r="B35" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1813,7 +1819,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -1821,7 +1827,7 @@
       <c r="B36" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1838,7 +1844,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -1846,7 +1852,7 @@
       <c r="B37" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1863,7 +1869,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -1871,7 +1877,7 @@
       <c r="B38" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1888,7 +1894,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -1896,7 +1902,7 @@
       <c r="B39" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1913,7 +1919,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -1921,7 +1927,7 @@
       <c r="B40" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1938,7 +1944,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -1946,7 +1952,7 @@
       <c r="B41" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1963,7 +1969,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -1971,7 +1977,7 @@
       <c r="B42" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1988,7 +1994,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="24" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -1996,7 +2002,7 @@
       <c r="B43" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2013,7 +2019,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -2021,7 +2027,7 @@
       <c r="B44" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2038,7 +2044,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="24" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -2046,7 +2052,7 @@
       <c r="B45" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C45" s="22" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2063,7 +2069,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="24" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -2071,7 +2077,7 @@
       <c r="B46" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2088,7 +2094,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -2096,7 +2102,7 @@
       <c r="B47" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C47" s="22" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2113,7 +2119,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="24" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -2121,7 +2127,7 @@
       <c r="B48" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C48" s="22" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2138,7 +2144,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="24" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -2146,7 +2152,7 @@
       <c r="B49" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C49" s="22" t="inlineStr">
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2163,7 +2169,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -2171,7 +2177,7 @@
       <c r="B50" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C50" s="22" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2188,7 +2194,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -2196,7 +2202,7 @@
       <c r="B51" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2213,7 +2219,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="24" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -2221,7 +2227,7 @@
       <c r="B52" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C52" s="22" t="inlineStr">
+      <c r="C52" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2238,7 +2244,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -2246,7 +2252,7 @@
       <c r="B53" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C53" s="22" t="inlineStr">
+      <c r="C53" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2263,7 +2269,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="24" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -2271,7 +2277,7 @@
       <c r="B54" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C54" s="22" t="inlineStr">
+      <c r="C54" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2288,7 +2294,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -2296,7 +2302,7 @@
       <c r="B55" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C55" s="22" t="inlineStr">
+      <c r="C55" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2313,7 +2319,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="inlineStr">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -2321,7 +2327,7 @@
       <c r="B56" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C56" s="22" t="inlineStr">
+      <c r="C56" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2338,7 +2344,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="inlineStr">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -2346,7 +2352,7 @@
       <c r="B57" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C57" s="22" t="inlineStr">
+      <c r="C57" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2363,7 +2369,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="inlineStr">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -2371,7 +2377,7 @@
       <c r="B58" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C58" s="22" t="inlineStr">
+      <c r="C58" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2388,7 +2394,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+      <c r="A59" s="24" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -2396,7 +2402,7 @@
       <c r="B59" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C59" s="22" t="inlineStr">
+      <c r="C59" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2413,7 +2419,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="inlineStr">
+      <c r="A60" s="24" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -2421,7 +2427,7 @@
       <c r="B60" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C60" s="22" t="inlineStr">
+      <c r="C60" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2438,7 +2444,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="inlineStr">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -2446,7 +2452,7 @@
       <c r="B61" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C61" s="22" t="inlineStr">
+      <c r="C61" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2463,7 +2469,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="inlineStr">
+      <c r="A62" s="24" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -2471,7 +2477,7 @@
       <c r="B62" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C62" s="22" t="inlineStr">
+      <c r="C62" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2488,7 +2494,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="inlineStr">
+      <c r="A63" s="24" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -2496,7 +2502,7 @@
       <c r="B63" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C63" s="22" t="inlineStr">
+      <c r="C63" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2513,7 +2519,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="24" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -2521,7 +2527,7 @@
       <c r="B64" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C64" s="22" t="inlineStr">
+      <c r="C64" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2538,7 +2544,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="inlineStr">
+      <c r="A65" s="24" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -2546,7 +2552,7 @@
       <c r="B65" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C65" s="22" t="inlineStr">
+      <c r="C65" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2563,7 +2569,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="inlineStr">
+      <c r="A66" s="24" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -2571,7 +2577,7 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="22" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2588,7 +2594,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="inlineStr">
+      <c r="A67" s="24" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -2596,7 +2602,7 @@
       <c r="B67" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="C67" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2613,7 +2619,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="inlineStr">
+      <c r="A68" s="24" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -2621,7 +2627,7 @@
       <c r="B68" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C68" s="22" t="inlineStr">
+      <c r="C68" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2638,7 +2644,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="inlineStr">
+      <c r="A69" s="24" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -2646,7 +2652,7 @@
       <c r="B69" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C69" s="22" t="inlineStr">
+      <c r="C69" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2663,7 +2669,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="inlineStr">
+      <c r="A70" s="24" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -2671,7 +2677,7 @@
       <c r="B70" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C70" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2688,7 +2694,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="inlineStr">
+      <c r="A71" s="24" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -2696,7 +2702,7 @@
       <c r="B71" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C71" s="22" t="inlineStr">
+      <c r="C71" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2713,7 +2719,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="22" t="inlineStr">
+      <c r="A72" s="24" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -2721,7 +2727,7 @@
       <c r="B72" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C72" s="22" t="inlineStr">
+      <c r="C72" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2738,7 +2744,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="22" t="inlineStr">
+      <c r="A73" s="24" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -2746,7 +2752,7 @@
       <c r="B73" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C73" s="22" t="inlineStr">
+      <c r="C73" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2763,7 +2769,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="inlineStr">
+      <c r="A74" s="24" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -2771,7 +2777,7 @@
       <c r="B74" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C74" s="22" t="inlineStr">
+      <c r="C74" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2788,7 +2794,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="22" t="inlineStr">
+      <c r="A75" s="24" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -2796,7 +2802,7 @@
       <c r="B75" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C75" s="22" t="inlineStr">
+      <c r="C75" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2813,7 +2819,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -2821,7 +2827,7 @@
       <c r="B76" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C76" s="22" t="inlineStr">
+      <c r="C76" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2838,7 +2844,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="inlineStr">
+      <c r="A77" s="24" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -2846,7 +2852,7 @@
       <c r="B77" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C77" s="22" t="inlineStr">
+      <c r="C77" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2863,7 +2869,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="22" t="inlineStr">
+      <c r="A78" s="24" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -2871,7 +2877,7 @@
       <c r="B78" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C78" s="22" t="inlineStr">
+      <c r="C78" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2888,7 +2894,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="inlineStr">
+      <c r="A79" s="24" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -2896,7 +2902,7 @@
       <c r="B79" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C79" s="22" t="inlineStr">
+      <c r="C79" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2913,7 +2919,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="inlineStr">
+      <c r="A80" s="24" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -2921,7 +2927,7 @@
       <c r="B80" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C80" s="22" t="inlineStr">
+      <c r="C80" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2938,7 +2944,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="22" t="inlineStr">
+      <c r="A81" s="24" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -2946,7 +2952,7 @@
       <c r="B81" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C81" s="22" t="inlineStr">
+      <c r="C81" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2963,7 +2969,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="22" t="inlineStr">
+      <c r="A82" s="24" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -2971,7 +2977,7 @@
       <c r="B82" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C82" s="22" t="inlineStr">
+      <c r="C82" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2988,7 +2994,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="inlineStr">
+      <c r="A83" s="24" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -2996,7 +3002,7 @@
       <c r="B83" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C83" s="22" t="inlineStr">
+      <c r="C83" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3013,7 +3019,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="22" t="inlineStr">
+      <c r="A84" s="24" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -3021,7 +3027,7 @@
       <c r="B84" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C84" s="22" t="inlineStr">
+      <c r="C84" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3038,7 +3044,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="inlineStr">
+      <c r="A85" s="24" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -3046,7 +3052,7 @@
       <c r="B85" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C85" s="22" t="inlineStr">
+      <c r="C85" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3063,7 +3069,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="22" t="inlineStr">
+      <c r="A86" s="24" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -3071,7 +3077,7 @@
       <c r="B86" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C86" s="22" t="inlineStr">
+      <c r="C86" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3088,7 +3094,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="22" t="inlineStr">
+      <c r="A87" s="24" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -3096,7 +3102,7 @@
       <c r="B87" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C87" s="22" t="inlineStr">
+      <c r="C87" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3113,7 +3119,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="inlineStr">
+      <c r="A88" s="24" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -3121,7 +3127,7 @@
       <c r="B88" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C88" s="22" t="inlineStr">
+      <c r="C88" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3138,7 +3144,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="22" t="inlineStr">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -3146,7 +3152,7 @@
       <c r="B89" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C89" s="22" t="inlineStr">
+      <c r="C89" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3163,7 +3169,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="inlineStr">
+      <c r="A90" s="24" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -3171,7 +3177,7 @@
       <c r="B90" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C90" s="22" t="inlineStr">
+      <c r="C90" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3188,7 +3194,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="22" t="inlineStr">
+      <c r="A91" s="24" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -3196,7 +3202,7 @@
       <c r="B91" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C91" s="22" t="inlineStr">
+      <c r="C91" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3213,7 +3219,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="22" t="inlineStr">
+      <c r="A92" s="24" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -3221,7 +3227,7 @@
       <c r="B92" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C92" s="22" t="inlineStr">
+      <c r="C92" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3238,7 +3244,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="inlineStr">
+      <c r="A93" s="24" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -3246,7 +3252,7 @@
       <c r="B93" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C93" s="22" t="inlineStr">
+      <c r="C93" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3263,7 +3269,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="22" t="inlineStr">
+      <c r="A94" s="24" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -3271,7 +3277,7 @@
       <c r="B94" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C94" s="22" t="inlineStr">
+      <c r="C94" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3288,7 +3294,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="22" t="inlineStr">
+      <c r="A95" s="24" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -3296,7 +3302,7 @@
       <c r="B95" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C95" s="22" t="inlineStr">
+      <c r="C95" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3313,7 +3319,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="22" t="inlineStr">
+      <c r="A96" s="24" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -3321,7 +3327,7 @@
       <c r="B96" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C96" s="22" t="inlineStr">
+      <c r="C96" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3338,7 +3344,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="22" t="inlineStr">
+      <c r="A97" s="24" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -3346,7 +3352,7 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="22" t="inlineStr">
+      <c r="C97" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3363,7 +3369,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="inlineStr">
+      <c r="A98" s="24" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -3371,7 +3377,7 @@
       <c r="B98" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C98" s="22" t="inlineStr">
+      <c r="C98" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3388,7 +3394,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="22" t="inlineStr">
+      <c r="A99" s="24" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -3396,7 +3402,7 @@
       <c r="B99" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C99" s="22" t="inlineStr">
+      <c r="C99" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3413,7 +3419,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="22" t="inlineStr">
+      <c r="A100" s="24" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -3421,7 +3427,7 @@
       <c r="B100" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C100" s="22" t="inlineStr">
+      <c r="C100" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3438,7 +3444,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="22" t="inlineStr">
+      <c r="A101" s="24" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -3446,7 +3452,7 @@
       <c r="B101" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C101" s="22" t="inlineStr">
+      <c r="C101" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3463,7 +3469,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="22" t="inlineStr">
+      <c r="A102" s="24" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -3471,7 +3477,7 @@
       <c r="B102" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C102" s="22" t="inlineStr">
+      <c r="C102" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3488,7 +3494,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="22" t="inlineStr">
+      <c r="A103" s="24" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -3496,7 +3502,7 @@
       <c r="B103" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C103" s="22" t="inlineStr">
+      <c r="C103" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3513,7 +3519,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="22" t="inlineStr">
+      <c r="A104" s="24" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -3521,7 +3527,7 @@
       <c r="B104" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C104" s="22" t="inlineStr">
+      <c r="C104" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3538,7 +3544,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="22" t="inlineStr">
+      <c r="A105" s="24" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -3546,7 +3552,7 @@
       <c r="B105" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C105" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3563,7 +3569,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="22" t="inlineStr">
+      <c r="A106" s="24" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -3571,7 +3577,7 @@
       <c r="B106" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C106" s="22" t="inlineStr">
+      <c r="C106" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3588,7 +3594,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="22" t="inlineStr">
+      <c r="A107" s="24" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -3596,7 +3602,7 @@
       <c r="B107" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C107" s="22" t="inlineStr">
+      <c r="C107" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3613,7 +3619,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="22" t="inlineStr">
+      <c r="A108" s="24" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -3621,7 +3627,7 @@
       <c r="B108" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C108" s="22" t="inlineStr">
+      <c r="C108" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3638,7 +3644,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="22" t="inlineStr">
+      <c r="A109" s="24" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -3646,7 +3652,7 @@
       <c r="B109" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C109" s="22" t="inlineStr">
+      <c r="C109" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3663,7 +3669,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="22" t="inlineStr">
+      <c r="A110" s="24" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -3671,7 +3677,7 @@
       <c r="B110" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C110" s="22" t="inlineStr">
+      <c r="C110" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3688,7 +3694,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="22" t="inlineStr">
+      <c r="A111" s="24" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -3696,7 +3702,7 @@
       <c r="B111" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C111" s="22" t="inlineStr">
+      <c r="C111" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3713,7 +3719,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="22" t="inlineStr">
+      <c r="A112" s="24" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -3721,7 +3727,7 @@
       <c r="B112" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C112" s="22" t="inlineStr">
+      <c r="C112" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3738,7 +3744,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="22" t="inlineStr">
+      <c r="A113" s="24" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -3746,7 +3752,7 @@
       <c r="B113" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C113" s="22" t="inlineStr">
+      <c r="C113" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3763,7 +3769,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="22" t="inlineStr">
+      <c r="A114" s="24" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -3771,7 +3777,7 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="22" t="inlineStr">
+      <c r="C114" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3788,7 +3794,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="22" t="inlineStr">
+      <c r="A115" s="24" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -3796,7 +3802,7 @@
       <c r="B115" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C115" s="22" t="inlineStr">
+      <c r="C115" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3813,7 +3819,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="22" t="inlineStr">
+      <c r="A116" s="24" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -3821,7 +3827,7 @@
       <c r="B116" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C116" s="22" t="inlineStr">
+      <c r="C116" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3838,7 +3844,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="22" t="inlineStr">
+      <c r="A117" s="24" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -3846,7 +3852,7 @@
       <c r="B117" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C117" s="22" t="inlineStr">
+      <c r="C117" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3863,7 +3869,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="22" t="inlineStr">
+      <c r="A118" s="24" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -3871,7 +3877,7 @@
       <c r="B118" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C118" s="22" t="inlineStr">
+      <c r="C118" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3888,7 +3894,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="22" t="inlineStr">
+      <c r="A119" s="24" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -3896,7 +3902,7 @@
       <c r="B119" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C119" s="22" t="inlineStr">
+      <c r="C119" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3913,7 +3919,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="22" t="inlineStr">
+      <c r="A120" s="24" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -3921,7 +3927,7 @@
       <c r="B120" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C120" s="22" t="inlineStr">
+      <c r="C120" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3938,7 +3944,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="22" t="inlineStr">
+      <c r="A121" s="24" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -3946,7 +3952,7 @@
       <c r="B121" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C121" s="22" t="inlineStr">
+      <c r="C121" s="24" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3963,7 +3969,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="22" t="inlineStr">
+      <c r="A122" s="24" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -3971,7 +3977,7 @@
       <c r="B122" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C122" s="22" t="inlineStr">
+      <c r="C122" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3988,7 +3994,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="22" t="inlineStr">
+      <c r="A123" s="24" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -3996,7 +4002,7 @@
       <c r="B123" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C123" s="22" t="inlineStr">
+      <c r="C123" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4013,7 +4019,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="22" t="inlineStr">
+      <c r="A124" s="24" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -4021,7 +4027,7 @@
       <c r="B124" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C124" s="22" t="inlineStr">
+      <c r="C124" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4038,7 +4044,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="22" t="inlineStr">
+      <c r="A125" s="24" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -4046,7 +4052,7 @@
       <c r="B125" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C125" s="22" t="inlineStr">
+      <c r="C125" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4063,7 +4069,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="22" t="inlineStr">
+      <c r="A126" s="24" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -4071,7 +4077,7 @@
       <c r="B126" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C126" s="22" t="inlineStr">
+      <c r="C126" s="24" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4088,7 +4094,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="23" t="inlineStr">
+      <c r="A127" s="25" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4096,9 +4102,9 @@
       <c r="B127" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C127" s="23" t="inlineStr"/>
-      <c r="D127" s="16" t="inlineStr"/>
-      <c r="E127" s="16" t="inlineStr"/>
+      <c r="C127" s="25" t="inlineStr"/>
+      <c r="D127" s="18" t="inlineStr"/>
+      <c r="E127" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4157,7 +4163,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -4173,7 +4179,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Налоги с ФОТ</t>
         </is>
@@ -4189,7 +4195,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -4205,7 +4211,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Расходы по кассе</t>
         </is>
@@ -4221,7 +4227,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Услуги банка (общие)</t>
         </is>
@@ -4237,7 +4243,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Эквайринг</t>
         </is>
@@ -4253,7 +4259,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -4269,7 +4275,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>% по кредиту</t>
         </is>
@@ -4285,7 +4291,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Поставщики (счёт 60)</t>
         </is>
@@ -4301,23 +4307,23 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="16" t="n">
         <v>72553130.98</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="16" t="n">
         <v>89178466</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="16" t="n">
         <v>16625335.02</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>ДОХОД (выручка − расходы)</t>
         </is>
@@ -4362,7 +4368,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -4378,7 +4384,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр.1</t>
         </is>
@@ -4394,7 +4400,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
@@ -4410,7 +4416,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Досудебный спор</t>
         </is>
@@ -4426,7 +4432,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Прочие поставщики</t>
         </is>
@@ -4442,7 +4448,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4510,7 +4516,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>01–10.08, старая управленка</t>
         </is>
@@ -4518,14 +4524,14 @@
       <c r="B5" s="6" t="n">
         <v>31243514</v>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>реестр «Оплаты от пациента» без двух документов, помеченных на удаление; сходится с «Ежедневным отчётом по кассам»</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>11–31.08, новая управленка</t>
         </is>
@@ -4533,14 +4539,14 @@
       <c r="B6" s="6" t="n">
         <v>66058340</v>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными», уже за вычетом возвратов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Возвраты пациентам, 01–10.08</t>
         </is>
@@ -4548,14 +4554,14 @@
       <c r="B7" s="6" t="n">
         <v>-360000</v>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>колонка «Возврат денег» «Ежедневного отчёта по кассам»</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
@@ -4563,19 +4569,19 @@
       <c r="B8" s="9" t="n">
         <v>96941854</v>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>деньги, поступившие за месяц</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr"/>
+      <c r="A9" s="24" t="inlineStr"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="22" t="inlineStr"/>
+      <c r="C9" s="24" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>01–10.08: платежи с указанным специалистом</t>
         </is>
@@ -4583,14 +4589,14 @@
       <c r="B10" s="6" t="n">
         <v>30534014</v>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>колонка «Специалист» реестра платежей</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>01–10.08: без специалиста</t>
         </is>
@@ -4598,14 +4604,14 @@
       <c r="B11" s="6" t="n">
         <v>709500</v>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>разнесены по врачам того же пациента, остаток — пропорционально</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>11–31.08: привязано к врачу напрямую</t>
         </is>
@@ -4613,14 +4619,14 @@
       <c r="B12" s="6" t="n">
         <v>46401840</v>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>документы «Оказание услуг» — врач указан в документе</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>11–31.08: авансы, разнесённые через пациента</t>
         </is>
@@ -4628,14 +4634,14 @@
       <c r="B13" s="6" t="n">
         <v>14588000</v>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>оплата картой и кассовые ордера</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>11–31.08: авансы без совпадения по пациенту</t>
         </is>
@@ -4643,7 +4649,7 @@
       <c r="B14" s="6" t="n">
         <v>5068500</v>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>разнесены пропорционально; пациентов нет в реестре услуг августа</t>
         </is>
@@ -4677,7 +4683,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -4691,12 +4697,12 @@
       <c r="D17" s="6" t="n">
         <v>4180781.46</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="13" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -4710,12 +4716,12 @@
       <c r="D18" s="6" t="n">
         <v>13054662.21</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="13" t="n">
         <v>0.13</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
@@ -4729,12 +4735,12 @@
       <c r="D19" s="6" t="n">
         <v>76485706.81999999</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="13" t="n">
         <v>0.79</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -4748,12 +4754,12 @@
       <c r="D20" s="6" t="n">
         <v>261238.64</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -4767,12 +4773,12 @@
       <c r="D21" s="6" t="n">
         <v>2959464.86</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="13" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4786,7 +4792,7 @@
       <c r="D22" s="9" t="n">
         <v>96941853.98999999</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4801,7 +4807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5189,7 +5195,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>62319954</v>
+        <v>61959954</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -5198,7 +5204,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>оборот сч. 57.03: розница и интернет-эквайринг</t>
+          <t>оборот сч. 57.03: розница и интернет-эквайринг, за вычетом возвратов</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -5215,11 +5221,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Возвраты пациентам</t>
+          <t>Комиссия эквайринга</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>-360000</v>
+        <v>373487.16</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -5228,28 +5234,28 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>строка «возврат пациенту ч/з банк и кассу»</t>
+          <t>сумма комиссий по группам врачей</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>ВЫРУЧКА, лист «Август 2026», справочный блок «услуги Банка в Отчет»</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Структура</t>
+          <t>Расходы</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
+          <t>Медицинские расходы + ИП</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>373487.16</v>
+        <v>56001798.49</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -5258,12 +5264,12 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>сумма комиссий по группам врачей</t>
+          <t>итог блока «МЕДИЦИНСКИЕ РАСХОДЫ+ИП»</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>ВЫРУЧКА, лист «Август 2026», справочный блок «услуги Банка в Отчет»</t>
+          <t>РАСХОДЫ (Обороты сч. 60), лист 1, колонки E–F</t>
         </is>
       </c>
     </row>
@@ -5275,11 +5281,11 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Медицинские расходы + ИП</t>
+          <t>Управленческие расходы</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>56001798.49</v>
+        <v>13792249.56</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -5288,7 +5294,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>итог блока «МЕДИЦИНСКИЕ РАСХОДЫ+ИП»</t>
+          <t>итог блока «УПРАВЛЕНЧЕСКИЕ РАСХОДЫ»</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -5305,11 +5311,11 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Управленческие расходы</t>
+          <t>в т.ч. гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13792249.56</v>
+        <v>39819623</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -5318,12 +5324,12 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>итог блока «УПРАВЛЕНЧЕСКИЕ РАСХОДЫ»</t>
+          <t>статья «ИП хирурги» медицинского блока</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>РАСХОДЫ (Обороты сч. 60), лист 1, колонки E–F</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5335,11 +5341,11 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>в т.ч. гонорары ИП хирургов</t>
+          <t>в т.ч. ремонт нового корпуса</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>39819623</v>
+        <v>516000</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -5348,28 +5354,28 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>статья «ИП хирурги» медицинского блока</t>
+          <t>статья «Ремонт Самокатная 1 стр.12»</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>РАСХОДЫ (Обороты сч. 60), лист 1, управленческий блок</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Расходы</t>
+          <t>Экономика</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>в т.ч. ремонт нового корпуса</t>
+          <t>Доход месяца (итог водопада)</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>516000</v>
+        <v>8159725.23</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -5378,28 +5384,28 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>статья «Ремонт Самокатная 1 стр.12»</t>
+          <t>выручка − все статьи расходов по шагам водопада</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>РАСХОДЫ (Обороты сч. 60), лист 1, управленческий блок</t>
+          <t>лист «08 Водопад»</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>ДДС</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Доход месяца (итог водопада)</t>
+          <t>Остаток на начало месяца</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>8159725.23</v>
+        <v>2691202.95</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -5408,12 +5414,12 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>выручка − все статьи расходов по шагам водопада</t>
+          <t>начальное сальдо сч. 51</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>лист «08 Водопад»</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5425,11 +5431,11 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Остаток на начало месяца</t>
+          <t>Поступления за месяц</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>2691202.95</v>
+        <v>674932579.65</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -5438,7 +5444,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>начальное сальдо сч. 51</t>
+          <t>оборот по дебету сч. 51</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -5455,11 +5461,11 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Поступления за месяц</t>
+          <t>Списания за месяц</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>674932579.65</v>
+        <v>658588463.84</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
@@ -5468,7 +5474,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>оборот по дебету сч. 51</t>
+          <t>оборот по кредиту сч. 51</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -5485,11 +5491,11 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Списания за месяц</t>
+          <t>Остаток на конец месяца</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>658588463.84</v>
+        <v>19035318.76</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -5498,7 +5504,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>оборот по кредиту сч. 51</t>
+          <t>конечное сальдо сч. 51</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -5510,16 +5516,16 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>ДДС</t>
+          <t>Учредители</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Остаток на конец месяца</t>
+          <t>Маланичев: личная выручка</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>19035318.76</v>
+        <v>4180781.46</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -5528,7 +5534,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>конечное сальдо сч. 51</t>
+          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -5545,11 +5551,11 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: личная выручка</t>
+          <t>Маланичев: ½ выручки других хирургов</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>4180781.46</v>
+        <v>38242853.41</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -5558,7 +5564,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
+          <t>выручка «Другие хирурги» / 2</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -5575,11 +5581,11 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: ½ выручки других хирургов</t>
+          <t>Маланичев: ½ косметологии и прочего</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>38242853.41</v>
+        <v>1610351.75</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -5588,7 +5594,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>выручка «Другие хирурги» / 2</t>
+          <t>(косметология + прочие доходы) / 2</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -5605,11 +5611,11 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: ½ косметологии и прочего</t>
+          <t>Маланичев: доля расходов</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1610351.75</v>
+        <v>-44598418.99</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5618,7 +5624,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>(косметология + прочие доходы) / 2</t>
+          <t>½ всех расходов месяца + личные анализы учредителя</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -5635,11 +5641,11 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: доля расходов</t>
+          <t>Маланичев: доход за месяц</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-44598418.99</v>
+        <v>-366263.75</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -5648,12 +5654,12 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>½ всех расходов месяца + личные анализы учредителя</t>
+          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>лист «07 Учредители»</t>
         </is>
       </c>
     </row>
@@ -5665,11 +5671,11 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: доход за месяц</t>
+          <t>Маланичев: остаток с прошлого месяца</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-366263.75</v>
+        <v>30658896.02</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -5678,12 +5684,12 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
+          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>лист «07 Учредители»</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
         </is>
       </c>
     </row>
@@ -5695,11 +5701,11 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: остаток с прошлого месяца</t>
+          <t>Маланичев: удержано в резерв (аренда)</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>30658896.02</v>
+        <v>0</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -5708,12 +5714,12 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
+          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5725,11 +5731,11 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: удержано в резерв (аренда)</t>
+          <t>Маланичев: к выплате на конец месяца</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0</v>
+        <v>24410279.27</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -5738,7 +5744,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
+          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -5755,11 +5761,11 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Маланичев: к выплате на конец месяца</t>
+          <t>Погосян: личная выручка</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>24410279.27</v>
+        <v>13054662.21</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -5768,7 +5774,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
+          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -5785,11 +5791,11 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Погосян: личная выручка</t>
+          <t>Погосян: ½ выручки других хирургов</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>13054662.21</v>
+        <v>38242853.41</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -5798,7 +5804,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>выручка своей группы (касса + эквайринг + р/с − возвраты)</t>
+          <t>выручка «Другие хирурги» / 2</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -5815,11 +5821,11 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Погосян: ½ выручки других хирургов</t>
+          <t>Погосян: ½ косметологии и прочего</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>38242853.41</v>
+        <v>1610351.75</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -5828,7 +5834,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>выручка «Другие хирурги» / 2</t>
+          <t>(косметология + прочие доходы) / 2</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -5845,11 +5851,11 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Погосян: ½ косметологии и прочего</t>
+          <t>Погосян: доля расходов</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1610351.75</v>
+        <v>-44580046.99</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5858,7 +5864,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>(косметология + прочие доходы) / 2</t>
+          <t>½ всех расходов месяца + личные анализы учредителя</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -5875,11 +5881,11 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Погосян: доля расходов</t>
+          <t>Погосян: доход за месяц</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>-44580046.99</v>
+        <v>8525989</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -5888,12 +5894,12 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>½ всех расходов месяца + личные анализы учредителя</t>
+          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
+          <t>лист «07 Учредители»</t>
         </is>
       </c>
     </row>
@@ -5905,11 +5911,11 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Погосян: доход за месяц</t>
+          <t>Погосян: остаток с прошлого месяца</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>8525989</v>
+        <v>45275972.21</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -5918,12 +5924,12 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>личная выручка − доля расходов + ½ др.хирургов + ½ косметологии + ½ прочего</t>
+          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>лист «07 Учредители»</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
         </is>
       </c>
     </row>
@@ -5935,11 +5941,11 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Погосян: остаток с прошлого месяца</t>
+          <t>Погосян: удержано в резерв (аренда)</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>45275972.21</v>
+        <v>0</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -5948,12 +5954,12 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (переносящийся долг компании)</t>
+          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet, стр. None</t>
+          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
       </c>
     </row>
@@ -5965,11 +5971,11 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Погосян: удержано в резерв (аренда)</t>
+          <t>Погосян: к выплате на конец месяца</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>0</v>
+        <v>47919608.21</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -5978,7 +5984,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии (депозит под аренду)</t>
+          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -5990,16 +5996,16 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Учредители</t>
+          <t>Справочно</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Погосян: к выплате на конец месяца</t>
+          <t>Долг по кредитной линии</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>47919608.21</v>
+        <v>27545367</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
@@ -6008,7 +6014,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>доход за месяц + остаток с прошлого месяца − резерв</t>
+          <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -6025,12 +6031,10 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Долг по кредитной линии</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>27545367</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
           <t>₽</t>
@@ -6055,10 +6059,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n"/>
+          <t>Проценты по депозитам</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>396337.24</v>
+      </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
           <t>₽</t>
@@ -6066,7 +6072,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии</t>
+          <t>оборот сч. 91.01 «% по депозитам»</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -6083,11 +6089,11 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Проценты по депозитам</t>
+          <t>Зарезервировано на аренду (всего)</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>396337.24</v>
+        <v>0</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
@@ -6096,40 +6102,10 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>оборот сч. 91.01 «% по депозитам»</t>
+          <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>БАНК (Анализ сч. 51), лист TDSheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Справочно</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Зарезервировано на аренду (всего)</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>₽</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>БАНК (Анализ сч. 51), лист TDSheet</t>
         </is>
@@ -7610,14 +7586,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7630,7 +7605,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Итог = касса + эквайринг (карты и онлайн-оплаты) − возвраты</t>
+          <t>Итог = касса + эквайринг (карты и онлайн-оплаты), за вычетом возвратов</t>
         </is>
       </c>
     </row>
@@ -7642,20 +7617,15 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Возвраты</t>
+          <t>Итого</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Итого</t>
+          <t>Доля</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Доля</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Комиссия эквайринга</t>
         </is>
@@ -7668,15 +7638,12 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6" t="n">
         <v>4180781.46</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="C5" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="E5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7685,15 +7652,12 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="n">
         <v>13054662.21</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="C6" s="10" t="n">
         <v>0.13</v>
       </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7702,15 +7666,12 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-360000</v>
-      </c>
-      <c r="C7" s="6" t="n">
         <v>76485706.81999999</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="C7" s="10" t="n">
         <v>0.79</v>
       </c>
-      <c r="E7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -7719,15 +7680,12 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="n">
         <v>261238.64</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="C8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7736,15 +7694,12 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
         <v>2959464.86</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="E9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7753,15 +7708,12 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>-360000</v>
-      </c>
-      <c r="C10" s="9" t="n">
         <v>96941853.98999999</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="C10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="D10" s="9" t="n">
         <v>373487.16</v>
       </c>
     </row>
@@ -7811,201 +7763,198 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>62319954</v>
+        <v>61959954</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>карты и онлайн-оплаты (в т.ч. онлайн-оплаты через сайт 1 035 500 ₽)</t>
+          <t>карты и онлайн-оплаты (в т.ч. онлайн-оплаты через сайт 1 035 500 ₽)  за вычетом возвратов пациентам 360 000 ₽</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Возвраты пациентам</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>-360000</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>вычитаются из выручки</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B16" s="9" t="n">
         <v>96941853.98999999</v>
       </c>
-      <c r="C17" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Динамика по месяцам (база: строка «Выручка за месяц», кассовый метод)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Изменение</t>
         </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Январь</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>65706942</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>95732197.48999999</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Январь</t>
+          <t>Февраль</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>65706942</v>
+        <v>74025535</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>95732197.48999999</v>
+        <v>99580226.87</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.46</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Февраль</t>
+          <t>Март</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>74025535</v>
+        <v>82158176</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>99580226.87</v>
+        <v>114153459.7</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Март</t>
+          <t>Апрель</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>82158176</v>
+        <v>84678135</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>114153459.7</v>
+        <v>115281361.15</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Апрель</t>
+          <t>Май</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>84678135</v>
+        <v>79591558</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>115281361.15</v>
+        <v>79719174.69</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Май</t>
+          <t>Июнь</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>79591558</v>
+        <v>72223764</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>79719174.69</v>
+        <v>84057781.89</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Июнь</t>
+          <t>Июль</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>72223764</v>
+        <v>69118798.5</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>84057781.89</v>
+        <v>108126415.72</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>69118798.5</v>
-      </c>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n">
-        <v>108126415.72</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+        <v>97707434</v>
+      </c>
+      <c r="D27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n">
-        <v>97707434</v>
-      </c>
+          <t>Сентябрь</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>81488546.61</v>
+      </c>
+      <c r="C28" s="6" t="n"/>
       <c r="D28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Сентябрь</t>
+          <t>Октябрь</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>81488546.61</v>
+        <v>112251113</v>
       </c>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="12" t="n"/>
@@ -8013,11 +7962,11 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Октябрь</t>
+          <t>Ноябрь</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>112251113</v>
+        <v>99764489.61</v>
       </c>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="12" t="n"/>
@@ -8025,26 +7974,14 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Ноябрь</t>
+          <t>Декабрь</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>99764489.61</v>
+        <v>86073459.34</v>
       </c>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Декабрь</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>86073459.34</v>
-      </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8109,7 +8046,7 @@
       <c r="C4" s="6" t="n">
         <v>39819623</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="13" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -8127,7 +8064,7 @@
       <c r="C5" s="6" t="n">
         <v>4527900</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="13" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -8145,7 +8082,7 @@
       <c r="C6" s="6" t="n">
         <v>3298432.06</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="13" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -8163,7 +8100,7 @@
       <c r="C7" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="13" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8181,7 +8118,7 @@
       <c r="C8" s="6" t="n">
         <v>2250790.16</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="13" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -8199,7 +8136,7 @@
       <c r="C9" s="6" t="n">
         <v>827352.65</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8217,7 +8154,7 @@
       <c r="C10" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8235,7 +8172,7 @@
       <c r="C11" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8253,7 +8190,7 @@
       <c r="C12" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8271,7 +8208,7 @@
       <c r="C13" s="6" t="n">
         <v>345200</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8289,7 +8226,7 @@
       <c r="C14" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8307,7 +8244,7 @@
       <c r="C15" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8325,7 +8262,7 @@
       <c r="C16" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8343,7 +8280,7 @@
       <c r="C17" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8361,7 +8298,7 @@
       <c r="C18" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8379,7 +8316,7 @@
       <c r="C19" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8397,7 +8334,7 @@
       <c r="C20" s="9" t="n">
         <v>56001798.49</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8415,7 +8352,7 @@
       <c r="C21" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="13" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -8433,7 +8370,7 @@
       <c r="C22" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="13" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -8451,7 +8388,7 @@
       <c r="C23" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="13" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -8469,7 +8406,7 @@
       <c r="C24" s="6" t="n">
         <v>878789.77</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="13" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -8487,7 +8424,7 @@
       <c r="C25" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="13" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -8505,7 +8442,7 @@
       <c r="C26" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="13" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -8523,7 +8460,7 @@
       <c r="C27" s="6" t="n">
         <v>337440</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="13" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8541,7 +8478,7 @@
       <c r="C28" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="13" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8559,7 +8496,7 @@
       <c r="C29" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="13" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8577,7 +8514,7 @@
       <c r="C30" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="13" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8595,7 +8532,7 @@
       <c r="C31" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="13" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8613,7 +8550,7 @@
       <c r="C32" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="13" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8631,7 +8568,7 @@
       <c r="C33" s="6" t="n">
         <v>247935.06</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="13" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8649,7 +8586,7 @@
       <c r="C34" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8667,7 +8604,7 @@
       <c r="C35" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="D35" s="10" t="n">
+      <c r="D35" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8685,7 +8622,7 @@
       <c r="C36" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8703,7 +8640,7 @@
       <c r="C37" s="6" t="n">
         <v>137116</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8721,7 +8658,7 @@
       <c r="C38" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8739,7 +8676,7 @@
       <c r="C39" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8757,7 +8694,7 @@
       <c r="C40" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8775,7 +8712,7 @@
       <c r="C41" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8793,7 +8730,7 @@
       <c r="C42" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="13" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8811,7 +8748,7 @@
       <c r="C43" s="6" t="n">
         <v>53760</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8829,7 +8766,7 @@
       <c r="C44" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8847,7 +8784,7 @@
       <c r="C45" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8865,7 +8802,7 @@
       <c r="C46" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8883,7 +8820,7 @@
       <c r="C47" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D47" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8901,7 +8838,7 @@
       <c r="C48" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8919,7 +8856,7 @@
       <c r="C49" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8937,7 +8874,7 @@
       <c r="C50" s="6" t="n">
         <v>26600</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8955,7 +8892,7 @@
       <c r="C51" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8973,7 +8910,7 @@
       <c r="C52" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8991,7 +8928,7 @@
       <c r="C53" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="D53" s="10" t="n">
+      <c r="D53" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9009,7 +8946,7 @@
       <c r="C54" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="D54" s="10" t="n">
+      <c r="D54" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9027,7 +8964,7 @@
       <c r="C55" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="D55" s="10" t="n">
+      <c r="D55" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9045,7 +8982,7 @@
       <c r="C56" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="D56" s="10" t="n">
+      <c r="D56" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9063,7 +9000,7 @@
       <c r="C57" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="D57" s="10" t="n">
+      <c r="D57" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9081,7 +9018,7 @@
       <c r="C58" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="D58" s="10" t="n">
+      <c r="D58" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9099,7 +9036,7 @@
       <c r="C59" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="D59" s="10" t="n">
+      <c r="D59" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9117,7 +9054,7 @@
       <c r="C60" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="D60" s="10" t="n">
+      <c r="D60" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9135,7 +9072,7 @@
       <c r="C61" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="D61" s="10" t="n">
+      <c r="D61" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9153,7 +9090,7 @@
       <c r="C62" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="D62" s="10" t="n">
+      <c r="D62" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9171,7 +9108,7 @@
       <c r="C63" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="D63" s="10" t="n">
+      <c r="D63" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9189,7 +9126,7 @@
       <c r="C64" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D64" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9207,7 +9144,7 @@
       <c r="C65" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="D65" s="10" t="n">
+      <c r="D65" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9225,7 +9162,7 @@
       <c r="C66" s="6" t="n">
         <v>1218.56</v>
       </c>
-      <c r="D66" s="10" t="n">
+      <c r="D66" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9243,21 +9180,21 @@
       <c r="C67" s="9" t="n">
         <v>13792249.56</v>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D67" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" s="15" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr"/>
-      <c r="C68" s="14" t="n">
+      <c r="B68" s="15" t="inlineStr"/>
+      <c r="C68" s="16" t="n">
         <v>69794048.05</v>
       </c>
-      <c r="D68" s="15" t="n"/>
+      <c r="D68" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11193,16 +11130,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Начальное сальдо</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="16" t="n">
         <v>2691202.95</v>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="15" t="inlineStr"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="17" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -11488,19 +11425,19 @@
       <c r="C22" s="9" t="n">
         <v>658588463.84</v>
       </c>
-      <c r="D22" s="16" t="inlineStr"/>
+      <c r="D22" s="18" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Конечное сальдо</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="16" t="n">
         <v>19035318.76</v>
       </c>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>'= начальное + поступления − списания</t>
         </is>
@@ -11517,7 +11454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11705,28 +11642,28 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>− Доля расходов, в том числе:</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>-44598418.99</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>-44580046.99</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-89178465.98</v>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>½ всех расходов месяца; личные анализы (Маланичев 30 620, Погосян 12 248) каждый несёт полностью — переносится половина разницы</t>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>− ½ общих расходов, в том числе:</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>-44567798.99</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>-44567798.99</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>-89135597.98</v>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>все расходы месяца без личных, пополам</t>
         </is>
       </c>
     </row>
@@ -11893,104 +11830,170 @@
       <c r="F19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      минус личные расходы врачей (вынесены в шаг 7)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>21434</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>21434</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>42868</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>чтобы не делить их пополам</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>ДОХОД ЗА МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>-366263.75</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>8525989</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>8159725.25</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>сумма шагов выше</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>+ Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>45275972.21</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>75934868.23</v>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>− Личные расходы (каждый свои), в том числе:</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>-30620</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>-12248</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>-42868</v>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>заказано лично под врача, пополам не делится</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>− Выплачены дивиденды</t>
+          <t xml:space="preserve">      Анализы</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>-5882353</v>
+        <v>-30620</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>-5882353</v>
+        <v>-12248</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>-11764706</v>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+        <v>-42868</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>ДОХОД ЗА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>-366263.75</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>8525989</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>8159725.25</v>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>сумма шагов выше</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>+ Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>45275972.21</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>75934868.23</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>− Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-11764706</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C26" s="9" t="n">
         <v>24410279.27</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D26" s="9" t="n">
         <v>47919608.21</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E26" s="9" t="n">
         <v>72329887.48</v>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>доход + остаток − дивиденды − резерв</t>
         </is>
@@ -12073,7 +12076,7 @@
       <c r="D5" s="9" t="n">
         <v>96941853.98999999</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="18" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12206,7 +12209,7 @@
       <c r="D12" s="9" t="n">
         <v>8159725.23</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -12225,7 +12228,7 @@
       <c r="D13" s="9" t="n">
         <v>8159725.23</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="18" t="n">
         <v>8.4</v>
       </c>
     </row>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>69794048.05</v>
+        <v>69792829.48999999</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>69794048.05</v>
+        <v>69792829.48999999</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Услуги банка (через счёт 60)</t>
+          <t>Услуги банка</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Услуги банка (через счёт 60)</t>
+          <t>Услуги банка</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
@@ -4236,10 +4236,10 @@
         <v>399308.17</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>141191.07</v>
+        <v>142409.63</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-258117.1</v>
+        <v>-256898.54</v>
       </c>
     </row>
     <row r="10">
@@ -4300,10 +4300,10 @@
         <v>53416727.72</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>69794048.05</v>
+        <v>69792829.48999999</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>16377320.33</v>
+        <v>16376101.77</v>
       </c>
     </row>
     <row r="14">
@@ -4441,10 +4441,10 @@
         <v>23506558.09</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>24126925.05</v>
+        <v>24125706.49</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>620366.96</v>
+        <v>619148.4</v>
       </c>
     </row>
     <row r="24">
@@ -4457,10 +4457,10 @@
         <v>53416727.72</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>69794048.05</v>
+        <v>69792829.48999999</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>16377320.33</v>
+        <v>16376101.77</v>
       </c>
     </row>
   </sheetData>
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>69794048.05</v>
+        <v>69792829.48999999</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13792249.56</v>
+        <v>13791031</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-44598418.99</v>
+        <v>-43931082.79</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-366263.75</v>
+        <v>301072.45</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>24410279.27</v>
+        <v>25077615.47</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>-44580046.99</v>
+        <v>-45247383.2</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>8525989</v>
+        <v>7858652.79</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>47919608.21</v>
+        <v>47252272</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9149,52 +9149,34 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Услуги банка (через счёт 60)</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="n">
-        <v>1218.56</v>
-      </c>
-      <c r="D66" s="13" t="n">
-        <v>0</v>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>13791031</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>Управленческие</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>13792249.56</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="inlineStr">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B68" s="15" t="inlineStr"/>
-      <c r="C68" s="16" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D68" s="17" t="n"/>
+      <c r="B67" s="15" t="inlineStr"/>
+      <c r="C67" s="16" t="n">
+        <v>69792829.48999999</v>
+      </c>
+      <c r="D67" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11050,7 +11032,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Услуги банка (через счёт 60)</t>
+          <t>Услуги банка</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11047,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Услуги банка (через счёт 60)</t>
+          <t>Услуги банка</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11653,13 +11635,13 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>-44567798.99</v>
+        <v>-43760221.15</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>-44567798.99</v>
+        <v>-43760221.15</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-89135597.98</v>
+        <v>-87520442.29000001</v>
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -11729,13 +11711,13 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-70595.53999999999</v>
+        <v>-71204.82000000001</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-70595.53999999999</v>
+        <v>-71204.82000000001</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-141191.08</v>
+        <v>-142409.64</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -11819,13 +11801,13 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-34897024.02</v>
+        <v>-34896414.74</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-34897024.02</v>
+        <v>-34896414.74</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-69794048.04000001</v>
+        <v>-69792829.48</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -11837,13 +11819,13 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>21434</v>
+        <v>829011.84</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>21434</v>
+        <v>829011.84</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>42868</v>
+        <v>1658023.69</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -11863,13 +11845,13 @@
         </is>
       </c>
       <c r="C21" s="20" t="n">
-        <v>-30620</v>
+        <v>-170861.64</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>-12248</v>
+        <v>-1487162.05</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>-42868</v>
+        <v>-1658023.69</v>
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
@@ -11896,104 +11878,122 @@
       <c r="F22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Материалы за операции</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-140241.64</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-1474914.05</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-1615155.69</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>-366263.75</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>8525989</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="C24" s="9" t="n">
+        <v>301072.45</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>7858652.79</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>8159725.25</v>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>сумма шагов выше</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>+ Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>45275972.21</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>75934868.23</v>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>+ Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>45275972.21</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>75934868.23</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>− Выплачены дивиденды</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C26" s="6" t="n">
         <v>-5882353</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D26" s="6" t="n">
         <v>-5882353</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>-11764706</v>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>К ВЫПЛАТЕ НА КОНЕЦ МЕСЯЦА</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
-        <v>24410279.27</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>47919608.21</v>
-      </c>
-      <c r="E26" s="9" t="n">
+      <c r="C27" s="9" t="n">
+        <v>25077615.47</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>47252272</v>
+      </c>
+      <c r="E27" s="9" t="n">
         <v>72329887.48</v>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>доход + остаток − дивиденды − резерв</t>
         </is>
@@ -12147,10 +12147,10 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>-13276249.56</v>
+        <v>-13275031</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8998455.15</v>
+        <v>8999673.710000001</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>13.7</v>
@@ -12169,7 +12169,7 @@
         <v>-516000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>8482455.15</v>
+        <v>8483673.710000001</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0.5</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>-719067.16</v>
+        <v>-720285.72</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>7763387.99</v>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -936,14 +936,14 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>ДДС: сальдо нач. + приход − расход = сальдо кон.</t>
+          <t>Налоги по ДДС = налоги с ФОТ + НДФЛ с дивидендов</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>19035318.76</v>
+        <v>7871244.91</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>19035318.76</v>
+        <v>7871244.91</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -953,29 +953,55 @@
           <t>сходится</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>НДФЛ с дивидендов в расходы учредителей не входит</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>ДДС: сальдо нач. + приход − расход = сальдо кон.</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>19035318.76</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>19035318.76</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>сходится</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>Выручка (отчёт) vs выручка кассовым методом (график динамики)</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B13" s="6" t="n">
         <v>96941853.98999999</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C13" s="6" t="n">
         <v>96941853.98999999</v>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>справочно</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>две разные базы — расхождение ожидаемо, см. README</t>
         </is>
@@ -4117,7 +4143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4323,143 +4349,159 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>ДОХОД (выручка − расходы)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>35573284.74</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>7763387.99</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>-27809896.75</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>+ Проценты по депозитам</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>442883.07</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-46545.83</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>ДОХОД УЧРЕДИТЕЛЕЙ</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>36016167.81</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>8159725.23</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>-27856442.58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Внутри поставщиков</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Разница</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>Гонорары ИП хирургов</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>25223566</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>39819623</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>14596057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>Аренда Самокатная 1 стр.1</t>
+          <t>Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>4462500</v>
+        <v>25223566</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1155000</v>
+        <v>39819623</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-3307500</v>
+        <v>14596057</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Коммунальные услуги</t>
+          <t>Аренда Самокатная 1 стр.1</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>224103.63</v>
+        <v>4462500</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0</v>
+        <v>1155000</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-224103.63</v>
+        <v>-3307500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>Досудебный спор</t>
+          <t>Коммунальные услуги</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0</v>
+        <v>224103.63</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>4692500</v>
+        <v>0</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4692500</v>
+        <v>-224103.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
+          <t>Досудебный спор</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>4692500</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>4692500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
           <t>Прочие поставщики</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B24" s="6" t="n">
         <v>23506558.09</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C24" s="6" t="n">
         <v>24125706.49</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D24" s="6" t="n">
         <v>619148.4</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B25" s="9" t="n">
         <v>53416727.72</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C25" s="9" t="n">
         <v>69792829.48999999</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D25" s="9" t="n">
         <v>16376101.77</v>
       </c>
     </row>
@@ -5015,7 +5057,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>794358051.51</v>
+        <v>793592471.5</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -7931,7 +7973,7 @@
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n">
-        <v>97707434</v>
+        <v>96941853.98999999</v>
       </c>
       <c r="D27" s="12" t="n"/>
     </row>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -2235,12 +2235,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Светильники и оборудование</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -2255,17 +2255,17 @@
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>Управленческие</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Медоборудование</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -2405,17 +2405,17 @@
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>Управленческие</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Импланты</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Реклама</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Внедрение финансового учёта</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -2955,17 +2955,17 @@
       </c>
       <c r="C80" s="24" t="inlineStr">
         <is>
-          <t>Управленческие</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Импланты</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -2980,17 +2980,17 @@
       </c>
       <c r="C81" s="24" t="inlineStr">
         <is>
-          <t>Управленческие</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Бланки, мед.журналы, мед.книжки</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3185,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Реклама</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Дизайн-услуги</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -4060,12 +4060,12 @@
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Консультационные услуги</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>56001798.49</v>
+        <v>56439832.65</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13791031</v>
+        <v>13352996.84</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>4527900</v>
+        <v>4728500</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>0.08</v>
@@ -8298,11 +8298,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Анализы</t>
+          <t>Медоборудование</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>102102</v>
+        <v>173834.16</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>0</v>
@@ -8316,11 +8316,11 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Вывоз ТКО и мед отходов</t>
+          <t>Анализы</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>52136.72</v>
+        <v>102102</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>0</v>
@@ -8334,11 +8334,11 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Утилизация медотходов</t>
+          <t>Бланки, мед.журналы, мед.книжки</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>23625</v>
+        <v>63600</v>
       </c>
       <c r="D18" s="13" t="n">
         <v>0</v>
@@ -8352,68 +8352,68 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Наркотики</t>
+          <t>Вывоз ТКО и мед отходов</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12760</v>
+        <v>52136.72</v>
       </c>
       <c r="D19" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Медицинские + ИП</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>56001798.49</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>1</v>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Утилизация медотходов</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>23625</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Управленческие</t>
+          <t>Медицинские + ИП</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Урегулирование досудебного спора</t>
+          <t>Наркотики</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>4692500</v>
+        <v>12760</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Управленческие</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Маркетинговые услуги</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>2505800</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>0.18</v>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Медицинские + ИП</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>56439832.65</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -8424,14 +8424,14 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Аренда Самокатная 1 стр1</t>
+          <t>Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1155000</v>
+        <v>4692500</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="24">
@@ -8442,14 +8442,14 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>878789.77</v>
+        <v>2505800</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="25">
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Ремонт</t>
+          <t>Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>516000</v>
+        <v>1155000</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="26">
@@ -8478,14 +8478,14 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Обслуживание 1СУправление</t>
+          <t>Ремонт</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>435435</v>
+        <v>516000</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="27">
@@ -8496,14 +8496,14 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Фото видео</t>
+          <t>Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>337440</v>
+        <v>441570</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28">
@@ -8514,14 +8514,14 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Услуги юриста</t>
+          <t>Фото видео</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>330000</v>
+        <v>337440</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="29">
@@ -8532,11 +8532,11 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Складской учет</t>
+          <t>Услуги юриста</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="D29" s="13" t="n">
         <v>0.02</v>
@@ -8550,11 +8550,11 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ПО и IT-сервисы</t>
+          <t>Складской учет</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>279349.86</v>
+        <v>320000</v>
       </c>
       <c r="D30" s="13" t="n">
         <v>0.02</v>
@@ -8568,11 +8568,11 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Битрикс 24</t>
+          <t>ПО и IT-сервисы</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>264850</v>
+        <v>279349.86</v>
       </c>
       <c r="D31" s="13" t="n">
         <v>0.02</v>
@@ -8586,11 +8586,11 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Сайт</t>
+          <t>Битрикс 24</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>254000</v>
+        <v>264850</v>
       </c>
       <c r="D32" s="13" t="n">
         <v>0.02</v>
@@ -8604,11 +8604,11 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>IT услуги</t>
+          <t>Сайт</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>247935.06</v>
+        <v>254000</v>
       </c>
       <c r="D33" s="13" t="n">
         <v>0.02</v>
@@ -8622,14 +8622,14 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Услуги инженера</t>
+          <t>IT услуги</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>159575</v>
+        <v>247935.06</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="35">
@@ -8640,14 +8640,14 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Канц и хоз расходы</t>
+          <t>Реклама</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>157671.72</v>
+        <v>227800</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36">
@@ -8658,11 +8658,11 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Сервис речевой аналитики</t>
+          <t>Светильники и оборудование</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>152250</v>
+        <v>179400</v>
       </c>
       <c r="D36" s="13" t="n">
         <v>0.01</v>
@@ -8676,11 +8676,11 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Общехозяйственные</t>
+          <t>Услуги инженера</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>137116</v>
+        <v>159575</v>
       </c>
       <c r="D37" s="13" t="n">
         <v>0.01</v>
@@ -8694,11 +8694,11 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Косметология</t>
+          <t>Канц и хоз расходы</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>114858</v>
+        <v>157671.72</v>
       </c>
       <c r="D38" s="13" t="n">
         <v>0.01</v>
@@ -8712,11 +8712,11 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Реклама</t>
+          <t>Сервис речевой аналитики</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>100000</v>
+        <v>152250</v>
       </c>
       <c r="D39" s="13" t="n">
         <v>0.01</v>
@@ -8730,11 +8730,11 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Такси</t>
+          <t>Общехозяйственные</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>100000</v>
+        <v>137116</v>
       </c>
       <c r="D40" s="13" t="n">
         <v>0.01</v>
@@ -8748,11 +8748,11 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Косметология</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>81075</v>
+        <v>114858</v>
       </c>
       <c r="D41" s="13" t="n">
         <v>0.01</v>
@@ -8766,11 +8766,11 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Хоз расходы</t>
+          <t>Такси</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>77247</v>
+        <v>100000</v>
       </c>
       <c r="D42" s="13" t="n">
         <v>0.01</v>
@@ -8784,14 +8784,14 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Связь</t>
+          <t>Внедрение финансового учёта</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>53760</v>
+        <v>85000</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="44">
@@ -8802,14 +8802,14 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Кофе</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>48301.44</v>
+        <v>81075</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="45">
@@ -8820,14 +8820,14 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Цветы</t>
+          <t>Хоз расходы</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>40000</v>
+        <v>77247</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="46">
@@ -8838,11 +8838,11 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Программное обнспечение</t>
+          <t>Связь</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>39200</v>
+        <v>53760</v>
       </c>
       <c r="D46" s="13" t="n">
         <v>0</v>
@@ -8856,11 +8856,11 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Средства гигиены</t>
+          <t>Кофе</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>37568</v>
+        <v>48301.44</v>
       </c>
       <c r="D47" s="13" t="n">
         <v>0</v>
@@ -8874,11 +8874,11 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Капвложения и работы</t>
+          <t>Цветы</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>29800</v>
+        <v>40000</v>
       </c>
       <c r="D48" s="13" t="n">
         <v>0</v>
@@ -8892,11 +8892,11 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Подбор персонала</t>
+          <t>Программное обнспечение</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>27629</v>
+        <v>39200</v>
       </c>
       <c r="D49" s="13" t="n">
         <v>0</v>
@@ -8910,11 +8910,11 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Охрана</t>
+          <t>Средства гигиены</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>26600</v>
+        <v>37568</v>
       </c>
       <c r="D50" s="13" t="n">
         <v>0</v>
@@ -8928,11 +8928,11 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Мебель, инвентарь</t>
+          <t>Прочие управленческие</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>22130</v>
+        <v>35920.61</v>
       </c>
       <c r="D51" s="13" t="n">
         <v>0</v>
@@ -8946,11 +8946,11 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Вода</t>
+          <t>Капвложения и работы</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>20000</v>
+        <v>29800</v>
       </c>
       <c r="D52" s="13" t="n">
         <v>0</v>
@@ -8964,11 +8964,11 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Техподдержка ККТ</t>
+          <t>Подбор персонала</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>17900</v>
+        <v>27629</v>
       </c>
       <c r="D53" s="13" t="n">
         <v>0</v>
@@ -8982,11 +8982,11 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Электрооборудование</t>
+          <t>Охрана</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>17740</v>
+        <v>26600</v>
       </c>
       <c r="D54" s="13" t="n">
         <v>0</v>
@@ -9000,11 +9000,11 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Интернет</t>
+          <t>Мебель, инвентарь</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>16235.15</v>
+        <v>22130</v>
       </c>
       <c r="D55" s="13" t="n">
         <v>0</v>
@@ -9018,11 +9018,11 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Расходник</t>
+          <t>Вода</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>15120</v>
+        <v>20000</v>
       </c>
       <c r="D56" s="13" t="n">
         <v>0</v>
@@ -9036,11 +9036,11 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Аренда кофемашины</t>
+          <t>Техподдержка ККТ</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>15000</v>
+        <v>17900</v>
       </c>
       <c r="D57" s="13" t="n">
         <v>0</v>
@@ -9054,11 +9054,11 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Дизайн-услуги</t>
+          <t>Электрооборудование</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>11660</v>
+        <v>17740</v>
       </c>
       <c r="D58" s="13" t="n">
         <v>0</v>
@@ -9072,11 +9072,11 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Обучение персонала</t>
+          <t>Дизайн-услуги</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>10900</v>
+        <v>17060</v>
       </c>
       <c r="D59" s="13" t="n">
         <v>0</v>
@@ -9090,11 +9090,11 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Общехоз.расходы прочие</t>
+          <t>Интернет</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>10000</v>
+        <v>16235.15</v>
       </c>
       <c r="D60" s="13" t="n">
         <v>0</v>
@@ -9108,11 +9108,11 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>ПроДокторов</t>
+          <t>Расходник</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>10000</v>
+        <v>15120</v>
       </c>
       <c r="D61" s="13" t="n">
         <v>0</v>
@@ -9126,11 +9126,11 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Доставка</t>
+          <t>Аренда кофемашины</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>7495</v>
+        <v>15000</v>
       </c>
       <c r="D62" s="13" t="n">
         <v>0</v>
@@ -9144,11 +9144,11 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>ТО СКУД, пожарной сигнализации</t>
+          <t>Обучение персонала</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>7000</v>
+        <v>10900</v>
       </c>
       <c r="D63" s="13" t="n">
         <v>0</v>
@@ -9162,11 +9162,11 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Оргтехника</t>
+          <t>Общехоз.расходы прочие</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>5100</v>
+        <v>10000</v>
       </c>
       <c r="D64" s="13" t="n">
         <v>0</v>
@@ -9180,45 +9180,135 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>ПроДокторов</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>7495</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>ТО СКУД, пожарной сигнализации</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Оргтехника</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>5100</v>
+      </c>
+      <c r="D68" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
           <t>Обслуживание аквариума</t>
         </is>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C69" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="D65" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="D69" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D70" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Управленческие</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C66" s="9" t="n">
-        <v>13791031</v>
-      </c>
-      <c r="D66" s="14" t="n">
+      <c r="C71" s="9" t="n">
+        <v>13352996.84</v>
+      </c>
+      <c r="D71" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B67" s="15" t="inlineStr"/>
-      <c r="C67" s="16" t="n">
+      <c r="B72" s="15" t="inlineStr"/>
+      <c r="C72" s="16" t="n">
         <v>69792829.48999999</v>
       </c>
-      <c r="D67" s="17" t="n"/>
+      <c r="D72" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9964,7 +10054,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Светильники и оборудование</t>
         </is>
       </c>
     </row>
@@ -9979,7 +10069,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Медоборудование</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10159,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Импланты</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10324,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Реклама</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10354,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Внедрение финансового учёта</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10489,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Импланты</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10504,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Бланки, мед.журналы, мед.книжки</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10624,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Реклама</t>
         </is>
       </c>
     </row>
@@ -10984,7 +11074,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Обслуживание 1СУправление</t>
         </is>
       </c>
     </row>
@@ -10999,7 +11089,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Дизайн-услуги</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11149,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Консультационные услуги</t>
         </is>
       </c>
     </row>
@@ -12151,13 +12241,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-16182175.49</v>
+        <v>-16620209.65</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>40940055.5</v>
+        <v>40502021.34</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="8">
@@ -12173,7 +12263,7 @@
         <v>-18665350.79</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>22274704.71</v>
+        <v>21836670.55</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>19.3</v>
@@ -12189,13 +12279,13 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>-13275031</v>
+        <v>-12836996.84</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>8999673.710000001</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="10">

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -847,10 +847,10 @@
         <v>8159725.23</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8159725.25</v>
+        <v>8159725.23</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>8159725.25</v>
+        <v>8159725.23</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8159725.25</v>
+        <v>8159725.23</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8159725.25</v>
+        <v>8159725.23</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>-45247383.2</v>
+        <v>-45247383.22</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>7858652.79</v>
+        <v>7858652.77</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>47252272</v>
+        <v>47252271.98</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -11770,10 +11770,10 @@
         <v>-43760221.15</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>-43760221.15</v>
+        <v>-43760221.17</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-87520442.29000001</v>
+        <v>-87520442.31</v>
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -11810,10 +11810,10 @@
         <v>-6245415.92</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>-6245415.92</v>
+        <v>-6245415.93</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-12490831.84</v>
+        <v>-12490831.85</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -11846,10 +11846,10 @@
         <v>-71204.82000000001</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-71204.82000000001</v>
+        <v>-71204.81</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-142409.64</v>
+        <v>-142409.63</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -11900,10 +11900,10 @@
         <v>-102194.46</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>-102194.46</v>
+        <v>-102194.47</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>-204388.92</v>
+        <v>-204388.93</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -11936,10 +11936,10 @@
         <v>-34896414.74</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-34896414.74</v>
+        <v>-34896414.75</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-69792829.48</v>
+        <v>-69792829.48999999</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -12042,10 +12042,10 @@
         <v>301072.45</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>7858652.79</v>
+        <v>7858652.77</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>8159725.25</v>
+        <v>8159725.23</v>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
@@ -12120,10 +12120,10 @@
         <v>25077615.47</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>47252272</v>
+        <v>47252271.98</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>72329887.48</v>
+        <v>72329887.45999999</v>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -3235,12 +3235,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Доктор Дискаунт (назначение уточняется)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+          <t>ручная пометка</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Доктор Дискаунт (назначение уточняется)</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Доктор Дискаунт (назначение уточняется)</t>
         </is>
       </c>
     </row>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3138769.48</v>
+        <v>3127156.58</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>1615200</v>
+        <v>1255200</v>
       </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
@@ -7608,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>97301854</v>
+        <v>96941854</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0</v>

--- a/out/Расшифровка-отчёта-Август-2026.xlsx
+++ b/out/Расшифровка-отчёта-Август-2026.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,18 +141,12 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -800,15 +794,15 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -822,15 +816,15 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>96941854</v>
+        <v>96500243.14</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
+        <v>-0.01</v>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -844,15 +838,15 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -870,15 +864,15 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -900,7 +894,7 @@
       <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -922,7 +916,7 @@
       <c r="D10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -948,7 +942,7 @@
       <c r="D11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -974,7 +968,7 @@
       <c r="D12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>сходится</t>
         </is>
@@ -988,15 +982,15 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>справочно</t>
         </is>
@@ -1070,7 +1064,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>КВАЛИТЕТ ООО</t>
         </is>
@@ -1078,7 +1072,7 @@
       <c r="B5" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1095,7 +1089,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
@@ -1103,7 +1097,7 @@
       <c r="B6" s="6" t="n">
         <v>10966274</v>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1120,7 +1114,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>БУРДИНА Е.С. ИП</t>
         </is>
@@ -1128,7 +1122,7 @@
       <c r="B7" s="6" t="n">
         <v>5382764</v>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1145,7 +1139,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Сехина Виктория Дмитриевна</t>
         </is>
@@ -1153,7 +1147,7 @@
       <c r="B8" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1170,7 +1164,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
@@ -1178,7 +1172,7 @@
       <c r="B9" s="6" t="n">
         <v>4518074</v>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1195,7 +1189,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>КЛОВЕРМЕД ООО</t>
         </is>
@@ -1203,7 +1197,7 @@
       <c r="B10" s="6" t="n">
         <v>4196900</v>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1220,7 +1214,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
@@ -1228,7 +1222,7 @@
       <c r="B11" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1245,7 +1239,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
@@ -1253,7 +1247,7 @@
       <c r="B12" s="6" t="n">
         <v>2811745</v>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1270,7 +1264,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
@@ -1278,7 +1272,7 @@
       <c r="B13" s="6" t="n">
         <v>2631347</v>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1295,7 +1289,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Ласукова Екатерина Борисовна</t>
         </is>
@@ -1303,7 +1297,7 @@
       <c r="B14" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1320,7 +1314,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
@@ -1328,7 +1322,7 @@
       <c r="B15" s="6" t="n">
         <v>2272677</v>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1345,7 +1339,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>БУРДИН С. А. ИП</t>
         </is>
@@ -1353,7 +1347,7 @@
       <c r="B16" s="6" t="n">
         <v>2227217</v>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1370,7 +1364,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Ханукаев Александр Ильич</t>
         </is>
@@ -1378,7 +1372,7 @@
       <c r="B17" s="6" t="n">
         <v>2210015</v>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1395,7 +1389,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>СистеМед ООО</t>
         </is>
@@ -1403,7 +1397,7 @@
       <c r="B18" s="6" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1420,7 +1414,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
@@ -1428,7 +1422,7 @@
       <c r="B19" s="6" t="n">
         <v>1740957</v>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1445,7 +1439,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
@@ -1453,7 +1447,7 @@
       <c r="B20" s="6" t="n">
         <v>1337422</v>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1470,7 +1464,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>ДельтаМед ООО</t>
         </is>
@@ -1478,7 +1472,7 @@
       <c r="B21" s="6" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1495,7 +1489,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Никифоров Сергей Арнольдович</t>
         </is>
@@ -1503,7 +1497,7 @@
       <c r="B22" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1520,7 +1514,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
@@ -1528,7 +1522,7 @@
       <c r="B23" s="6" t="n">
         <v>927938</v>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1545,7 +1539,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
@@ -1553,7 +1547,7 @@
       <c r="B24" s="6" t="n">
         <v>792876</v>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1570,7 +1564,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
@@ -1578,7 +1572,7 @@
       <c r="B25" s="6" t="n">
         <v>703266</v>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1595,7 +1589,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
@@ -1603,7 +1597,7 @@
       <c r="B26" s="6" t="n">
         <v>656611</v>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1620,7 +1614,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
@@ -1628,7 +1622,7 @@
       <c r="B27" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1645,7 +1639,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>СИРИУС ММ ООО</t>
         </is>
@@ -1653,7 +1647,7 @@
       <c r="B28" s="6" t="n">
         <v>550653.36</v>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1670,7 +1664,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
@@ -1678,7 +1672,7 @@
       <c r="B29" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1695,7 +1689,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>КИТ МЕД ООО</t>
         </is>
@@ -1703,7 +1697,7 @@
       <c r="B30" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1720,7 +1714,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>ЦВ ПРОТЕК АО</t>
         </is>
@@ -1728,7 +1722,7 @@
       <c r="B31" s="6" t="n">
         <v>477406.58</v>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1745,7 +1739,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
@@ -1753,7 +1747,7 @@
       <c r="B32" s="6" t="n">
         <v>435435</v>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1770,7 +1764,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
@@ -1778,7 +1772,7 @@
       <c r="B33" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1795,7 +1789,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
@@ -1803,7 +1797,7 @@
       <c r="B34" s="6" t="n">
         <v>349946.07</v>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1820,7 +1814,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
@@ -1828,7 +1822,7 @@
       <c r="B35" s="6" t="n">
         <v>331000</v>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1845,7 +1839,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Электростальский филиал МОКА</t>
         </is>
@@ -1853,7 +1847,7 @@
       <c r="B36" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1870,7 +1864,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
@@ -1878,7 +1872,7 @@
       <c r="B37" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1895,7 +1889,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
@@ -1903,7 +1897,7 @@
       <c r="B38" s="6" t="n">
         <v>293400</v>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1920,7 +1914,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>ПФ СКБ Контур АО</t>
         </is>
@@ -1928,7 +1922,7 @@
       <c r="B39" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1945,7 +1939,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
@@ -1953,7 +1947,7 @@
       <c r="B40" s="6" t="n">
         <v>275300</v>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -1970,7 +1964,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
@@ -1978,7 +1972,7 @@
       <c r="B41" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -1995,7 +1989,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
@@ -2003,7 +1997,7 @@
       <c r="B42" s="6" t="n">
         <v>260766</v>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2020,7 +2014,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
@@ -2028,7 +2022,7 @@
       <c r="B43" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2045,7 +2039,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>КРЕЙТ ООО</t>
         </is>
@@ -2053,7 +2047,7 @@
       <c r="B44" s="6" t="n">
         <v>246913.68</v>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2070,7 +2064,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>МЕДПРО ООО</t>
         </is>
@@ -2078,7 +2072,7 @@
       <c r="B45" s="6" t="n">
         <v>235200</v>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2095,7 +2089,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
@@ -2103,7 +2097,7 @@
       <c r="B46" s="6" t="n">
         <v>222551.24</v>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2120,7 +2114,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
@@ -2128,7 +2122,7 @@
       <c r="B47" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2145,7 +2139,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
@@ -2153,7 +2147,7 @@
       <c r="B48" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="C48" s="24" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2170,7 +2164,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>МЕДИНТОРГ АО</t>
         </is>
@@ -2178,7 +2172,7 @@
       <c r="B49" s="6" t="n">
         <v>206303.7</v>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2195,7 +2189,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
@@ -2203,7 +2197,7 @@
       <c r="B50" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2220,7 +2214,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>ПЗСПП ООО</t>
         </is>
@@ -2228,7 +2222,7 @@
       <c r="B51" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2245,7 +2239,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>БЕЛВА ООО ПТК</t>
         </is>
@@ -2253,7 +2247,7 @@
       <c r="B52" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2270,7 +2264,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
@@ -2278,7 +2272,7 @@
       <c r="B53" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2295,7 +2289,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>КОМУС ООО</t>
         </is>
@@ -2303,7 +2297,7 @@
       <c r="B54" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2320,7 +2314,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>ИМОТИО ООО</t>
         </is>
@@ -2328,7 +2322,7 @@
       <c r="B55" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="C55" s="24" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2345,7 +2339,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
@@ -2353,7 +2347,7 @@
       <c r="B56" s="6" t="n">
         <v>149600</v>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2370,7 +2364,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>АЛКАНА А ООО</t>
         </is>
@@ -2378,7 +2372,7 @@
       <c r="B57" s="6" t="n">
         <v>146600</v>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2395,7 +2389,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
@@ -2403,7 +2397,7 @@
       <c r="B58" s="6" t="n">
         <v>136000</v>
       </c>
-      <c r="C58" s="24" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2420,7 +2414,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="22" t="inlineStr">
         <is>
           <t>ТД ТИНКО ООО</t>
         </is>
@@ -2428,7 +2422,7 @@
       <c r="B59" s="6" t="n">
         <v>118740.75</v>
       </c>
-      <c r="C59" s="24" t="inlineStr">
+      <c r="C59" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2445,7 +2439,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
@@ -2453,7 +2447,7 @@
       <c r="B60" s="6" t="n">
         <v>118735.06</v>
       </c>
-      <c r="C60" s="24" t="inlineStr">
+      <c r="C60" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2470,7 +2464,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>А410 ООО</t>
         </is>
@@ -2478,7 +2472,7 @@
       <c r="B61" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C61" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2495,7 +2489,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="22" t="inlineStr">
         <is>
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
@@ -2503,7 +2497,7 @@
       <c r="B62" s="6" t="n">
         <v>111300</v>
       </c>
-      <c r="C62" s="24" t="inlineStr">
+      <c r="C62" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2520,7 +2514,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="22" t="inlineStr">
         <is>
           <t>МИА ООО</t>
         </is>
@@ -2528,7 +2522,7 @@
       <c r="B63" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="C63" s="24" t="inlineStr">
+      <c r="C63" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2545,7 +2539,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="22" t="inlineStr">
         <is>
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
@@ -2553,7 +2547,7 @@
       <c r="B64" s="6" t="n">
         <v>104374</v>
       </c>
-      <c r="C64" s="24" t="inlineStr">
+      <c r="C64" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2570,7 +2564,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="22" t="inlineStr">
         <is>
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
@@ -2578,7 +2572,7 @@
       <c r="B65" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="C65" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2595,7 +2589,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Звоник Юрий Алексеевич</t>
         </is>
@@ -2603,7 +2597,7 @@
       <c r="B66" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C66" s="24" t="inlineStr">
+      <c r="C66" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2620,7 +2614,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="22" t="inlineStr">
         <is>
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
@@ -2628,7 +2622,7 @@
       <c r="B67" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="C67" s="24" t="inlineStr">
+      <c r="C67" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2645,7 +2639,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>ТЕХПРОФИТ ООО</t>
         </is>
@@ -2653,7 +2647,7 @@
       <c r="B68" s="6" t="n">
         <v>99200</v>
       </c>
-      <c r="C68" s="24" t="inlineStr">
+      <c r="C68" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2670,7 +2664,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="24" t="inlineStr">
+      <c r="A69" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
@@ -2678,7 +2672,7 @@
       <c r="B69" s="6" t="n">
         <v>90100</v>
       </c>
-      <c r="C69" s="24" t="inlineStr">
+      <c r="C69" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2695,7 +2689,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="A70" s="22" t="inlineStr">
         <is>
           <t>ДельтаМедКомпани ООО</t>
         </is>
@@ -2703,7 +2697,7 @@
       <c r="B70" s="6" t="n">
         <v>87600</v>
       </c>
-      <c r="C70" s="24" t="inlineStr">
+      <c r="C70" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2720,7 +2714,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="inlineStr">
+      <c r="A71" s="22" t="inlineStr">
         <is>
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
@@ -2728,7 +2722,7 @@
       <c r="B71" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="C71" s="24" t="inlineStr">
+      <c r="C71" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2745,7 +2739,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="inlineStr">
+      <c r="A72" s="22" t="inlineStr">
         <is>
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
@@ -2753,7 +2747,7 @@
       <c r="B72" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="C72" s="24" t="inlineStr">
+      <c r="C72" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2770,7 +2764,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24" t="inlineStr">
+      <c r="A73" s="22" t="inlineStr">
         <is>
           <t>М-ИНВЕСТ ООО</t>
         </is>
@@ -2778,7 +2772,7 @@
       <c r="B73" s="6" t="n">
         <v>77412</v>
       </c>
-      <c r="C73" s="24" t="inlineStr">
+      <c r="C73" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2795,7 +2789,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24" t="inlineStr">
+      <c r="A74" s="22" t="inlineStr">
         <is>
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
@@ -2803,7 +2797,7 @@
       <c r="B74" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="C74" s="24" t="inlineStr">
+      <c r="C74" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2820,7 +2814,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="24" t="inlineStr">
+      <c r="A75" s="22" t="inlineStr">
         <is>
           <t>ДЕЗНЭТ ООО</t>
         </is>
@@ -2828,7 +2822,7 @@
       <c r="B75" s="6" t="n">
         <v>76940</v>
       </c>
-      <c r="C75" s="24" t="inlineStr">
+      <c r="C75" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2845,7 +2839,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="inlineStr">
+      <c r="A76" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
@@ -2853,7 +2847,7 @@
       <c r="B76" s="6" t="n">
         <v>76540</v>
       </c>
-      <c r="C76" s="24" t="inlineStr">
+      <c r="C76" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2870,7 +2864,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="inlineStr">
+      <c r="A77" s="22" t="inlineStr">
         <is>
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
@@ -2878,7 +2872,7 @@
       <c r="B77" s="6" t="n">
         <v>76000</v>
       </c>
-      <c r="C77" s="24" t="inlineStr">
+      <c r="C77" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2895,7 +2889,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="24" t="inlineStr">
+      <c r="A78" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
@@ -2903,7 +2897,7 @@
       <c r="B78" s="6" t="n">
         <v>72360</v>
       </c>
-      <c r="C78" s="24" t="inlineStr">
+      <c r="C78" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2920,7 +2914,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="24" t="inlineStr">
+      <c r="A79" s="22" t="inlineStr">
         <is>
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
@@ -2928,7 +2922,7 @@
       <c r="B79" s="6" t="n">
         <v>64756</v>
       </c>
-      <c r="C79" s="24" t="inlineStr">
+      <c r="C79" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -2945,7 +2939,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="24" t="inlineStr">
+      <c r="A80" s="22" t="inlineStr">
         <is>
           <t>АЛКАНА М ООО</t>
         </is>
@@ -2953,7 +2947,7 @@
       <c r="B80" s="6" t="n">
         <v>64600</v>
       </c>
-      <c r="C80" s="24" t="inlineStr">
+      <c r="C80" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2970,7 +2964,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="24" t="inlineStr">
+      <c r="A81" s="22" t="inlineStr">
         <is>
           <t>СитиМед ООО</t>
         </is>
@@ -2978,7 +2972,7 @@
       <c r="B81" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="C81" s="24" t="inlineStr">
+      <c r="C81" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -2995,7 +2989,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="24" t="inlineStr">
+      <c r="A82" s="22" t="inlineStr">
         <is>
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
@@ -3003,7 +2997,7 @@
       <c r="B82" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="C82" s="24" t="inlineStr">
+      <c r="C82" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3020,7 +3014,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="24" t="inlineStr">
+      <c r="A83" s="22" t="inlineStr">
         <is>
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
@@ -3028,7 +3022,7 @@
       <c r="B83" s="6" t="n">
         <v>51760</v>
       </c>
-      <c r="C83" s="24" t="inlineStr">
+      <c r="C83" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3045,7 +3039,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="24" t="inlineStr">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>КРИОФАРМ ООО</t>
         </is>
@@ -3053,7 +3047,7 @@
       <c r="B84" s="6" t="n">
         <v>51675</v>
       </c>
-      <c r="C84" s="24" t="inlineStr">
+      <c r="C84" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3070,7 +3064,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24" t="inlineStr">
+      <c r="A85" s="22" t="inlineStr">
         <is>
           <t>БАРИСТА ООО</t>
         </is>
@@ -3078,7 +3072,7 @@
       <c r="B85" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="C85" s="24" t="inlineStr">
+      <c r="C85" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3095,7 +3089,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="24" t="inlineStr">
+      <c r="A86" s="22" t="inlineStr">
         <is>
           <t>СИСТЕМА ООО</t>
         </is>
@@ -3103,7 +3097,7 @@
       <c r="B86" s="6" t="n">
         <v>48285.78</v>
       </c>
-      <c r="C86" s="24" t="inlineStr">
+      <c r="C86" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3120,7 +3114,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="24" t="inlineStr">
+      <c r="A87" s="22" t="inlineStr">
         <is>
           <t>Семин Сергей Владиславович</t>
         </is>
@@ -3128,7 +3122,7 @@
       <c r="B87" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C87" s="24" t="inlineStr">
+      <c r="C87" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3145,7 +3139,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="24" t="inlineStr">
+      <c r="A88" s="22" t="inlineStr">
         <is>
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
@@ -3153,7 +3147,7 @@
       <c r="B88" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="C88" s="24" t="inlineStr">
+      <c r="C88" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3170,7 +3164,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24" t="inlineStr">
+      <c r="A89" s="22" t="inlineStr">
         <is>
           <t>СМБ-СЕРВИС ООО</t>
         </is>
@@ -3178,7 +3172,7 @@
       <c r="B89" s="6" t="n">
         <v>37700</v>
       </c>
-      <c r="C89" s="24" t="inlineStr">
+      <c r="C89" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3195,7 +3189,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="24" t="inlineStr">
+      <c r="A90" s="22" t="inlineStr">
         <is>
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
@@ -3203,7 +3197,7 @@
       <c r="B90" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="C90" s="24" t="inlineStr">
+      <c r="C90" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3220,7 +3214,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="24" t="inlineStr">
+      <c r="A91" s="22" t="inlineStr">
         <is>
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
@@ -3228,7 +3222,7 @@
       <c r="B91" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="C91" s="24" t="inlineStr">
+      <c r="C91" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3245,7 +3239,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="24" t="inlineStr">
+      <c r="A92" s="22" t="inlineStr">
         <is>
           <t>Селектел АО</t>
         </is>
@@ -3253,7 +3247,7 @@
       <c r="B92" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C92" s="24" t="inlineStr">
+      <c r="C92" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3270,7 +3264,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="inlineStr">
+      <c r="A93" s="22" t="inlineStr">
         <is>
           <t>МЕДЛИГА АО</t>
         </is>
@@ -3278,7 +3272,7 @@
       <c r="B93" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="C93" s="24" t="inlineStr">
+      <c r="C93" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3295,7 +3289,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="24" t="inlineStr">
+      <c r="A94" s="22" t="inlineStr">
         <is>
           <t>ХЭДХАНТЕР ООО</t>
         </is>
@@ -3303,7 +3297,7 @@
       <c r="B94" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="C94" s="24" t="inlineStr">
+      <c r="C94" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3320,7 +3314,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="24" t="inlineStr">
+      <c r="A95" s="22" t="inlineStr">
         <is>
           <t>ЭКМУС ООО</t>
         </is>
@@ -3328,7 +3322,7 @@
       <c r="B95" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="C95" s="24" t="inlineStr">
+      <c r="C95" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3345,7 +3339,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="24" t="inlineStr">
+      <c r="A96" s="22" t="inlineStr">
         <is>
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
@@ -3353,7 +3347,7 @@
       <c r="B96" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="C96" s="24" t="inlineStr">
+      <c r="C96" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3370,7 +3364,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="24" t="inlineStr">
+      <c r="A97" s="22" t="inlineStr">
         <is>
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
@@ -3378,7 +3372,7 @@
       <c r="B97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C97" s="24" t="inlineStr">
+      <c r="C97" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3395,7 +3389,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="24" t="inlineStr">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
@@ -3403,7 +3397,7 @@
       <c r="B98" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C98" s="24" t="inlineStr">
+      <c r="C98" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3420,7 +3414,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="24" t="inlineStr">
+      <c r="A99" s="22" t="inlineStr">
         <is>
           <t>ТАКСКОМ ООО</t>
         </is>
@@ -3428,7 +3422,7 @@
       <c r="B99" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="C99" s="24" t="inlineStr">
+      <c r="C99" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3445,7 +3439,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="24" t="inlineStr">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>МРК-СНАБ ООО</t>
         </is>
@@ -3453,7 +3447,7 @@
       <c r="B100" s="6" t="n">
         <v>17750</v>
       </c>
-      <c r="C100" s="24" t="inlineStr">
+      <c r="C100" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3470,7 +3464,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="inlineStr">
+      <c r="A101" s="22" t="inlineStr">
         <is>
           <t>ОнЛайн Трейд ООО</t>
         </is>
@@ -3478,7 +3472,7 @@
       <c r="B101" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="C101" s="24" t="inlineStr">
+      <c r="C101" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3495,7 +3489,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="inlineStr">
+      <c r="A102" s="22" t="inlineStr">
         <is>
           <t>КантриКом АО</t>
         </is>
@@ -3503,7 +3497,7 @@
       <c r="B102" s="6" t="n">
         <v>17568</v>
       </c>
-      <c r="C102" s="24" t="inlineStr">
+      <c r="C102" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3520,7 +3514,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="24" t="inlineStr">
+      <c r="A103" s="22" t="inlineStr">
         <is>
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
@@ -3528,7 +3522,7 @@
       <c r="B103" s="6" t="n">
         <v>16800</v>
       </c>
-      <c r="C103" s="24" t="inlineStr">
+      <c r="C103" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3545,7 +3539,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="24" t="inlineStr">
+      <c r="A104" s="22" t="inlineStr">
         <is>
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
@@ -3553,7 +3547,7 @@
       <c r="B104" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="C104" s="24" t="inlineStr">
+      <c r="C104" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3570,7 +3564,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="24" t="inlineStr">
+      <c r="A105" s="22" t="inlineStr">
         <is>
           <t>ТЕЛЕМИР ООО</t>
         </is>
@@ -3578,7 +3572,7 @@
       <c r="B105" s="6" t="n">
         <v>16192</v>
       </c>
-      <c r="C105" s="24" t="inlineStr">
+      <c r="C105" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3595,7 +3589,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="24" t="inlineStr">
+      <c r="A106" s="22" t="inlineStr">
         <is>
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
@@ -3603,7 +3597,7 @@
       <c r="B106" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="C106" s="24" t="inlineStr">
+      <c r="C106" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3620,7 +3614,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="24" t="inlineStr">
+      <c r="A107" s="22" t="inlineStr">
         <is>
           <t>Алдошин Павел Александрович ИП</t>
         </is>
@@ -3628,7 +3622,7 @@
       <c r="B107" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C107" s="24" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3645,7 +3639,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="24" t="inlineStr">
+      <c r="A108" s="22" t="inlineStr">
         <is>
           <t>Вилорд ООО</t>
         </is>
@@ -3653,7 +3647,7 @@
       <c r="B108" s="6" t="n">
         <v>12800</v>
       </c>
-      <c r="C108" s="24" t="inlineStr">
+      <c r="C108" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3670,7 +3664,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="24" t="inlineStr">
+      <c r="A109" s="22" t="inlineStr">
         <is>
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
@@ -3678,7 +3672,7 @@
       <c r="B109" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="C109" s="24" t="inlineStr">
+      <c r="C109" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3695,7 +3689,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="24" t="inlineStr">
+      <c r="A110" s="22" t="inlineStr">
         <is>
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
@@ -3703,7 +3697,7 @@
       <c r="B110" s="6" t="n">
         <v>12505</v>
       </c>
-      <c r="C110" s="24" t="inlineStr">
+      <c r="C110" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3720,7 +3714,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="24" t="inlineStr">
+      <c r="A111" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
@@ -3728,7 +3722,7 @@
       <c r="B111" s="6" t="n">
         <v>11660</v>
       </c>
-      <c r="C111" s="24" t="inlineStr">
+      <c r="C111" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3745,7 +3739,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="24" t="inlineStr">
+      <c r="A112" s="22" t="inlineStr">
         <is>
           <t>АСПРОМЕД ООО</t>
         </is>
@@ -3753,7 +3747,7 @@
       <c r="B112" s="6" t="n">
         <v>10940</v>
       </c>
-      <c r="C112" s="24" t="inlineStr">
+      <c r="C112" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3770,7 +3764,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="24" t="inlineStr">
+      <c r="A113" s="22" t="inlineStr">
         <is>
           <t>МГУТУ АНО ДПО</t>
         </is>
@@ -3778,7 +3772,7 @@
       <c r="B113" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="C113" s="24" t="inlineStr">
+      <c r="C113" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3795,7 +3789,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="24" t="inlineStr">
+      <c r="A114" s="22" t="inlineStr">
         <is>
           <t>АО "Почта России"</t>
         </is>
@@ -3803,7 +3797,7 @@
       <c r="B114" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C114" s="24" t="inlineStr">
+      <c r="C114" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3820,7 +3814,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="24" t="inlineStr">
+      <c r="A115" s="22" t="inlineStr">
         <is>
           <t>МЕДРОКЕТ ООО</t>
         </is>
@@ -3828,7 +3822,7 @@
       <c r="B115" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C115" s="24" t="inlineStr">
+      <c r="C115" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3845,7 +3839,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="24" t="inlineStr">
+      <c r="A116" s="22" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
@@ -3853,7 +3847,7 @@
       <c r="B116" s="6" t="n">
         <v>9800</v>
       </c>
-      <c r="C116" s="24" t="inlineStr">
+      <c r="C116" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3870,7 +3864,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="24" t="inlineStr">
+      <c r="A117" s="22" t="inlineStr">
         <is>
           <t>Деловые линии ООО</t>
         </is>
@@ -3878,7 +3872,7 @@
       <c r="B117" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="C117" s="24" t="inlineStr">
+      <c r="C117" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3895,7 +3889,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="24" t="inlineStr">
+      <c r="A118" s="22" t="inlineStr">
         <is>
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
@@ -3903,7 +3897,7 @@
       <c r="B118" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="C118" s="24" t="inlineStr">
+      <c r="C118" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3920,7 +3914,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="24" t="inlineStr">
+      <c r="A119" s="22" t="inlineStr">
         <is>
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
@@ -3928,7 +3922,7 @@
       <c r="B119" s="6" t="n">
         <v>6135</v>
       </c>
-      <c r="C119" s="24" t="inlineStr">
+      <c r="C119" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3945,7 +3939,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="24" t="inlineStr">
+      <c r="A120" s="22" t="inlineStr">
         <is>
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
@@ -3953,7 +3947,7 @@
       <c r="B120" s="6" t="n">
         <v>5400</v>
       </c>
-      <c r="C120" s="24" t="inlineStr">
+      <c r="C120" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -3970,7 +3964,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="24" t="inlineStr">
+      <c r="A121" s="22" t="inlineStr">
         <is>
           <t>ДЕАЛМЕД АО</t>
         </is>
@@ -3978,7 +3972,7 @@
       <c r="B121" s="6" t="n">
         <v>5170</v>
       </c>
-      <c r="C121" s="24" t="inlineStr">
+      <c r="C121" s="22" t="inlineStr">
         <is>
           <t>Медицинские</t>
         </is>
@@ -3995,7 +3989,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="24" t="inlineStr">
+      <c r="A122" s="22" t="inlineStr">
         <is>
           <t>ИНФОТЕХ ООО</t>
         </is>
@@ -4003,7 +3997,7 @@
       <c r="B122" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="C122" s="24" t="inlineStr">
+      <c r="C122" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4020,7 +4014,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="24" t="inlineStr">
+      <c r="A123" s="22" t="inlineStr">
         <is>
           <t>Аквапрактика ООО</t>
         </is>
@@ -4028,7 +4022,7 @@
       <c r="B123" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C123" s="24" t="inlineStr">
+      <c r="C123" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4045,7 +4039,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="24" t="inlineStr">
+      <c r="A124" s="22" t="inlineStr">
         <is>
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
@@ -4053,7 +4047,7 @@
       <c r="B124" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="C124" s="24" t="inlineStr">
+      <c r="C124" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4070,7 +4064,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="24" t="inlineStr">
+      <c r="A125" s="22" t="inlineStr">
         <is>
           <t>АО "Альфа Банк"</t>
         </is>
@@ -4078,7 +4072,7 @@
       <c r="B125" s="6" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="C125" s="24" t="inlineStr">
+      <c r="C125" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4095,7 +4089,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="24" t="inlineStr">
+      <c r="A126" s="22" t="inlineStr">
         <is>
           <t>БАНК ВТБ (ПАО)</t>
         </is>
@@ -4103,7 +4097,7 @@
       <c r="B126" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C126" s="24" t="inlineStr">
+      <c r="C126" s="22" t="inlineStr">
         <is>
           <t>Управленческие</t>
         </is>
@@ -4120,7 +4114,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="25" t="inlineStr">
+      <c r="A127" s="23" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4128,9 +4122,9 @@
       <c r="B127" s="9" t="n">
         <v>80794048.05</v>
       </c>
-      <c r="C127" s="25" t="inlineStr"/>
-      <c r="D127" s="18" t="inlineStr"/>
-      <c r="E127" s="18" t="inlineStr"/>
+      <c r="C127" s="23" t="inlineStr"/>
+      <c r="D127" s="16" t="inlineStr"/>
+      <c r="E127" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4189,7 +4183,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Выручка</t>
         </is>
@@ -4198,14 +4192,14 @@
         <v>108126415.72</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-11184561.73</v>
+        <v>-11626172.57</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Налоги с ФОТ</t>
         </is>
@@ -4221,7 +4215,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Зарплата</t>
         </is>
@@ -4237,7 +4231,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Расходы по кассе</t>
         </is>
@@ -4253,7 +4247,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Услуги банка (общие)</t>
         </is>
@@ -4269,7 +4263,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Эквайринг</t>
         </is>
@@ -4278,14 +4272,14 @@
         <v>41563.8</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>373487.16</v>
+        <v>0</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>331923.36</v>
+        <v>-41563.8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Алименты</t>
         </is>
@@ -4301,7 +4295,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>% по кредиту</t>
         </is>
@@ -4317,7 +4311,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Поставщики (счёт 60)</t>
         </is>
@@ -4333,23 +4327,23 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="14" t="n">
         <v>72553130.98</v>
       </c>
-      <c r="C14" s="16" t="n">
-        <v>89178466</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>16625335.02</v>
+      <c r="C14" s="14" t="n">
+        <v>88804978.84</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>16251847.86</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>+ Проценты по депозитам</t>
         </is>
@@ -4365,7 +4359,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>ДОХОД УЧРЕДИТЕЛЕЙ</t>
         </is>
@@ -4374,10 +4368,10 @@
         <v>36016167.81</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>-27856442.58</v>
+        <v>-27924566.26</v>
       </c>
     </row>
     <row r="18">
@@ -4410,7 +4404,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -4426,7 +4420,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр.1</t>
         </is>
@@ -4442,7 +4436,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
@@ -4458,7 +4452,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Досудебный спор</t>
         </is>
@@ -4474,7 +4468,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Прочие поставщики</t>
         </is>
@@ -4490,7 +4484,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4558,7 +4552,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>01–10.08, старая управленка</t>
         </is>
@@ -4566,14 +4560,14 @@
       <c r="B5" s="6" t="n">
         <v>31243514</v>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>реестр «Оплаты от пациента» без двух документов, помеченных на удаление; сходится с «Ежедневным отчётом по кассам»</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>11–31.08, новая управленка</t>
         </is>
@@ -4581,49 +4575,49 @@
       <c r="B6" s="6" t="n">
         <v>66058340</v>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>отчёт «Оплаты», виды оплаты «Наличными» и «Безналичными», уже за вычетом возвратов</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Возвраты пациентам, 01–10.08</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>-360000</v>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
+        <v>-465000</v>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>колонка «Возврат денег» «Ежедневного отчёта по кассам»</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>96941854</v>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
+        <v>96836854</v>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>деньги, поступившие за месяц</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr"/>
+      <c r="A9" s="22" t="inlineStr"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="24" t="inlineStr"/>
+      <c r="C9" s="22" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>01–10.08: платежи с указанным специалистом</t>
         </is>
@@ -4631,14 +4625,14 @@
       <c r="B10" s="6" t="n">
         <v>30534014</v>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>колонка «Специалист» реестра платежей</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>01–10.08: без специалиста</t>
         </is>
@@ -4646,14 +4640,14 @@
       <c r="B11" s="6" t="n">
         <v>709500</v>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>разнесены по врачам того же пациента, остаток — пропорционально</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>11–31.08: привязано к врачу напрямую</t>
         </is>
@@ -4661,14 +4655,14 @@
       <c r="B12" s="6" t="n">
         <v>46401840</v>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>документы «Оказание услуг» — врач указан в документе</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>11–31.08: авансы, разнесённые через пациента</t>
         </is>
@@ -4676,14 +4670,14 @@
       <c r="B13" s="6" t="n">
         <v>14588000</v>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>оплата картой и кассовые ордера</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>11–31.08: авансы без совпадения по пациенту</t>
         </is>
@@ -4691,7 +4685,7 @@
       <c r="B14" s="6" t="n">
         <v>5068500</v>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>разнесены пропорционально; пациентов нет в реестре услуг августа</t>
         </is>
@@ -4725,7 +4719,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
@@ -4734,17 +4728,17 @@
         <v>0</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>4180781.46</v>
+        <v>4259965.12</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4180781.46</v>
-      </c>
-      <c r="E17" s="13" t="n">
+        <v>4229901.79</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
@@ -4753,36 +4747,36 @@
         <v>0</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13054662.21</v>
+        <v>13105596.99</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>13054662.21</v>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>0.13</v>
+        <v>13039550.06</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>29879660.71</v>
+        <v>29879866.39</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>46606046.11</v>
+        <v>46458823.88</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>76485706.81999999</v>
-      </c>
-      <c r="E19" s="13" t="n">
+        <v>76010267.98999999</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>0.79</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
@@ -4791,36 +4785,36 @@
         <v>0</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>261238.64</v>
+        <v>263397.16</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>261238.64</v>
-      </c>
-      <c r="E20" s="13" t="n">
+        <v>261913.99</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1003853.29</v>
+        <v>1003647.61</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1955611.58</v>
+        <v>1970556.86</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2959464.86</v>
-      </c>
-      <c r="E21" s="13" t="n">
+        <v>2958609.32</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -4829,12 +4823,12 @@
         <v>30883514</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>66058340</v>
+        <v>66058340.01</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>96941853.98999999</v>
-      </c>
-      <c r="E22" s="14" t="n">
+        <v>96500243.15000001</v>
+      </c>
+      <c r="E22" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4911,7 +4905,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -4941,7 +4935,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -5057,7 +5051,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>793592471.5</v>
+        <v>793150860.66</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -5237,7 +5231,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>61959954</v>
+        <v>61518343.14</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -5417,7 +5411,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -5567,7 +5561,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>4180781.46</v>
+        <v>4229901.79</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -5597,7 +5591,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>38242853.41</v>
+        <v>38005133.99</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -5627,7 +5621,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>1610351.75</v>
+        <v>1610261.65</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -5657,7 +5651,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-43931082.79</v>
+        <v>-43744339.21</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5687,7 +5681,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>301072.45</v>
+        <v>299126.85</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -5777,7 +5771,7 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>25077615.47</v>
+        <v>25075669.87</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -5807,7 +5801,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>13054662.21</v>
+        <v>13039550.06</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -5837,7 +5831,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>38242853.41</v>
+        <v>38005133.99</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -5867,7 +5861,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1610351.75</v>
+        <v>1610261.65</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -5897,7 +5891,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>-45247383.22</v>
+        <v>-45060639.63</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -5927,7 +5921,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>7858652.77</v>
+        <v>7792474.7</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -6017,7 +6011,7 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>47252271.98</v>
+        <v>47186093.91</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -7628,13 +7622,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7659,15 +7655,25 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Касса</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Доля</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Комиссия эквайринга</t>
         </is>
@@ -7680,12 +7686,18 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4180781.46</v>
-      </c>
-      <c r="C5" s="10" t="n">
+        <v>41946.83</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4187954.96</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4229901.79</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="D5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7694,12 +7706,18 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>13054662.21</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="D6" s="6" t="n"/>
+        <v>3838920.69</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>9200629.369999999</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>13039550.06</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7708,12 +7726,18 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>76485706.81999999</v>
-      </c>
-      <c r="C7" s="10" t="n">
+        <v>30259592.24</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>45750675.75</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>76010267.98999999</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>0.79</v>
       </c>
-      <c r="D7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -7722,12 +7746,18 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>261238.64</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="n"/>
+        <v>55303.87</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>206610.12</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>261913.99</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7736,12 +7766,18 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2959464.86</v>
-      </c>
-      <c r="C9" s="10" t="n">
+        <v>786136.38</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2172472.94</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2958609.32</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="D9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7750,280 +7786,221 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>96941853.98999999</v>
-      </c>
-      <c r="C10" s="11" t="n">
+        <v>34981900</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>61983343.14</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>96500243.15000001</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="F10" s="9" t="n">
         <v>373487.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Каналы поступления</t>
+          <t>Динамика по месяцам (база: строка «Выручка за месяц», кассовый метод)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Канал</t>
+          <t>Месяц</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Сумма</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Комментарий</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Изменение</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Наличными</t>
+          <t>Январь</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>34981900</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>касса клиники</t>
-        </is>
+        <v>65706942</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>95732197.48999999</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Безналичными</t>
+          <t>Февраль</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>61959954</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>карты и онлайн-оплаты (в т.ч. онлайн-оплаты через сайт 1 035 500 ₽)  за вычетом возвратов пациентам 360 000 ₽</t>
-        </is>
+        <v>74025535</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>99580226.87</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>96941853.98999999</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Март</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>82158176</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>114153459.7</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>84678135</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>115281361.15</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Динамика по месяцам (база: строка «Выручка за месяц», кассовый метод)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Изменение</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>79591558</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>79719174.69</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>72223764</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>84057781.89</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Январь</t>
+          <t>Июль</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>65706942</v>
+        <v>69118798.5</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>95732197.48999999</v>
+        <v>108126415.72</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Февраль</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>74025535</v>
-      </c>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n">
-        <v>99580226.87</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>0.35</v>
-      </c>
+        <v>96500243.15000001</v>
+      </c>
+      <c r="D21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Март</t>
+          <t>Сентябрь</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>82158176</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>114153459.7</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>0.39</v>
-      </c>
+        <v>81488546.61</v>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Апрель</t>
+          <t>Октябрь</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>84678135</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>115281361.15</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>0.36</v>
-      </c>
+        <v>112251113</v>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Май</t>
+          <t>Ноябрь</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>79591558</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>79719174.69</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>0</v>
-      </c>
+        <v>99764489.61</v>
+      </c>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Июнь</t>
+          <t>Декабрь</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>72223764</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>84057781.89</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>69118798.5</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>108126415.72</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n">
-        <v>96941853.98999999</v>
-      </c>
-      <c r="D27" s="12" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Сентябрь</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>81488546.61</v>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Октябрь</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>112251113</v>
-      </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="12" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ноябрь</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>99764489.61</v>
-      </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Декабрь</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
         <v>86073459.34</v>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="12" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8088,7 +8065,7 @@
       <c r="C4" s="6" t="n">
         <v>39819623</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="10" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -8106,7 +8083,7 @@
       <c r="C5" s="6" t="n">
         <v>4728500</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="10" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -8124,7 +8101,7 @@
       <c r="C6" s="6" t="n">
         <v>3298432.06</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -8142,7 +8119,7 @@
       <c r="C7" s="6" t="n">
         <v>2887658</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="10" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8160,7 +8137,7 @@
       <c r="C8" s="6" t="n">
         <v>2250790.16</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="10" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -8178,7 +8155,7 @@
       <c r="C9" s="6" t="n">
         <v>827352.65</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8196,7 +8173,7 @@
       <c r="C10" s="6" t="n">
         <v>570005</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8214,7 +8191,7 @@
       <c r="C11" s="6" t="n">
         <v>515528</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8232,7 +8209,7 @@
       <c r="C12" s="6" t="n">
         <v>376950</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8250,7 +8227,7 @@
       <c r="C13" s="6" t="n">
         <v>345200</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8268,7 +8245,7 @@
       <c r="C14" s="6" t="n">
         <v>210000</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8286,7 +8263,7 @@
       <c r="C15" s="6" t="n">
         <v>181735.9</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8304,7 +8281,7 @@
       <c r="C16" s="6" t="n">
         <v>173834.16</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8322,7 +8299,7 @@
       <c r="C17" s="6" t="n">
         <v>102102</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8340,7 +8317,7 @@
       <c r="C18" s="6" t="n">
         <v>63600</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8358,7 +8335,7 @@
       <c r="C19" s="6" t="n">
         <v>52136.72</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8376,7 +8353,7 @@
       <c r="C20" s="6" t="n">
         <v>23625</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8394,7 +8371,7 @@
       <c r="C21" s="6" t="n">
         <v>12760</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8412,7 +8389,7 @@
       <c r="C22" s="9" t="n">
         <v>56439832.65</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8430,7 +8407,7 @@
       <c r="C23" s="6" t="n">
         <v>4692500</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="10" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -8448,7 +8425,7 @@
       <c r="C24" s="6" t="n">
         <v>2505800</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="10" t="n">
         <v>0.19</v>
       </c>
     </row>
@@ -8466,7 +8443,7 @@
       <c r="C25" s="6" t="n">
         <v>1155000</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="10" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -8484,7 +8461,7 @@
       <c r="C26" s="6" t="n">
         <v>516000</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="10" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -8502,7 +8479,7 @@
       <c r="C27" s="6" t="n">
         <v>441570</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="10" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -8520,7 +8497,7 @@
       <c r="C28" s="6" t="n">
         <v>337440</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="10" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -8538,7 +8515,7 @@
       <c r="C29" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8556,7 +8533,7 @@
       <c r="C30" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8574,7 +8551,7 @@
       <c r="C31" s="6" t="n">
         <v>279349.86</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8592,7 +8569,7 @@
       <c r="C32" s="6" t="n">
         <v>264850</v>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8610,7 +8587,7 @@
       <c r="C33" s="6" t="n">
         <v>254000</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8628,7 +8605,7 @@
       <c r="C34" s="6" t="n">
         <v>247935.06</v>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8646,7 +8623,7 @@
       <c r="C35" s="6" t="n">
         <v>227800</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -8664,7 +8641,7 @@
       <c r="C36" s="6" t="n">
         <v>179400</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8682,7 +8659,7 @@
       <c r="C37" s="6" t="n">
         <v>159575</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8700,7 +8677,7 @@
       <c r="C38" s="6" t="n">
         <v>157671.72</v>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8718,7 +8695,7 @@
       <c r="C39" s="6" t="n">
         <v>152250</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8736,7 +8713,7 @@
       <c r="C40" s="6" t="n">
         <v>137116</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8754,7 +8731,7 @@
       <c r="C41" s="6" t="n">
         <v>114858</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8772,7 +8749,7 @@
       <c r="C42" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8790,7 +8767,7 @@
       <c r="C43" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8808,7 +8785,7 @@
       <c r="C44" s="6" t="n">
         <v>81075</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8826,7 +8803,7 @@
       <c r="C45" s="6" t="n">
         <v>77247</v>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -8844,7 +8821,7 @@
       <c r="C46" s="6" t="n">
         <v>53760</v>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8862,7 +8839,7 @@
       <c r="C47" s="6" t="n">
         <v>48301.44</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8880,7 +8857,7 @@
       <c r="C48" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8898,7 +8875,7 @@
       <c r="C49" s="6" t="n">
         <v>39200</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8916,7 +8893,7 @@
       <c r="C50" s="6" t="n">
         <v>37568</v>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8934,7 +8911,7 @@
       <c r="C51" s="6" t="n">
         <v>35920.61</v>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8952,7 +8929,7 @@
       <c r="C52" s="6" t="n">
         <v>29800</v>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8970,7 +8947,7 @@
       <c r="C53" s="6" t="n">
         <v>27629</v>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8988,7 +8965,7 @@
       <c r="C54" s="6" t="n">
         <v>26600</v>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9006,7 +8983,7 @@
       <c r="C55" s="6" t="n">
         <v>22130</v>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9024,7 +9001,7 @@
       <c r="C56" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9042,7 +9019,7 @@
       <c r="C57" s="6" t="n">
         <v>17900</v>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9060,7 +9037,7 @@
       <c r="C58" s="6" t="n">
         <v>17740</v>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9078,7 +9055,7 @@
       <c r="C59" s="6" t="n">
         <v>17060</v>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9096,7 +9073,7 @@
       <c r="C60" s="6" t="n">
         <v>16235.15</v>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9114,7 +9091,7 @@
       <c r="C61" s="6" t="n">
         <v>15120</v>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9132,7 +9109,7 @@
       <c r="C62" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9150,7 +9127,7 @@
       <c r="C63" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9168,7 +9145,7 @@
       <c r="C64" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9186,7 +9163,7 @@
       <c r="C65" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9204,7 +9181,7 @@
       <c r="C66" s="6" t="n">
         <v>7495</v>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9222,7 +9199,7 @@
       <c r="C67" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9240,7 +9217,7 @@
       <c r="C68" s="6" t="n">
         <v>5100</v>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9258,7 +9235,7 @@
       <c r="C69" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="D69" s="13" t="n">
+      <c r="D69" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9276,7 +9253,7 @@
       <c r="C70" s="6" t="n">
         <v>1100</v>
       </c>
-      <c r="D70" s="13" t="n">
+      <c r="D70" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9294,21 +9271,21 @@
       <c r="C71" s="9" t="n">
         <v>13352996.84</v>
       </c>
-      <c r="D71" s="14" t="n">
+      <c r="D71" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>ВСЕГО ПО СЧЁТУ 60</t>
         </is>
       </c>
-      <c r="B72" s="15" t="inlineStr"/>
-      <c r="C72" s="16" t="n">
+      <c r="B72" s="13" t="inlineStr"/>
+      <c r="C72" s="14" t="n">
         <v>69792829.48999999</v>
       </c>
-      <c r="D72" s="17" t="n"/>
+      <c r="D72" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11244,16 +11221,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Начальное сальдо</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="14" t="n">
         <v>2691202.95</v>
       </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="17" t="inlineStr"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -11539,19 +11516,19 @@
       <c r="C22" s="9" t="n">
         <v>658588463.84</v>
       </c>
-      <c r="D22" s="18" t="inlineStr"/>
+      <c r="D22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Конечное сальдо</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="14" t="n">
         <v>19035318.76</v>
       </c>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>'= начальное + поступления − списания</t>
         </is>
@@ -11637,13 +11614,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>4180781.46</v>
+        <v>4229901.79</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>13054662.21</v>
+        <v>13039550.06</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>17235443.67</v>
+        <v>17269451.85</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -11663,13 +11640,13 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>38242853.41</v>
+        <v>38005133.99</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>38242853.41</v>
+        <v>38005133.99</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>76485706.81999999</v>
+        <v>76010267.98999999</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -11689,13 +11666,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1479732.43</v>
+        <v>1479304.66</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1479732.43</v>
+        <v>1479304.66</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2959464.86</v>
+        <v>2958609.32</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -11715,13 +11692,13 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>130619.32</v>
+        <v>130956.99</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>130619.32</v>
+        <v>130956.99</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>261238.64</v>
+        <v>261913.99</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -11756,26 +11733,26 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>− ½ общих расходов, в том числе:</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
-        <v>-43760221.15</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>-43760221.17</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>-87520442.31</v>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="C10" s="18" t="n">
+        <v>-43573477.57</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>-43573477.59</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-87146955.15000001</v>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>все расходы месяца без личных, пополам</t>
         </is>
@@ -11861,13 +11838,13 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-186743.58</v>
+        <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-186743.58</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-373487.16</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -11966,26 +11943,26 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>− Личные расходы (каждый свои), в том числе:</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="18" t="n">
         <v>-170861.64</v>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D21" s="18" t="n">
         <v>-1487162.05</v>
       </c>
-      <c r="E21" s="20" t="n">
+      <c r="E21" s="18" t="n">
         <v>-1658023.69</v>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>заказано лично под врача, пополам не делится</t>
         </is>
@@ -12039,15 +12016,15 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>301072.45</v>
+        <v>299126.85</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>7858652.77</v>
+        <v>7792474.7</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>8159725.23</v>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
+        <v>8091601.55</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>сумма шагов выше</t>
         </is>
@@ -12117,15 +12094,15 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>25077615.47</v>
+        <v>25075669.87</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>47252271.98</v>
+        <v>47186093.91</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>72329887.45999999</v>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
+        <v>72261763.78</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>доход + остаток − дивиденды − резерв</t>
         </is>
@@ -12203,12 +12180,12 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>96941853.98999999</v>
-      </c>
-      <c r="E5" s="18" t="n">
+        <v>96500243.15000001</v>
+      </c>
+      <c r="E5" s="16" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12225,10 +12202,10 @@
         <v>-39819623</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>57122230.99</v>
+        <v>56680620.15</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="7">
@@ -12244,10 +12221,10 @@
         <v>-16620209.65</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>40502021.34</v>
+        <v>40060410.5</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="8">
@@ -12263,7 +12240,7 @@
         <v>-18665350.79</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>21836670.55</v>
+        <v>21395059.71</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>19.3</v>
@@ -12282,10 +12259,10 @@
         <v>-12836996.84</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8999673.710000001</v>
+        <v>8558062.869999999</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="10">
@@ -12301,7 +12278,7 @@
         <v>-516000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>8483673.710000001</v>
+        <v>8042062.87</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0.5</v>
@@ -12317,13 +12294,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>-720285.72</v>
+        <v>-346798.56</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>7763387.99</v>
+        <v>7695264.31</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -12339,9 +12316,9 @@
         <v>396337.24</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8159725.23</v>
-      </c>
-      <c r="E12" s="18" t="n">
+        <v>8091601.55</v>
+      </c>
+      <c r="E12" s="16" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -12355,12 +12332,12 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>8159725.23</v>
+        <v>8091601.55</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>8159725.23</v>
-      </c>
-      <c r="E13" s="18" t="n">
+        <v>8091601.55</v>
+      </c>
+      <c r="E13" s="16" t="n">
         <v>8.4</v>
       </c>
     </row>
